--- a/backend/catalogues_src/Grade 10 Technical Science Catalogue.xlsx
+++ b/backend/catalogues_src/Grade 10 Technical Science Catalogue.xlsx
@@ -30,7 +30,7 @@
     <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -190,8 +190,14 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill/>
     </fill>
@@ -382,6 +388,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -966,7 +978,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -1145,6 +1157,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="17" fontId="21" fillId="33" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="21" fillId="33" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="17" fontId="21" fillId="33" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1530,15 +1548,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:L160"/>
+  <dimension ref="B2:L160"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="8.12844036697248" customWidth="1" style="25" min="1" max="1"/>
     <col width="15.6238532110092" customWidth="1" style="25" min="2" max="3"/>
     <col width="30.6238532110092" customWidth="1" style="25" min="4" max="36"/>
+    <col width="13" customWidth="1" style="25" min="5" max="5"/>
+    <col width="13" customWidth="1" style="25" min="6" max="6"/>
+    <col width="13" customWidth="1" style="25" min="7" max="7"/>
+    <col width="13" customWidth="1" style="25" min="8" max="8"/>
+    <col width="13" customWidth="1" style="25" min="9" max="9"/>
+    <col width="13" customWidth="1" style="25" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="61" t="inlineStr">
         <is>
@@ -1622,12 +1645,12 @@
       </c>
       <c r="C5" s="35" t="n"/>
       <c r="D5" s="36" t="n"/>
-      <c r="E5" s="37" t="n"/>
+      <c r="E5" s="36" t="n"/>
       <c r="F5" s="36" t="n"/>
-      <c r="G5" s="37" t="n"/>
+      <c r="G5" s="36" t="n"/>
       <c r="H5" s="36" t="n"/>
-      <c r="I5" s="40" t="n"/>
-      <c r="J5" s="55" t="n"/>
+      <c r="I5" s="36" t="n"/>
+      <c r="J5" s="36" t="n"/>
       <c r="K5" s="49" t="n"/>
       <c r="L5" s="49" t="n"/>
     </row>
@@ -1638,13 +1661,13 @@
         </is>
       </c>
       <c r="C6" s="39" t="n"/>
-      <c r="D6" s="40" t="n"/>
-      <c r="E6" s="41" t="n"/>
-      <c r="F6" s="40" t="n"/>
-      <c r="G6" s="41" t="n"/>
-      <c r="H6" s="40" t="n"/>
-      <c r="I6" s="40" t="n"/>
-      <c r="J6" s="55" t="n"/>
+      <c r="D6" s="36" t="n"/>
+      <c r="E6" s="36" t="n"/>
+      <c r="F6" s="36" t="n"/>
+      <c r="G6" s="36" t="n"/>
+      <c r="H6" s="36" t="n"/>
+      <c r="I6" s="36" t="n"/>
+      <c r="J6" s="36" t="n"/>
       <c r="K6" s="49" t="n"/>
       <c r="L6" s="49" t="n"/>
     </row>
@@ -1656,12 +1679,12 @@
       </c>
       <c r="C7" s="35" t="n"/>
       <c r="D7" s="36" t="n"/>
-      <c r="E7" s="37" t="n"/>
+      <c r="E7" s="36" t="n"/>
       <c r="F7" s="36" t="n"/>
-      <c r="G7" s="37" t="n"/>
+      <c r="G7" s="36" t="n"/>
       <c r="H7" s="36" t="n"/>
       <c r="I7" s="36" t="n"/>
-      <c r="J7" s="56" t="n"/>
+      <c r="J7" s="36" t="n"/>
       <c r="K7" s="49" t="n"/>
       <c r="L7" s="49" t="n"/>
     </row>
@@ -1673,12 +1696,12 @@
       </c>
       <c r="C8" s="35" t="n"/>
       <c r="D8" s="36" t="n"/>
-      <c r="E8" s="37" t="n"/>
+      <c r="E8" s="36" t="n"/>
       <c r="F8" s="36" t="n"/>
-      <c r="G8" s="37" t="n"/>
+      <c r="G8" s="36" t="n"/>
       <c r="H8" s="36" t="n"/>
       <c r="I8" s="36" t="n"/>
-      <c r="J8" s="56" t="n"/>
+      <c r="J8" s="36" t="n"/>
       <c r="K8" s="49" t="n"/>
       <c r="L8" s="49" t="n"/>
     </row>
@@ -1690,12 +1713,12 @@
       </c>
       <c r="C9" s="35" t="n"/>
       <c r="D9" s="36" t="n"/>
-      <c r="E9" s="37" t="n"/>
+      <c r="E9" s="36" t="n"/>
       <c r="F9" s="36" t="n"/>
-      <c r="G9" s="37" t="n"/>
+      <c r="G9" s="36" t="n"/>
       <c r="H9" s="36" t="n"/>
       <c r="I9" s="36" t="n"/>
-      <c r="J9" s="56" t="n"/>
+      <c r="J9" s="36" t="n"/>
       <c r="K9" s="49" t="n"/>
       <c r="L9" s="49" t="n"/>
     </row>
@@ -1707,12 +1730,12 @@
       </c>
       <c r="C10" s="35" t="n"/>
       <c r="D10" s="36" t="n"/>
-      <c r="E10" s="37" t="n"/>
+      <c r="E10" s="36" t="n"/>
       <c r="F10" s="36" t="n"/>
-      <c r="G10" s="37" t="n"/>
+      <c r="G10" s="36" t="n"/>
       <c r="H10" s="36" t="n"/>
       <c r="I10" s="36" t="n"/>
-      <c r="J10" s="56" t="n"/>
+      <c r="J10" s="36" t="n"/>
       <c r="K10" s="49" t="n"/>
       <c r="L10" s="49" t="n"/>
     </row>
@@ -1724,12 +1747,12 @@
       </c>
       <c r="C11" s="35" t="n"/>
       <c r="D11" s="36" t="n"/>
-      <c r="E11" s="42" t="n"/>
-      <c r="F11" s="43" t="n"/>
-      <c r="G11" s="42" t="n"/>
-      <c r="H11" s="43" t="n"/>
-      <c r="I11" s="43" t="n"/>
-      <c r="J11" s="57" t="n"/>
+      <c r="E11" s="36" t="n"/>
+      <c r="F11" s="36" t="n"/>
+      <c r="G11" s="36" t="n"/>
+      <c r="H11" s="36" t="n"/>
+      <c r="I11" s="36" t="n"/>
+      <c r="J11" s="36" t="n"/>
       <c r="K11" s="49" t="n"/>
       <c r="L11" s="49" t="n"/>
     </row>
@@ -1741,12 +1764,12 @@
       </c>
       <c r="C12" s="35" t="n"/>
       <c r="D12" s="36" t="n"/>
-      <c r="E12" s="37" t="n"/>
+      <c r="E12" s="36" t="n"/>
       <c r="F12" s="36" t="n"/>
-      <c r="G12" s="37" t="n"/>
+      <c r="G12" s="36" t="n"/>
       <c r="H12" s="36" t="n"/>
       <c r="I12" s="36" t="n"/>
-      <c r="J12" s="56" t="n"/>
+      <c r="J12" s="36" t="n"/>
       <c r="K12" s="49" t="n"/>
       <c r="L12" s="49" t="n"/>
     </row>
@@ -1758,12 +1781,12 @@
       </c>
       <c r="C13" s="35" t="n"/>
       <c r="D13" s="36" t="n"/>
-      <c r="E13" s="37" t="n"/>
+      <c r="E13" s="36" t="n"/>
       <c r="F13" s="36" t="n"/>
-      <c r="G13" s="37" t="n"/>
+      <c r="G13" s="36" t="n"/>
       <c r="H13" s="36" t="n"/>
       <c r="I13" s="36" t="n"/>
-      <c r="J13" s="56" t="n"/>
+      <c r="J13" s="36" t="n"/>
       <c r="K13" s="49" t="n"/>
       <c r="L13" s="49" t="n"/>
     </row>
@@ -1775,12 +1798,12 @@
       </c>
       <c r="C14" s="35" t="n"/>
       <c r="D14" s="36" t="n"/>
-      <c r="E14" s="37" t="n"/>
+      <c r="E14" s="36" t="n"/>
       <c r="F14" s="36" t="n"/>
-      <c r="G14" s="37" t="n"/>
+      <c r="G14" s="36" t="n"/>
       <c r="H14" s="36" t="n"/>
       <c r="I14" s="36" t="n"/>
-      <c r="J14" s="56" t="n"/>
+      <c r="J14" s="36" t="n"/>
       <c r="K14" s="49" t="n"/>
       <c r="L14" s="49" t="n"/>
     </row>
@@ -1792,12 +1815,12 @@
       </c>
       <c r="C15" s="35" t="n"/>
       <c r="D15" s="36" t="n"/>
-      <c r="E15" s="37" t="n"/>
+      <c r="E15" s="36" t="n"/>
       <c r="F15" s="36" t="n"/>
-      <c r="G15" s="37" t="n"/>
+      <c r="G15" s="36" t="n"/>
       <c r="H15" s="36" t="n"/>
       <c r="I15" s="36" t="n"/>
-      <c r="J15" s="56" t="n"/>
+      <c r="J15" s="36" t="n"/>
       <c r="K15" s="49" t="n"/>
       <c r="L15" s="49" t="n"/>
     </row>
@@ -1809,12 +1832,12 @@
       </c>
       <c r="C16" s="35" t="n"/>
       <c r="D16" s="36" t="n"/>
-      <c r="E16" s="37" t="n"/>
+      <c r="E16" s="36" t="n"/>
       <c r="F16" s="36" t="n"/>
-      <c r="G16" s="37" t="n"/>
+      <c r="G16" s="36" t="n"/>
       <c r="H16" s="36" t="n"/>
       <c r="I16" s="36" t="n"/>
-      <c r="J16" s="56" t="n"/>
+      <c r="J16" s="36" t="n"/>
       <c r="K16" s="49" t="n"/>
       <c r="L16" s="49" t="n"/>
     </row>
@@ -1826,12 +1849,12 @@
       </c>
       <c r="C17" s="35" t="n"/>
       <c r="D17" s="36" t="n"/>
-      <c r="E17" s="37" t="n"/>
+      <c r="E17" s="36" t="n"/>
       <c r="F17" s="36" t="n"/>
-      <c r="G17" s="37" t="n"/>
+      <c r="G17" s="36" t="n"/>
       <c r="H17" s="36" t="n"/>
       <c r="I17" s="36" t="n"/>
-      <c r="J17" s="56" t="n"/>
+      <c r="J17" s="36" t="n"/>
       <c r="K17" s="49" t="n"/>
       <c r="L17" s="49" t="n"/>
     </row>
@@ -1843,12 +1866,12 @@
       </c>
       <c r="C18" s="35" t="n"/>
       <c r="D18" s="36" t="n"/>
-      <c r="E18" s="37" t="n"/>
+      <c r="E18" s="36" t="n"/>
       <c r="F18" s="36" t="n"/>
-      <c r="G18" s="37" t="n"/>
+      <c r="G18" s="36" t="n"/>
       <c r="H18" s="36" t="n"/>
       <c r="I18" s="36" t="n"/>
-      <c r="J18" s="56" t="n"/>
+      <c r="J18" s="36" t="n"/>
       <c r="K18" s="49" t="n"/>
       <c r="L18" s="49" t="n"/>
     </row>
@@ -1860,12 +1883,12 @@
       </c>
       <c r="C19" s="35" t="n"/>
       <c r="D19" s="36" t="n"/>
-      <c r="E19" s="37" t="n"/>
+      <c r="E19" s="36" t="n"/>
       <c r="F19" s="36" t="n"/>
-      <c r="G19" s="37" t="n"/>
+      <c r="G19" s="36" t="n"/>
       <c r="H19" s="36" t="n"/>
       <c r="I19" s="36" t="n"/>
-      <c r="J19" s="56" t="n"/>
+      <c r="J19" s="36" t="n"/>
       <c r="K19" s="49" t="n"/>
       <c r="L19" s="49" t="n"/>
     </row>
@@ -1876,13 +1899,13 @@
         </is>
       </c>
       <c r="C20" s="45" t="n"/>
-      <c r="D20" s="46" t="n"/>
-      <c r="E20" s="47" t="n"/>
-      <c r="F20" s="46" t="n"/>
-      <c r="G20" s="47" t="n"/>
-      <c r="H20" s="46" t="n"/>
-      <c r="I20" s="46" t="n"/>
-      <c r="J20" s="58" t="n"/>
+      <c r="D20" s="36" t="n"/>
+      <c r="E20" s="36" t="n"/>
+      <c r="F20" s="36" t="n"/>
+      <c r="G20" s="36" t="n"/>
+      <c r="H20" s="36" t="n"/>
+      <c r="I20" s="36" t="n"/>
+      <c r="J20" s="36" t="n"/>
       <c r="K20" s="49" t="n"/>
       <c r="L20" s="49" t="n"/>
     </row>
@@ -1933,7 +1956,7 @@
           <t>Heat &amp; Temperature</t>
         </is>
       </c>
-      <c r="F23" s="24" t="inlineStr">
+      <c r="F23" s="31" t="inlineStr">
         <is>
           <t>Waves, Sound &amp; Light</t>
         </is>
@@ -1950,7 +1973,7 @@
       <c r="C24" s="65" t="n"/>
       <c r="D24" s="66" t="n"/>
       <c r="E24" s="66" t="n"/>
-      <c r="F24" s="65" t="n"/>
+      <c r="F24" s="66" t="n"/>
       <c r="I24" s="59" t="n"/>
       <c r="J24" s="53" t="n"/>
       <c r="K24" s="60" t="n"/>
@@ -1964,7 +1987,7 @@
       </c>
       <c r="C25" s="35" t="n"/>
       <c r="D25" s="36" t="n"/>
-      <c r="E25" s="37" t="n"/>
+      <c r="E25" s="36" t="n"/>
       <c r="F25" s="36" t="n"/>
       <c r="G25" s="49" t="n"/>
       <c r="H25" s="49" t="n"/>
@@ -1980,9 +2003,9 @@
         </is>
       </c>
       <c r="C26" s="39" t="n"/>
-      <c r="D26" s="40" t="n"/>
-      <c r="E26" s="41" t="n"/>
-      <c r="F26" s="40" t="n"/>
+      <c r="D26" s="36" t="n"/>
+      <c r="E26" s="36" t="n"/>
+      <c r="F26" s="36" t="n"/>
       <c r="G26" s="49" t="n"/>
       <c r="H26" s="49" t="n"/>
       <c r="I26" s="59" t="n"/>
@@ -1998,7 +2021,7 @@
       </c>
       <c r="C27" s="35" t="n"/>
       <c r="D27" s="36" t="n"/>
-      <c r="E27" s="37" t="n"/>
+      <c r="E27" s="36" t="n"/>
       <c r="F27" s="36" t="n"/>
       <c r="G27" s="49" t="n"/>
       <c r="H27" s="49" t="n"/>
@@ -2015,7 +2038,7 @@
       </c>
       <c r="C28" s="35" t="n"/>
       <c r="D28" s="36" t="n"/>
-      <c r="E28" s="37" t="n"/>
+      <c r="E28" s="36" t="n"/>
       <c r="F28" s="36" t="n"/>
       <c r="G28" s="49" t="n"/>
       <c r="H28" s="49" t="n"/>
@@ -2032,7 +2055,7 @@
       </c>
       <c r="C29" s="35" t="n"/>
       <c r="D29" s="36" t="n"/>
-      <c r="E29" s="37" t="n"/>
+      <c r="E29" s="36" t="n"/>
       <c r="F29" s="36" t="n"/>
       <c r="G29" s="49" t="n"/>
       <c r="H29" s="49" t="n"/>
@@ -2049,7 +2072,7 @@
       </c>
       <c r="C30" s="35" t="n"/>
       <c r="D30" s="36" t="n"/>
-      <c r="E30" s="37" t="n"/>
+      <c r="E30" s="36" t="n"/>
       <c r="F30" s="36" t="n"/>
       <c r="G30" s="49" t="n"/>
       <c r="H30" s="49" t="n"/>
@@ -2065,9 +2088,9 @@
         </is>
       </c>
       <c r="C31" s="35" t="n"/>
-      <c r="D31" s="43" t="n"/>
-      <c r="E31" s="42" t="n"/>
-      <c r="F31" s="43" t="n"/>
+      <c r="D31" s="36" t="n"/>
+      <c r="E31" s="36" t="n"/>
+      <c r="F31" s="36" t="n"/>
       <c r="G31" s="49" t="n"/>
       <c r="H31" s="49" t="n"/>
       <c r="I31" s="59" t="n"/>
@@ -2083,7 +2106,7 @@
       </c>
       <c r="C32" s="35" t="n"/>
       <c r="D32" s="36" t="n"/>
-      <c r="E32" s="37" t="n"/>
+      <c r="E32" s="36" t="n"/>
       <c r="F32" s="36" t="n"/>
       <c r="G32" s="49" t="n"/>
       <c r="H32" s="49" t="n"/>
@@ -2100,7 +2123,7 @@
       </c>
       <c r="C33" s="35" t="n"/>
       <c r="D33" s="36" t="n"/>
-      <c r="E33" s="37" t="n"/>
+      <c r="E33" s="36" t="n"/>
       <c r="F33" s="36" t="n"/>
       <c r="G33" s="49" t="n"/>
       <c r="H33" s="49" t="n"/>
@@ -2117,7 +2140,7 @@
       </c>
       <c r="C34" s="35" t="n"/>
       <c r="D34" s="36" t="n"/>
-      <c r="E34" s="37" t="n"/>
+      <c r="E34" s="36" t="n"/>
       <c r="F34" s="36" t="n"/>
       <c r="G34" s="49" t="n"/>
       <c r="H34" s="49" t="n"/>
@@ -2134,7 +2157,7 @@
       </c>
       <c r="C35" s="35" t="n"/>
       <c r="D35" s="36" t="n"/>
-      <c r="E35" s="37" t="n"/>
+      <c r="E35" s="36" t="n"/>
       <c r="F35" s="36" t="n"/>
       <c r="G35" s="49" t="n"/>
       <c r="H35" s="49" t="n"/>
@@ -2151,7 +2174,7 @@
       </c>
       <c r="C36" s="35" t="n"/>
       <c r="D36" s="36" t="n"/>
-      <c r="E36" s="37" t="n"/>
+      <c r="E36" s="36" t="n"/>
       <c r="F36" s="36" t="n"/>
       <c r="G36" s="49" t="n"/>
       <c r="H36" s="49" t="n"/>
@@ -2168,7 +2191,7 @@
       </c>
       <c r="C37" s="35" t="n"/>
       <c r="D37" s="36" t="n"/>
-      <c r="E37" s="37" t="n"/>
+      <c r="E37" s="36" t="n"/>
       <c r="F37" s="36" t="n"/>
       <c r="G37" s="49" t="n"/>
       <c r="H37" s="49" t="n"/>
@@ -2185,7 +2208,7 @@
       </c>
       <c r="C38" s="35" t="n"/>
       <c r="D38" s="36" t="n"/>
-      <c r="E38" s="37" t="n"/>
+      <c r="E38" s="36" t="n"/>
       <c r="F38" s="36" t="n"/>
       <c r="G38" s="49" t="n"/>
       <c r="H38" s="49" t="n"/>
@@ -2202,7 +2225,7 @@
       </c>
       <c r="C39" s="35" t="n"/>
       <c r="D39" s="36" t="n"/>
-      <c r="E39" s="37" t="n"/>
+      <c r="E39" s="36" t="n"/>
       <c r="F39" s="36" t="n"/>
       <c r="G39" s="49" t="n"/>
       <c r="H39" s="49" t="n"/>
@@ -2218,9 +2241,9 @@
         </is>
       </c>
       <c r="C40" s="45" t="n"/>
-      <c r="D40" s="46" t="n"/>
-      <c r="E40" s="47" t="n"/>
-      <c r="F40" s="46" t="n"/>
+      <c r="D40" s="36" t="n"/>
+      <c r="E40" s="36" t="n"/>
+      <c r="F40" s="36" t="n"/>
       <c r="G40" s="49" t="n"/>
       <c r="H40" s="49" t="n"/>
       <c r="I40" s="59" t="n"/>
@@ -2324,12 +2347,12 @@
       </c>
       <c r="C45" s="35" t="n"/>
       <c r="D45" s="36" t="n"/>
-      <c r="E45" s="37" t="n"/>
+      <c r="E45" s="36" t="n"/>
       <c r="F45" s="36" t="n"/>
-      <c r="G45" s="37" t="n"/>
+      <c r="G45" s="36" t="n"/>
       <c r="H45" s="36" t="n"/>
-      <c r="I45" s="40" t="n"/>
-      <c r="J45" s="55" t="n"/>
+      <c r="I45" s="36" t="n"/>
+      <c r="J45" s="36" t="n"/>
       <c r="K45" s="49" t="n"/>
       <c r="L45" s="49" t="n"/>
     </row>
@@ -2340,13 +2363,13 @@
         </is>
       </c>
       <c r="C46" s="39" t="n"/>
-      <c r="D46" s="40" t="n"/>
-      <c r="E46" s="41" t="n"/>
-      <c r="F46" s="40" t="n"/>
-      <c r="G46" s="41" t="n"/>
-      <c r="H46" s="40" t="n"/>
-      <c r="I46" s="40" t="n"/>
-      <c r="J46" s="55" t="n"/>
+      <c r="D46" s="36" t="n"/>
+      <c r="E46" s="36" t="n"/>
+      <c r="F46" s="36" t="n"/>
+      <c r="G46" s="36" t="n"/>
+      <c r="H46" s="36" t="n"/>
+      <c r="I46" s="36" t="n"/>
+      <c r="J46" s="36" t="n"/>
       <c r="K46" s="49" t="n"/>
       <c r="L46" s="49" t="n"/>
     </row>
@@ -2358,12 +2381,12 @@
       </c>
       <c r="C47" s="35" t="n"/>
       <c r="D47" s="36" t="n"/>
-      <c r="E47" s="37" t="n"/>
+      <c r="E47" s="36" t="n"/>
       <c r="F47" s="36" t="n"/>
-      <c r="G47" s="37" t="n"/>
+      <c r="G47" s="36" t="n"/>
       <c r="H47" s="36" t="n"/>
       <c r="I47" s="36" t="n"/>
-      <c r="J47" s="56" t="n"/>
+      <c r="J47" s="36" t="n"/>
       <c r="K47" s="49" t="n"/>
       <c r="L47" s="49" t="n"/>
     </row>
@@ -2375,12 +2398,12 @@
       </c>
       <c r="C48" s="35" t="n"/>
       <c r="D48" s="36" t="n"/>
-      <c r="E48" s="37" t="n"/>
+      <c r="E48" s="36" t="n"/>
       <c r="F48" s="36" t="n"/>
-      <c r="G48" s="37" t="n"/>
+      <c r="G48" s="36" t="n"/>
       <c r="H48" s="36" t="n"/>
       <c r="I48" s="36" t="n"/>
-      <c r="J48" s="56" t="n"/>
+      <c r="J48" s="36" t="n"/>
       <c r="K48" s="49" t="n"/>
       <c r="L48" s="49" t="n"/>
     </row>
@@ -2392,12 +2415,12 @@
       </c>
       <c r="C49" s="35" t="n"/>
       <c r="D49" s="36" t="n"/>
-      <c r="E49" s="37" t="n"/>
+      <c r="E49" s="36" t="n"/>
       <c r="F49" s="36" t="n"/>
-      <c r="G49" s="37" t="n"/>
+      <c r="G49" s="36" t="n"/>
       <c r="H49" s="36" t="n"/>
       <c r="I49" s="36" t="n"/>
-      <c r="J49" s="56" t="n"/>
+      <c r="J49" s="36" t="n"/>
       <c r="K49" s="49" t="n"/>
       <c r="L49" s="49" t="n"/>
     </row>
@@ -2409,12 +2432,12 @@
       </c>
       <c r="C50" s="35" t="n"/>
       <c r="D50" s="36" t="n"/>
-      <c r="E50" s="37" t="n"/>
+      <c r="E50" s="36" t="n"/>
       <c r="F50" s="36" t="n"/>
-      <c r="G50" s="37" t="n"/>
+      <c r="G50" s="36" t="n"/>
       <c r="H50" s="36" t="n"/>
       <c r="I50" s="36" t="n"/>
-      <c r="J50" s="56" t="n"/>
+      <c r="J50" s="36" t="n"/>
       <c r="K50" s="49" t="n"/>
       <c r="L50" s="49" t="n"/>
     </row>
@@ -2426,12 +2449,12 @@
       </c>
       <c r="C51" s="35" t="n"/>
       <c r="D51" s="36" t="n"/>
-      <c r="E51" s="42" t="n"/>
-      <c r="F51" s="43" t="n"/>
-      <c r="G51" s="42" t="n"/>
-      <c r="H51" s="43" t="n"/>
-      <c r="I51" s="43" t="n"/>
-      <c r="J51" s="57" t="n"/>
+      <c r="E51" s="36" t="n"/>
+      <c r="F51" s="36" t="n"/>
+      <c r="G51" s="36" t="n"/>
+      <c r="H51" s="36" t="n"/>
+      <c r="I51" s="36" t="n"/>
+      <c r="J51" s="36" t="n"/>
       <c r="K51" s="49" t="n"/>
       <c r="L51" s="49" t="n"/>
     </row>
@@ -2443,12 +2466,12 @@
       </c>
       <c r="C52" s="35" t="n"/>
       <c r="D52" s="36" t="n"/>
-      <c r="E52" s="37" t="n"/>
+      <c r="E52" s="36" t="n"/>
       <c r="F52" s="36" t="n"/>
-      <c r="G52" s="37" t="n"/>
+      <c r="G52" s="36" t="n"/>
       <c r="H52" s="36" t="n"/>
       <c r="I52" s="36" t="n"/>
-      <c r="J52" s="56" t="n"/>
+      <c r="J52" s="36" t="n"/>
       <c r="K52" s="49" t="n"/>
       <c r="L52" s="49" t="n"/>
     </row>
@@ -2460,12 +2483,12 @@
       </c>
       <c r="C53" s="35" t="n"/>
       <c r="D53" s="36" t="n"/>
-      <c r="E53" s="37" t="n"/>
+      <c r="E53" s="36" t="n"/>
       <c r="F53" s="36" t="n"/>
-      <c r="G53" s="37" t="n"/>
+      <c r="G53" s="36" t="n"/>
       <c r="H53" s="36" t="n"/>
       <c r="I53" s="36" t="n"/>
-      <c r="J53" s="56" t="n"/>
+      <c r="J53" s="36" t="n"/>
       <c r="K53" s="49" t="n"/>
       <c r="L53" s="49" t="n"/>
     </row>
@@ -2477,12 +2500,12 @@
       </c>
       <c r="C54" s="35" t="n"/>
       <c r="D54" s="36" t="n"/>
-      <c r="E54" s="37" t="n"/>
+      <c r="E54" s="36" t="n"/>
       <c r="F54" s="36" t="n"/>
-      <c r="G54" s="37" t="n"/>
+      <c r="G54" s="36" t="n"/>
       <c r="H54" s="36" t="n"/>
       <c r="I54" s="36" t="n"/>
-      <c r="J54" s="56" t="n"/>
+      <c r="J54" s="36" t="n"/>
       <c r="K54" s="49" t="n"/>
       <c r="L54" s="49" t="n"/>
     </row>
@@ -2494,12 +2517,12 @@
       </c>
       <c r="C55" s="35" t="n"/>
       <c r="D55" s="36" t="n"/>
-      <c r="E55" s="37" t="n"/>
+      <c r="E55" s="36" t="n"/>
       <c r="F55" s="36" t="n"/>
-      <c r="G55" s="37" t="n"/>
+      <c r="G55" s="36" t="n"/>
       <c r="H55" s="36" t="n"/>
       <c r="I55" s="36" t="n"/>
-      <c r="J55" s="56" t="n"/>
+      <c r="J55" s="36" t="n"/>
       <c r="K55" s="49" t="n"/>
       <c r="L55" s="49" t="n"/>
     </row>
@@ -2511,12 +2534,12 @@
       </c>
       <c r="C56" s="35" t="n"/>
       <c r="D56" s="36" t="n"/>
-      <c r="E56" s="37" t="n"/>
+      <c r="E56" s="36" t="n"/>
       <c r="F56" s="36" t="n"/>
-      <c r="G56" s="37" t="n"/>
+      <c r="G56" s="36" t="n"/>
       <c r="H56" s="36" t="n"/>
       <c r="I56" s="36" t="n"/>
-      <c r="J56" s="56" t="n"/>
+      <c r="J56" s="36" t="n"/>
       <c r="K56" s="49" t="n"/>
       <c r="L56" s="49" t="n"/>
     </row>
@@ -2528,12 +2551,12 @@
       </c>
       <c r="C57" s="35" t="n"/>
       <c r="D57" s="36" t="n"/>
-      <c r="E57" s="37" t="n"/>
+      <c r="E57" s="36" t="n"/>
       <c r="F57" s="36" t="n"/>
-      <c r="G57" s="37" t="n"/>
+      <c r="G57" s="36" t="n"/>
       <c r="H57" s="36" t="n"/>
       <c r="I57" s="36" t="n"/>
-      <c r="J57" s="56" t="n"/>
+      <c r="J57" s="36" t="n"/>
       <c r="K57" s="49" t="n"/>
       <c r="L57" s="49" t="n"/>
     </row>
@@ -2545,12 +2568,12 @@
       </c>
       <c r="C58" s="35" t="n"/>
       <c r="D58" s="36" t="n"/>
-      <c r="E58" s="37" t="n"/>
+      <c r="E58" s="36" t="n"/>
       <c r="F58" s="36" t="n"/>
-      <c r="G58" s="37" t="n"/>
+      <c r="G58" s="36" t="n"/>
       <c r="H58" s="36" t="n"/>
       <c r="I58" s="36" t="n"/>
-      <c r="J58" s="56" t="n"/>
+      <c r="J58" s="36" t="n"/>
       <c r="K58" s="49" t="n"/>
       <c r="L58" s="49" t="n"/>
     </row>
@@ -2562,12 +2585,12 @@
       </c>
       <c r="C59" s="35" t="n"/>
       <c r="D59" s="36" t="n"/>
-      <c r="E59" s="37" t="n"/>
+      <c r="E59" s="36" t="n"/>
       <c r="F59" s="36" t="n"/>
-      <c r="G59" s="37" t="n"/>
+      <c r="G59" s="36" t="n"/>
       <c r="H59" s="36" t="n"/>
       <c r="I59" s="36" t="n"/>
-      <c r="J59" s="56" t="n"/>
+      <c r="J59" s="36" t="n"/>
       <c r="K59" s="49" t="n"/>
       <c r="L59" s="49" t="n"/>
     </row>
@@ -2578,13 +2601,13 @@
         </is>
       </c>
       <c r="C60" s="45" t="n"/>
-      <c r="D60" s="46" t="n"/>
-      <c r="E60" s="47" t="n"/>
-      <c r="F60" s="46" t="n"/>
-      <c r="G60" s="47" t="n"/>
-      <c r="H60" s="46" t="n"/>
-      <c r="I60" s="46" t="n"/>
-      <c r="J60" s="58" t="n"/>
+      <c r="D60" s="36" t="n"/>
+      <c r="E60" s="36" t="n"/>
+      <c r="F60" s="36" t="n"/>
+      <c r="G60" s="36" t="n"/>
+      <c r="H60" s="36" t="n"/>
+      <c r="I60" s="36" t="n"/>
+      <c r="J60" s="36" t="n"/>
       <c r="K60" s="49" t="n"/>
       <c r="L60" s="49" t="n"/>
     </row>
@@ -2635,7 +2658,7 @@
           <t>Heat &amp; Temperature</t>
         </is>
       </c>
-      <c r="F63" s="24" t="inlineStr">
+      <c r="F63" s="31" t="inlineStr">
         <is>
           <t>Waves, Sound &amp; Light</t>
         </is>
@@ -2652,7 +2675,7 @@
       <c r="C64" s="65" t="n"/>
       <c r="D64" s="66" t="n"/>
       <c r="E64" s="66" t="n"/>
-      <c r="F64" s="65" t="n"/>
+      <c r="F64" s="66" t="n"/>
       <c r="I64" s="53" t="n"/>
       <c r="J64" s="53" t="n"/>
       <c r="K64" s="60" t="n"/>
@@ -2666,7 +2689,7 @@
       </c>
       <c r="C65" s="35" t="n"/>
       <c r="D65" s="36" t="n"/>
-      <c r="E65" s="37" t="n"/>
+      <c r="E65" s="36" t="n"/>
       <c r="F65" s="36" t="n"/>
       <c r="G65" s="49" t="n"/>
       <c r="H65" s="49" t="n"/>
@@ -2682,9 +2705,9 @@
         </is>
       </c>
       <c r="C66" s="39" t="n"/>
-      <c r="D66" s="40" t="n"/>
-      <c r="E66" s="41" t="n"/>
-      <c r="F66" s="40" t="n"/>
+      <c r="D66" s="36" t="n"/>
+      <c r="E66" s="36" t="n"/>
+      <c r="F66" s="36" t="n"/>
       <c r="G66" s="49" t="n"/>
       <c r="H66" s="49" t="n"/>
       <c r="I66" s="53" t="n"/>
@@ -2700,7 +2723,7 @@
       </c>
       <c r="C67" s="35" t="n"/>
       <c r="D67" s="36" t="n"/>
-      <c r="E67" s="37" t="n"/>
+      <c r="E67" s="36" t="n"/>
       <c r="F67" s="36" t="n"/>
       <c r="G67" s="49" t="n"/>
       <c r="H67" s="49" t="n"/>
@@ -2717,7 +2740,7 @@
       </c>
       <c r="C68" s="35" t="n"/>
       <c r="D68" s="36" t="n"/>
-      <c r="E68" s="37" t="n"/>
+      <c r="E68" s="36" t="n"/>
       <c r="F68" s="36" t="n"/>
       <c r="G68" s="49" t="n"/>
       <c r="H68" s="49" t="n"/>
@@ -2734,7 +2757,7 @@
       </c>
       <c r="C69" s="35" t="n"/>
       <c r="D69" s="36" t="n"/>
-      <c r="E69" s="37" t="n"/>
+      <c r="E69" s="36" t="n"/>
       <c r="F69" s="36" t="n"/>
       <c r="G69" s="49" t="n"/>
       <c r="H69" s="49" t="n"/>
@@ -2751,7 +2774,7 @@
       </c>
       <c r="C70" s="35" t="n"/>
       <c r="D70" s="36" t="n"/>
-      <c r="E70" s="37" t="n"/>
+      <c r="E70" s="36" t="n"/>
       <c r="F70" s="36" t="n"/>
       <c r="G70" s="49" t="n"/>
       <c r="H70" s="49" t="n"/>
@@ -2767,9 +2790,9 @@
         </is>
       </c>
       <c r="C71" s="35" t="n"/>
-      <c r="D71" s="43" t="n"/>
-      <c r="E71" s="42" t="n"/>
-      <c r="F71" s="43" t="n"/>
+      <c r="D71" s="36" t="n"/>
+      <c r="E71" s="36" t="n"/>
+      <c r="F71" s="36" t="n"/>
       <c r="G71" s="49" t="n"/>
       <c r="H71" s="49" t="n"/>
       <c r="I71" s="53" t="n"/>
@@ -2785,7 +2808,7 @@
       </c>
       <c r="C72" s="35" t="n"/>
       <c r="D72" s="36" t="n"/>
-      <c r="E72" s="37" t="n"/>
+      <c r="E72" s="36" t="n"/>
       <c r="F72" s="36" t="n"/>
       <c r="G72" s="49" t="n"/>
       <c r="H72" s="49" t="n"/>
@@ -2802,7 +2825,7 @@
       </c>
       <c r="C73" s="35" t="n"/>
       <c r="D73" s="36" t="n"/>
-      <c r="E73" s="37" t="n"/>
+      <c r="E73" s="36" t="n"/>
       <c r="F73" s="36" t="n"/>
       <c r="G73" s="49" t="n"/>
       <c r="H73" s="49" t="n"/>
@@ -2819,7 +2842,7 @@
       </c>
       <c r="C74" s="35" t="n"/>
       <c r="D74" s="36" t="n"/>
-      <c r="E74" s="37" t="n"/>
+      <c r="E74" s="36" t="n"/>
       <c r="F74" s="36" t="n"/>
       <c r="G74" s="49" t="n"/>
       <c r="H74" s="49" t="n"/>
@@ -2836,7 +2859,7 @@
       </c>
       <c r="C75" s="35" t="n"/>
       <c r="D75" s="36" t="n"/>
-      <c r="E75" s="37" t="n"/>
+      <c r="E75" s="36" t="n"/>
       <c r="F75" s="36" t="n"/>
       <c r="G75" s="49" t="n"/>
       <c r="H75" s="49" t="n"/>
@@ -2853,7 +2876,7 @@
       </c>
       <c r="C76" s="35" t="n"/>
       <c r="D76" s="36" t="n"/>
-      <c r="E76" s="37" t="n"/>
+      <c r="E76" s="36" t="n"/>
       <c r="F76" s="36" t="n"/>
       <c r="G76" s="49" t="n"/>
       <c r="H76" s="49" t="n"/>
@@ -2870,7 +2893,7 @@
       </c>
       <c r="C77" s="35" t="n"/>
       <c r="D77" s="36" t="n"/>
-      <c r="E77" s="37" t="n"/>
+      <c r="E77" s="36" t="n"/>
       <c r="F77" s="36" t="n"/>
       <c r="G77" s="49" t="n"/>
       <c r="H77" s="49" t="n"/>
@@ -2887,7 +2910,7 @@
       </c>
       <c r="C78" s="35" t="n"/>
       <c r="D78" s="36" t="n"/>
-      <c r="E78" s="37" t="n"/>
+      <c r="E78" s="36" t="n"/>
       <c r="F78" s="36" t="n"/>
       <c r="G78" s="49" t="n"/>
       <c r="H78" s="49" t="n"/>
@@ -2904,7 +2927,7 @@
       </c>
       <c r="C79" s="35" t="n"/>
       <c r="D79" s="36" t="n"/>
-      <c r="E79" s="37" t="n"/>
+      <c r="E79" s="36" t="n"/>
       <c r="F79" s="36" t="n"/>
       <c r="G79" s="49" t="n"/>
       <c r="H79" s="49" t="n"/>
@@ -2920,9 +2943,9 @@
         </is>
       </c>
       <c r="C80" s="45" t="n"/>
-      <c r="D80" s="46" t="n"/>
-      <c r="E80" s="47" t="n"/>
-      <c r="F80" s="46" t="n"/>
+      <c r="D80" s="36" t="n"/>
+      <c r="E80" s="36" t="n"/>
+      <c r="F80" s="36" t="n"/>
       <c r="G80" s="49" t="n"/>
       <c r="H80" s="49" t="n"/>
       <c r="I80" s="53" t="n"/>
@@ -3026,12 +3049,12 @@
       </c>
       <c r="C85" s="35" t="n"/>
       <c r="D85" s="36" t="n"/>
-      <c r="E85" s="37" t="n"/>
+      <c r="E85" s="36" t="n"/>
       <c r="F85" s="36" t="n"/>
-      <c r="G85" s="37" t="n"/>
+      <c r="G85" s="36" t="n"/>
       <c r="H85" s="36" t="n"/>
-      <c r="I85" s="40" t="n"/>
-      <c r="J85" s="55" t="n"/>
+      <c r="I85" s="36" t="n"/>
+      <c r="J85" s="36" t="n"/>
       <c r="K85" s="49" t="n"/>
       <c r="L85" s="49" t="n"/>
     </row>
@@ -3042,13 +3065,13 @@
         </is>
       </c>
       <c r="C86" s="39" t="n"/>
-      <c r="D86" s="40" t="n"/>
-      <c r="E86" s="41" t="n"/>
-      <c r="F86" s="40" t="n"/>
-      <c r="G86" s="41" t="n"/>
-      <c r="H86" s="40" t="n"/>
-      <c r="I86" s="40" t="n"/>
-      <c r="J86" s="55" t="n"/>
+      <c r="D86" s="36" t="n"/>
+      <c r="E86" s="36" t="n"/>
+      <c r="F86" s="36" t="n"/>
+      <c r="G86" s="36" t="n"/>
+      <c r="H86" s="36" t="n"/>
+      <c r="I86" s="36" t="n"/>
+      <c r="J86" s="36" t="n"/>
       <c r="K86" s="49" t="n"/>
       <c r="L86" s="49" t="n"/>
     </row>
@@ -3060,12 +3083,12 @@
       </c>
       <c r="C87" s="35" t="n"/>
       <c r="D87" s="36" t="n"/>
-      <c r="E87" s="37" t="n"/>
+      <c r="E87" s="36" t="n"/>
       <c r="F87" s="36" t="n"/>
-      <c r="G87" s="37" t="n"/>
+      <c r="G87" s="36" t="n"/>
       <c r="H87" s="36" t="n"/>
       <c r="I87" s="36" t="n"/>
-      <c r="J87" s="56" t="n"/>
+      <c r="J87" s="36" t="n"/>
       <c r="K87" s="49" t="n"/>
       <c r="L87" s="49" t="n"/>
     </row>
@@ -3077,12 +3100,12 @@
       </c>
       <c r="C88" s="35" t="n"/>
       <c r="D88" s="36" t="n"/>
-      <c r="E88" s="37" t="n"/>
+      <c r="E88" s="36" t="n"/>
       <c r="F88" s="36" t="n"/>
-      <c r="G88" s="37" t="n"/>
+      <c r="G88" s="36" t="n"/>
       <c r="H88" s="36" t="n"/>
       <c r="I88" s="36" t="n"/>
-      <c r="J88" s="56" t="n"/>
+      <c r="J88" s="36" t="n"/>
       <c r="K88" s="49" t="n"/>
       <c r="L88" s="49" t="n"/>
     </row>
@@ -3094,12 +3117,12 @@
       </c>
       <c r="C89" s="35" t="n"/>
       <c r="D89" s="36" t="n"/>
-      <c r="E89" s="37" t="n"/>
+      <c r="E89" s="36" t="n"/>
       <c r="F89" s="36" t="n"/>
-      <c r="G89" s="37" t="n"/>
+      <c r="G89" s="36" t="n"/>
       <c r="H89" s="36" t="n"/>
       <c r="I89" s="36" t="n"/>
-      <c r="J89" s="56" t="n"/>
+      <c r="J89" s="36" t="n"/>
       <c r="K89" s="49" t="n"/>
       <c r="L89" s="49" t="n"/>
     </row>
@@ -3111,12 +3134,12 @@
       </c>
       <c r="C90" s="35" t="n"/>
       <c r="D90" s="36" t="n"/>
-      <c r="E90" s="37" t="n"/>
+      <c r="E90" s="36" t="n"/>
       <c r="F90" s="36" t="n"/>
-      <c r="G90" s="37" t="n"/>
+      <c r="G90" s="36" t="n"/>
       <c r="H90" s="36" t="n"/>
       <c r="I90" s="36" t="n"/>
-      <c r="J90" s="56" t="n"/>
+      <c r="J90" s="36" t="n"/>
       <c r="K90" s="49" t="n"/>
       <c r="L90" s="49" t="n"/>
     </row>
@@ -3128,12 +3151,12 @@
       </c>
       <c r="C91" s="35" t="n"/>
       <c r="D91" s="36" t="n"/>
-      <c r="E91" s="42" t="n"/>
-      <c r="F91" s="43" t="n"/>
-      <c r="G91" s="42" t="n"/>
-      <c r="H91" s="43" t="n"/>
-      <c r="I91" s="43" t="n"/>
-      <c r="J91" s="57" t="n"/>
+      <c r="E91" s="36" t="n"/>
+      <c r="F91" s="36" t="n"/>
+      <c r="G91" s="36" t="n"/>
+      <c r="H91" s="36" t="n"/>
+      <c r="I91" s="36" t="n"/>
+      <c r="J91" s="36" t="n"/>
       <c r="K91" s="49" t="n"/>
       <c r="L91" s="49" t="n"/>
     </row>
@@ -3145,12 +3168,12 @@
       </c>
       <c r="C92" s="35" t="n"/>
       <c r="D92" s="36" t="n"/>
-      <c r="E92" s="37" t="n"/>
+      <c r="E92" s="36" t="n"/>
       <c r="F92" s="36" t="n"/>
-      <c r="G92" s="37" t="n"/>
+      <c r="G92" s="36" t="n"/>
       <c r="H92" s="36" t="n"/>
       <c r="I92" s="36" t="n"/>
-      <c r="J92" s="56" t="n"/>
+      <c r="J92" s="36" t="n"/>
       <c r="K92" s="49" t="n"/>
       <c r="L92" s="49" t="n"/>
     </row>
@@ -3162,12 +3185,12 @@
       </c>
       <c r="C93" s="35" t="n"/>
       <c r="D93" s="36" t="n"/>
-      <c r="E93" s="37" t="n"/>
+      <c r="E93" s="36" t="n"/>
       <c r="F93" s="36" t="n"/>
-      <c r="G93" s="37" t="n"/>
+      <c r="G93" s="36" t="n"/>
       <c r="H93" s="36" t="n"/>
       <c r="I93" s="36" t="n"/>
-      <c r="J93" s="56" t="n"/>
+      <c r="J93" s="36" t="n"/>
       <c r="K93" s="49" t="n"/>
       <c r="L93" s="49" t="n"/>
     </row>
@@ -3179,12 +3202,12 @@
       </c>
       <c r="C94" s="35" t="n"/>
       <c r="D94" s="36" t="n"/>
-      <c r="E94" s="37" t="n"/>
+      <c r="E94" s="36" t="n"/>
       <c r="F94" s="36" t="n"/>
-      <c r="G94" s="37" t="n"/>
+      <c r="G94" s="36" t="n"/>
       <c r="H94" s="36" t="n"/>
       <c r="I94" s="36" t="n"/>
-      <c r="J94" s="56" t="n"/>
+      <c r="J94" s="36" t="n"/>
       <c r="K94" s="49" t="n"/>
       <c r="L94" s="49" t="n"/>
     </row>
@@ -3196,12 +3219,12 @@
       </c>
       <c r="C95" s="35" t="n"/>
       <c r="D95" s="36" t="n"/>
-      <c r="E95" s="37" t="n"/>
+      <c r="E95" s="36" t="n"/>
       <c r="F95" s="36" t="n"/>
-      <c r="G95" s="37" t="n"/>
+      <c r="G95" s="36" t="n"/>
       <c r="H95" s="36" t="n"/>
       <c r="I95" s="36" t="n"/>
-      <c r="J95" s="56" t="n"/>
+      <c r="J95" s="36" t="n"/>
       <c r="K95" s="49" t="n"/>
       <c r="L95" s="49" t="n"/>
     </row>
@@ -3213,12 +3236,12 @@
       </c>
       <c r="C96" s="35" t="n"/>
       <c r="D96" s="36" t="n"/>
-      <c r="E96" s="37" t="n"/>
+      <c r="E96" s="36" t="n"/>
       <c r="F96" s="36" t="n"/>
-      <c r="G96" s="37" t="n"/>
+      <c r="G96" s="36" t="n"/>
       <c r="H96" s="36" t="n"/>
       <c r="I96" s="36" t="n"/>
-      <c r="J96" s="56" t="n"/>
+      <c r="J96" s="36" t="n"/>
       <c r="K96" s="49" t="n"/>
       <c r="L96" s="49" t="n"/>
     </row>
@@ -3230,12 +3253,12 @@
       </c>
       <c r="C97" s="35" t="n"/>
       <c r="D97" s="36" t="n"/>
-      <c r="E97" s="37" t="n"/>
+      <c r="E97" s="36" t="n"/>
       <c r="F97" s="36" t="n"/>
-      <c r="G97" s="37" t="n"/>
+      <c r="G97" s="36" t="n"/>
       <c r="H97" s="36" t="n"/>
       <c r="I97" s="36" t="n"/>
-      <c r="J97" s="56" t="n"/>
+      <c r="J97" s="36" t="n"/>
       <c r="K97" s="49" t="n"/>
       <c r="L97" s="49" t="n"/>
     </row>
@@ -3247,12 +3270,12 @@
       </c>
       <c r="C98" s="35" t="n"/>
       <c r="D98" s="36" t="n"/>
-      <c r="E98" s="37" t="n"/>
+      <c r="E98" s="36" t="n"/>
       <c r="F98" s="36" t="n"/>
-      <c r="G98" s="37" t="n"/>
+      <c r="G98" s="36" t="n"/>
       <c r="H98" s="36" t="n"/>
       <c r="I98" s="36" t="n"/>
-      <c r="J98" s="56" t="n"/>
+      <c r="J98" s="36" t="n"/>
       <c r="K98" s="49" t="n"/>
       <c r="L98" s="49" t="n"/>
     </row>
@@ -3264,12 +3287,12 @@
       </c>
       <c r="C99" s="35" t="n"/>
       <c r="D99" s="36" t="n"/>
-      <c r="E99" s="37" t="n"/>
+      <c r="E99" s="36" t="n"/>
       <c r="F99" s="36" t="n"/>
-      <c r="G99" s="37" t="n"/>
+      <c r="G99" s="36" t="n"/>
       <c r="H99" s="36" t="n"/>
       <c r="I99" s="36" t="n"/>
-      <c r="J99" s="56" t="n"/>
+      <c r="J99" s="36" t="n"/>
       <c r="K99" s="49" t="n"/>
       <c r="L99" s="49" t="n"/>
     </row>
@@ -3280,13 +3303,13 @@
         </is>
       </c>
       <c r="C100" s="45" t="n"/>
-      <c r="D100" s="46" t="n"/>
-      <c r="E100" s="47" t="n"/>
-      <c r="F100" s="46" t="n"/>
-      <c r="G100" s="47" t="n"/>
-      <c r="H100" s="46" t="n"/>
-      <c r="I100" s="46" t="n"/>
-      <c r="J100" s="58" t="n"/>
+      <c r="D100" s="36" t="n"/>
+      <c r="E100" s="36" t="n"/>
+      <c r="F100" s="36" t="n"/>
+      <c r="G100" s="36" t="n"/>
+      <c r="H100" s="36" t="n"/>
+      <c r="I100" s="36" t="n"/>
+      <c r="J100" s="36" t="n"/>
       <c r="K100" s="49" t="n"/>
       <c r="L100" s="49" t="n"/>
     </row>
@@ -3337,7 +3360,7 @@
           <t>Heat &amp; Temperature</t>
         </is>
       </c>
-      <c r="F103" s="24" t="inlineStr">
+      <c r="F103" s="31" t="inlineStr">
         <is>
           <t>Waves, Sound &amp; Light</t>
         </is>
@@ -3354,7 +3377,7 @@
       <c r="C104" s="65" t="n"/>
       <c r="D104" s="66" t="n"/>
       <c r="E104" s="66" t="n"/>
-      <c r="F104" s="65" t="n"/>
+      <c r="F104" s="66" t="n"/>
       <c r="I104" s="53" t="n"/>
       <c r="J104" s="53" t="n"/>
       <c r="K104" s="60" t="n"/>
@@ -3368,7 +3391,7 @@
       </c>
       <c r="C105" s="35" t="n"/>
       <c r="D105" s="36" t="n"/>
-      <c r="E105" s="37" t="n"/>
+      <c r="E105" s="36" t="n"/>
       <c r="F105" s="36" t="n"/>
       <c r="G105" s="49" t="n"/>
       <c r="H105" s="49" t="n"/>
@@ -3384,9 +3407,9 @@
         </is>
       </c>
       <c r="C106" s="39" t="n"/>
-      <c r="D106" s="40" t="n"/>
-      <c r="E106" s="41" t="n"/>
-      <c r="F106" s="40" t="n"/>
+      <c r="D106" s="36" t="n"/>
+      <c r="E106" s="36" t="n"/>
+      <c r="F106" s="36" t="n"/>
       <c r="G106" s="49" t="n"/>
       <c r="H106" s="49" t="n"/>
       <c r="I106" s="53" t="n"/>
@@ -3402,7 +3425,7 @@
       </c>
       <c r="C107" s="35" t="n"/>
       <c r="D107" s="36" t="n"/>
-      <c r="E107" s="37" t="n"/>
+      <c r="E107" s="36" t="n"/>
       <c r="F107" s="36" t="n"/>
       <c r="G107" s="49" t="n"/>
       <c r="H107" s="49" t="n"/>
@@ -3419,7 +3442,7 @@
       </c>
       <c r="C108" s="35" t="n"/>
       <c r="D108" s="36" t="n"/>
-      <c r="E108" s="37" t="n"/>
+      <c r="E108" s="36" t="n"/>
       <c r="F108" s="36" t="n"/>
       <c r="G108" s="49" t="n"/>
       <c r="H108" s="49" t="n"/>
@@ -3436,7 +3459,7 @@
       </c>
       <c r="C109" s="35" t="n"/>
       <c r="D109" s="36" t="n"/>
-      <c r="E109" s="37" t="n"/>
+      <c r="E109" s="36" t="n"/>
       <c r="F109" s="36" t="n"/>
       <c r="G109" s="49" t="n"/>
       <c r="H109" s="49" t="n"/>
@@ -3453,7 +3476,7 @@
       </c>
       <c r="C110" s="35" t="n"/>
       <c r="D110" s="36" t="n"/>
-      <c r="E110" s="37" t="n"/>
+      <c r="E110" s="36" t="n"/>
       <c r="F110" s="36" t="n"/>
       <c r="G110" s="49" t="n"/>
       <c r="H110" s="49" t="n"/>
@@ -3469,9 +3492,9 @@
         </is>
       </c>
       <c r="C111" s="35" t="n"/>
-      <c r="D111" s="43" t="n"/>
-      <c r="E111" s="42" t="n"/>
-      <c r="F111" s="43" t="n"/>
+      <c r="D111" s="36" t="n"/>
+      <c r="E111" s="36" t="n"/>
+      <c r="F111" s="36" t="n"/>
       <c r="G111" s="49" t="n"/>
       <c r="H111" s="49" t="n"/>
       <c r="I111" s="53" t="n"/>
@@ -3487,7 +3510,7 @@
       </c>
       <c r="C112" s="35" t="n"/>
       <c r="D112" s="36" t="n"/>
-      <c r="E112" s="37" t="n"/>
+      <c r="E112" s="36" t="n"/>
       <c r="F112" s="36" t="n"/>
       <c r="G112" s="49" t="n"/>
       <c r="H112" s="49" t="n"/>
@@ -3504,7 +3527,7 @@
       </c>
       <c r="C113" s="35" t="n"/>
       <c r="D113" s="36" t="n"/>
-      <c r="E113" s="37" t="n"/>
+      <c r="E113" s="36" t="n"/>
       <c r="F113" s="36" t="n"/>
       <c r="G113" s="49" t="n"/>
       <c r="H113" s="49" t="n"/>
@@ -3521,7 +3544,7 @@
       </c>
       <c r="C114" s="35" t="n"/>
       <c r="D114" s="36" t="n"/>
-      <c r="E114" s="37" t="n"/>
+      <c r="E114" s="36" t="n"/>
       <c r="F114" s="36" t="n"/>
       <c r="G114" s="49" t="n"/>
       <c r="H114" s="49" t="n"/>
@@ -3538,7 +3561,7 @@
       </c>
       <c r="C115" s="35" t="n"/>
       <c r="D115" s="36" t="n"/>
-      <c r="E115" s="37" t="n"/>
+      <c r="E115" s="36" t="n"/>
       <c r="F115" s="36" t="n"/>
       <c r="G115" s="49" t="n"/>
       <c r="H115" s="49" t="n"/>
@@ -3555,7 +3578,7 @@
       </c>
       <c r="C116" s="35" t="n"/>
       <c r="D116" s="36" t="n"/>
-      <c r="E116" s="37" t="n"/>
+      <c r="E116" s="36" t="n"/>
       <c r="F116" s="36" t="n"/>
       <c r="G116" s="49" t="n"/>
       <c r="H116" s="49" t="n"/>
@@ -3572,7 +3595,7 @@
       </c>
       <c r="C117" s="35" t="n"/>
       <c r="D117" s="36" t="n"/>
-      <c r="E117" s="37" t="n"/>
+      <c r="E117" s="36" t="n"/>
       <c r="F117" s="36" t="n"/>
       <c r="G117" s="49" t="n"/>
       <c r="H117" s="49" t="n"/>
@@ -3589,7 +3612,7 @@
       </c>
       <c r="C118" s="35" t="n"/>
       <c r="D118" s="36" t="n"/>
-      <c r="E118" s="37" t="n"/>
+      <c r="E118" s="36" t="n"/>
       <c r="F118" s="36" t="n"/>
       <c r="G118" s="49" t="n"/>
       <c r="H118" s="49" t="n"/>
@@ -3606,7 +3629,7 @@
       </c>
       <c r="C119" s="35" t="n"/>
       <c r="D119" s="36" t="n"/>
-      <c r="E119" s="37" t="n"/>
+      <c r="E119" s="36" t="n"/>
       <c r="F119" s="36" t="n"/>
       <c r="G119" s="49" t="n"/>
       <c r="H119" s="49" t="n"/>
@@ -3622,9 +3645,9 @@
         </is>
       </c>
       <c r="C120" s="45" t="n"/>
-      <c r="D120" s="46" t="n"/>
-      <c r="E120" s="47" t="n"/>
-      <c r="F120" s="46" t="n"/>
+      <c r="D120" s="36" t="n"/>
+      <c r="E120" s="36" t="n"/>
+      <c r="F120" s="36" t="n"/>
       <c r="G120" s="49" t="n"/>
       <c r="H120" s="49" t="n"/>
       <c r="I120" s="53" t="n"/>
@@ -3728,12 +3751,12 @@
       </c>
       <c r="C125" s="35" t="n"/>
       <c r="D125" s="36" t="n"/>
-      <c r="E125" s="37" t="n"/>
+      <c r="E125" s="36" t="n"/>
       <c r="F125" s="36" t="n"/>
-      <c r="G125" s="37" t="n"/>
+      <c r="G125" s="36" t="n"/>
       <c r="H125" s="36" t="n"/>
-      <c r="I125" s="40" t="n"/>
-      <c r="J125" s="55" t="n"/>
+      <c r="I125" s="36" t="n"/>
+      <c r="J125" s="36" t="n"/>
       <c r="K125" s="49" t="n"/>
       <c r="L125" s="49" t="n"/>
     </row>
@@ -3744,13 +3767,13 @@
         </is>
       </c>
       <c r="C126" s="39" t="n"/>
-      <c r="D126" s="40" t="n"/>
-      <c r="E126" s="41" t="n"/>
-      <c r="F126" s="40" t="n"/>
-      <c r="G126" s="41" t="n"/>
-      <c r="H126" s="40" t="n"/>
-      <c r="I126" s="40" t="n"/>
-      <c r="J126" s="55" t="n"/>
+      <c r="D126" s="36" t="n"/>
+      <c r="E126" s="36" t="n"/>
+      <c r="F126" s="36" t="n"/>
+      <c r="G126" s="36" t="n"/>
+      <c r="H126" s="36" t="n"/>
+      <c r="I126" s="36" t="n"/>
+      <c r="J126" s="36" t="n"/>
       <c r="K126" s="49" t="n"/>
       <c r="L126" s="49" t="n"/>
     </row>
@@ -3762,12 +3785,12 @@
       </c>
       <c r="C127" s="35" t="n"/>
       <c r="D127" s="36" t="n"/>
-      <c r="E127" s="37" t="n"/>
+      <c r="E127" s="36" t="n"/>
       <c r="F127" s="36" t="n"/>
-      <c r="G127" s="37" t="n"/>
+      <c r="G127" s="36" t="n"/>
       <c r="H127" s="36" t="n"/>
       <c r="I127" s="36" t="n"/>
-      <c r="J127" s="56" t="n"/>
+      <c r="J127" s="36" t="n"/>
       <c r="K127" s="49" t="n"/>
       <c r="L127" s="49" t="n"/>
     </row>
@@ -3779,12 +3802,12 @@
       </c>
       <c r="C128" s="35" t="n"/>
       <c r="D128" s="36" t="n"/>
-      <c r="E128" s="37" t="n"/>
+      <c r="E128" s="36" t="n"/>
       <c r="F128" s="36" t="n"/>
-      <c r="G128" s="37" t="n"/>
+      <c r="G128" s="36" t="n"/>
       <c r="H128" s="36" t="n"/>
       <c r="I128" s="36" t="n"/>
-      <c r="J128" s="56" t="n"/>
+      <c r="J128" s="36" t="n"/>
       <c r="K128" s="49" t="n"/>
       <c r="L128" s="49" t="n"/>
     </row>
@@ -3796,12 +3819,12 @@
       </c>
       <c r="C129" s="35" t="n"/>
       <c r="D129" s="36" t="n"/>
-      <c r="E129" s="37" t="n"/>
+      <c r="E129" s="36" t="n"/>
       <c r="F129" s="36" t="n"/>
-      <c r="G129" s="37" t="n"/>
+      <c r="G129" s="36" t="n"/>
       <c r="H129" s="36" t="n"/>
       <c r="I129" s="36" t="n"/>
-      <c r="J129" s="56" t="n"/>
+      <c r="J129" s="36" t="n"/>
       <c r="K129" s="49" t="n"/>
       <c r="L129" s="49" t="n"/>
     </row>
@@ -3813,12 +3836,12 @@
       </c>
       <c r="C130" s="35" t="n"/>
       <c r="D130" s="36" t="n"/>
-      <c r="E130" s="37" t="n"/>
+      <c r="E130" s="36" t="n"/>
       <c r="F130" s="36" t="n"/>
-      <c r="G130" s="37" t="n"/>
+      <c r="G130" s="36" t="n"/>
       <c r="H130" s="36" t="n"/>
       <c r="I130" s="36" t="n"/>
-      <c r="J130" s="56" t="n"/>
+      <c r="J130" s="36" t="n"/>
       <c r="K130" s="49" t="n"/>
       <c r="L130" s="49" t="n"/>
     </row>
@@ -3830,12 +3853,12 @@
       </c>
       <c r="C131" s="35" t="n"/>
       <c r="D131" s="36" t="n"/>
-      <c r="E131" s="42" t="n"/>
-      <c r="F131" s="43" t="n"/>
-      <c r="G131" s="42" t="n"/>
-      <c r="H131" s="43" t="n"/>
-      <c r="I131" s="43" t="n"/>
-      <c r="J131" s="57" t="n"/>
+      <c r="E131" s="36" t="n"/>
+      <c r="F131" s="36" t="n"/>
+      <c r="G131" s="36" t="n"/>
+      <c r="H131" s="36" t="n"/>
+      <c r="I131" s="36" t="n"/>
+      <c r="J131" s="36" t="n"/>
       <c r="K131" s="49" t="n"/>
       <c r="L131" s="49" t="n"/>
     </row>
@@ -3847,12 +3870,12 @@
       </c>
       <c r="C132" s="35" t="n"/>
       <c r="D132" s="36" t="n"/>
-      <c r="E132" s="37" t="n"/>
+      <c r="E132" s="36" t="n"/>
       <c r="F132" s="36" t="n"/>
-      <c r="G132" s="37" t="n"/>
+      <c r="G132" s="36" t="n"/>
       <c r="H132" s="36" t="n"/>
       <c r="I132" s="36" t="n"/>
-      <c r="J132" s="56" t="n"/>
+      <c r="J132" s="36" t="n"/>
       <c r="K132" s="49" t="n"/>
       <c r="L132" s="49" t="n"/>
     </row>
@@ -3864,12 +3887,12 @@
       </c>
       <c r="C133" s="35" t="n"/>
       <c r="D133" s="36" t="n"/>
-      <c r="E133" s="37" t="n"/>
+      <c r="E133" s="36" t="n"/>
       <c r="F133" s="36" t="n"/>
-      <c r="G133" s="37" t="n"/>
+      <c r="G133" s="36" t="n"/>
       <c r="H133" s="36" t="n"/>
       <c r="I133" s="36" t="n"/>
-      <c r="J133" s="56" t="n"/>
+      <c r="J133" s="36" t="n"/>
       <c r="K133" s="49" t="n"/>
       <c r="L133" s="49" t="n"/>
     </row>
@@ -3881,12 +3904,12 @@
       </c>
       <c r="C134" s="35" t="n"/>
       <c r="D134" s="36" t="n"/>
-      <c r="E134" s="37" t="n"/>
+      <c r="E134" s="36" t="n"/>
       <c r="F134" s="36" t="n"/>
-      <c r="G134" s="37" t="n"/>
+      <c r="G134" s="36" t="n"/>
       <c r="H134" s="36" t="n"/>
       <c r="I134" s="36" t="n"/>
-      <c r="J134" s="56" t="n"/>
+      <c r="J134" s="36" t="n"/>
       <c r="K134" s="49" t="n"/>
       <c r="L134" s="49" t="n"/>
     </row>
@@ -3898,12 +3921,12 @@
       </c>
       <c r="C135" s="35" t="n"/>
       <c r="D135" s="36" t="n"/>
-      <c r="E135" s="37" t="n"/>
+      <c r="E135" s="36" t="n"/>
       <c r="F135" s="36" t="n"/>
-      <c r="G135" s="37" t="n"/>
+      <c r="G135" s="36" t="n"/>
       <c r="H135" s="36" t="n"/>
       <c r="I135" s="36" t="n"/>
-      <c r="J135" s="56" t="n"/>
+      <c r="J135" s="36" t="n"/>
       <c r="K135" s="49" t="n"/>
       <c r="L135" s="49" t="n"/>
     </row>
@@ -3915,12 +3938,12 @@
       </c>
       <c r="C136" s="35" t="n"/>
       <c r="D136" s="36" t="n"/>
-      <c r="E136" s="37" t="n"/>
+      <c r="E136" s="36" t="n"/>
       <c r="F136" s="36" t="n"/>
-      <c r="G136" s="37" t="n"/>
+      <c r="G136" s="36" t="n"/>
       <c r="H136" s="36" t="n"/>
       <c r="I136" s="36" t="n"/>
-      <c r="J136" s="56" t="n"/>
+      <c r="J136" s="36" t="n"/>
       <c r="K136" s="49" t="n"/>
       <c r="L136" s="49" t="n"/>
     </row>
@@ -3932,12 +3955,12 @@
       </c>
       <c r="C137" s="35" t="n"/>
       <c r="D137" s="36" t="n"/>
-      <c r="E137" s="37" t="n"/>
+      <c r="E137" s="36" t="n"/>
       <c r="F137" s="36" t="n"/>
-      <c r="G137" s="37" t="n"/>
+      <c r="G137" s="36" t="n"/>
       <c r="H137" s="36" t="n"/>
       <c r="I137" s="36" t="n"/>
-      <c r="J137" s="56" t="n"/>
+      <c r="J137" s="36" t="n"/>
       <c r="K137" s="49" t="n"/>
       <c r="L137" s="49" t="n"/>
     </row>
@@ -3949,12 +3972,12 @@
       </c>
       <c r="C138" s="35" t="n"/>
       <c r="D138" s="36" t="n"/>
-      <c r="E138" s="37" t="n"/>
+      <c r="E138" s="36" t="n"/>
       <c r="F138" s="36" t="n"/>
-      <c r="G138" s="37" t="n"/>
+      <c r="G138" s="36" t="n"/>
       <c r="H138" s="36" t="n"/>
       <c r="I138" s="36" t="n"/>
-      <c r="J138" s="56" t="n"/>
+      <c r="J138" s="36" t="n"/>
       <c r="K138" s="49" t="n"/>
       <c r="L138" s="49" t="n"/>
     </row>
@@ -3966,12 +3989,12 @@
       </c>
       <c r="C139" s="35" t="n"/>
       <c r="D139" s="36" t="n"/>
-      <c r="E139" s="37" t="n"/>
+      <c r="E139" s="36" t="n"/>
       <c r="F139" s="36" t="n"/>
-      <c r="G139" s="37" t="n"/>
+      <c r="G139" s="36" t="n"/>
       <c r="H139" s="36" t="n"/>
       <c r="I139" s="36" t="n"/>
-      <c r="J139" s="56" t="n"/>
+      <c r="J139" s="36" t="n"/>
       <c r="K139" s="49" t="n"/>
       <c r="L139" s="49" t="n"/>
     </row>
@@ -3982,13 +4005,13 @@
         </is>
       </c>
       <c r="C140" s="45" t="n"/>
-      <c r="D140" s="46" t="n"/>
-      <c r="E140" s="47" t="n"/>
-      <c r="F140" s="46" t="n"/>
-      <c r="G140" s="47" t="n"/>
-      <c r="H140" s="46" t="n"/>
-      <c r="I140" s="46" t="n"/>
-      <c r="J140" s="58" t="n"/>
+      <c r="D140" s="36" t="n"/>
+      <c r="E140" s="36" t="n"/>
+      <c r="F140" s="36" t="n"/>
+      <c r="G140" s="36" t="n"/>
+      <c r="H140" s="36" t="n"/>
+      <c r="I140" s="36" t="n"/>
+      <c r="J140" s="36" t="n"/>
       <c r="K140" s="49" t="n"/>
       <c r="L140" s="49" t="n"/>
     </row>
@@ -4039,7 +4062,7 @@
           <t>Heat &amp; Temperature</t>
         </is>
       </c>
-      <c r="F143" s="24" t="inlineStr">
+      <c r="F143" s="31" t="inlineStr">
         <is>
           <t>Waves, Sound &amp; Light</t>
         </is>
@@ -4056,7 +4079,7 @@
       <c r="C144" s="65" t="n"/>
       <c r="D144" s="66" t="n"/>
       <c r="E144" s="66" t="n"/>
-      <c r="F144" s="65" t="n"/>
+      <c r="F144" s="66" t="n"/>
       <c r="I144" s="53" t="n"/>
       <c r="J144" s="53" t="n"/>
       <c r="K144" s="60" t="n"/>
@@ -4070,7 +4093,7 @@
       </c>
       <c r="C145" s="35" t="n"/>
       <c r="D145" s="36" t="n"/>
-      <c r="E145" s="37" t="n"/>
+      <c r="E145" s="36" t="n"/>
       <c r="F145" s="36" t="n"/>
       <c r="G145" s="49" t="n"/>
       <c r="H145" s="49" t="n"/>
@@ -4086,9 +4109,9 @@
         </is>
       </c>
       <c r="C146" s="39" t="n"/>
-      <c r="D146" s="40" t="n"/>
-      <c r="E146" s="41" t="n"/>
-      <c r="F146" s="40" t="n"/>
+      <c r="D146" s="36" t="n"/>
+      <c r="E146" s="36" t="n"/>
+      <c r="F146" s="36" t="n"/>
       <c r="G146" s="49" t="n"/>
       <c r="H146" s="49" t="n"/>
       <c r="I146" s="53" t="n"/>
@@ -4104,7 +4127,7 @@
       </c>
       <c r="C147" s="35" t="n"/>
       <c r="D147" s="36" t="n"/>
-      <c r="E147" s="37" t="n"/>
+      <c r="E147" s="36" t="n"/>
       <c r="F147" s="36" t="n"/>
       <c r="G147" s="49" t="n"/>
       <c r="H147" s="49" t="n"/>
@@ -4121,7 +4144,7 @@
       </c>
       <c r="C148" s="35" t="n"/>
       <c r="D148" s="36" t="n"/>
-      <c r="E148" s="37" t="n"/>
+      <c r="E148" s="36" t="n"/>
       <c r="F148" s="36" t="n"/>
       <c r="G148" s="49" t="n"/>
       <c r="H148" s="49" t="n"/>
@@ -4138,7 +4161,7 @@
       </c>
       <c r="C149" s="35" t="n"/>
       <c r="D149" s="36" t="n"/>
-      <c r="E149" s="37" t="n"/>
+      <c r="E149" s="36" t="n"/>
       <c r="F149" s="36" t="n"/>
       <c r="G149" s="49" t="n"/>
       <c r="H149" s="49" t="n"/>
@@ -4155,7 +4178,7 @@
       </c>
       <c r="C150" s="35" t="n"/>
       <c r="D150" s="36" t="n"/>
-      <c r="E150" s="37" t="n"/>
+      <c r="E150" s="36" t="n"/>
       <c r="F150" s="36" t="n"/>
       <c r="G150" s="49" t="n"/>
       <c r="H150" s="49" t="n"/>
@@ -4171,9 +4194,9 @@
         </is>
       </c>
       <c r="C151" s="35" t="n"/>
-      <c r="D151" s="43" t="n"/>
-      <c r="E151" s="42" t="n"/>
-      <c r="F151" s="43" t="n"/>
+      <c r="D151" s="36" t="n"/>
+      <c r="E151" s="36" t="n"/>
+      <c r="F151" s="36" t="n"/>
       <c r="G151" s="49" t="n"/>
       <c r="H151" s="49" t="n"/>
       <c r="I151" s="53" t="n"/>
@@ -4189,7 +4212,7 @@
       </c>
       <c r="C152" s="35" t="n"/>
       <c r="D152" s="36" t="n"/>
-      <c r="E152" s="37" t="n"/>
+      <c r="E152" s="36" t="n"/>
       <c r="F152" s="36" t="n"/>
       <c r="G152" s="49" t="n"/>
       <c r="H152" s="49" t="n"/>
@@ -4206,7 +4229,7 @@
       </c>
       <c r="C153" s="35" t="n"/>
       <c r="D153" s="36" t="n"/>
-      <c r="E153" s="37" t="n"/>
+      <c r="E153" s="36" t="n"/>
       <c r="F153" s="36" t="n"/>
       <c r="G153" s="49" t="n"/>
       <c r="H153" s="49" t="n"/>
@@ -4223,7 +4246,7 @@
       </c>
       <c r="C154" s="35" t="n"/>
       <c r="D154" s="36" t="n"/>
-      <c r="E154" s="37" t="n"/>
+      <c r="E154" s="36" t="n"/>
       <c r="F154" s="36" t="n"/>
       <c r="G154" s="49" t="n"/>
       <c r="H154" s="49" t="n"/>
@@ -4240,7 +4263,7 @@
       </c>
       <c r="C155" s="35" t="n"/>
       <c r="D155" s="36" t="n"/>
-      <c r="E155" s="37" t="n"/>
+      <c r="E155" s="36" t="n"/>
       <c r="F155" s="36" t="n"/>
       <c r="G155" s="49" t="n"/>
       <c r="H155" s="49" t="n"/>
@@ -4257,7 +4280,7 @@
       </c>
       <c r="C156" s="35" t="n"/>
       <c r="D156" s="36" t="n"/>
-      <c r="E156" s="37" t="n"/>
+      <c r="E156" s="36" t="n"/>
       <c r="F156" s="36" t="n"/>
       <c r="G156" s="49" t="n"/>
       <c r="H156" s="49" t="n"/>
@@ -4274,7 +4297,7 @@
       </c>
       <c r="C157" s="35" t="n"/>
       <c r="D157" s="36" t="n"/>
-      <c r="E157" s="37" t="n"/>
+      <c r="E157" s="36" t="n"/>
       <c r="F157" s="36" t="n"/>
       <c r="G157" s="49" t="n"/>
       <c r="H157" s="49" t="n"/>
@@ -4291,7 +4314,7 @@
       </c>
       <c r="C158" s="35" t="n"/>
       <c r="D158" s="36" t="n"/>
-      <c r="E158" s="37" t="n"/>
+      <c r="E158" s="36" t="n"/>
       <c r="F158" s="36" t="n"/>
       <c r="G158" s="49" t="n"/>
       <c r="H158" s="49" t="n"/>
@@ -4308,7 +4331,7 @@
       </c>
       <c r="C159" s="35" t="n"/>
       <c r="D159" s="36" t="n"/>
-      <c r="E159" s="37" t="n"/>
+      <c r="E159" s="36" t="n"/>
       <c r="F159" s="36" t="n"/>
       <c r="G159" s="49" t="n"/>
       <c r="H159" s="49" t="n"/>
@@ -4324,9 +4347,9 @@
         </is>
       </c>
       <c r="C160" s="45" t="n"/>
-      <c r="D160" s="46" t="n"/>
-      <c r="E160" s="47" t="n"/>
-      <c r="F160" s="46" t="n"/>
+      <c r="D160" s="36" t="n"/>
+      <c r="E160" s="36" t="n"/>
+      <c r="F160" s="36" t="n"/>
       <c r="G160" s="49" t="n"/>
       <c r="H160" s="49" t="n"/>
       <c r="I160" s="60" t="n"/>
@@ -4335,20 +4358,19 @@
       <c r="L160" s="60" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="72">
+  <mergeCells count="64">
     <mergeCell ref="E123:E124"/>
     <mergeCell ref="E43:E44"/>
     <mergeCell ref="C103:C104"/>
     <mergeCell ref="G43:G44"/>
-    <mergeCell ref="G23:G24"/>
     <mergeCell ref="B43:B44"/>
     <mergeCell ref="B62:F62"/>
+    <mergeCell ref="H43:H44"/>
+    <mergeCell ref="F83:F84"/>
     <mergeCell ref="B42:J42"/>
-    <mergeCell ref="F83:F84"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="H83:H84"/>
     <mergeCell ref="F103:F104"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="H43:H44"/>
-    <mergeCell ref="H83:H84"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="E23:E24"/>
     <mergeCell ref="C63:C64"/>
@@ -4364,13 +4386,11 @@
     <mergeCell ref="J83:J84"/>
     <mergeCell ref="E103:E104"/>
     <mergeCell ref="C123:C124"/>
-    <mergeCell ref="G103:G104"/>
     <mergeCell ref="G83:G84"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="I83:I84"/>
     <mergeCell ref="I3:I4"/>
     <mergeCell ref="D3:D4"/>
-    <mergeCell ref="H63:H64"/>
     <mergeCell ref="B143:B144"/>
     <mergeCell ref="F23:F24"/>
     <mergeCell ref="D143:D144"/>
@@ -4378,16 +4398,14 @@
     <mergeCell ref="G123:G124"/>
     <mergeCell ref="C43:C44"/>
     <mergeCell ref="C23:C24"/>
-    <mergeCell ref="G63:G64"/>
+    <mergeCell ref="I123:I124"/>
     <mergeCell ref="B103:B104"/>
     <mergeCell ref="B83:B84"/>
     <mergeCell ref="D43:D44"/>
     <mergeCell ref="D103:D104"/>
     <mergeCell ref="D83:D84"/>
     <mergeCell ref="F43:F44"/>
-    <mergeCell ref="I123:I124"/>
     <mergeCell ref="H3:H4"/>
-    <mergeCell ref="G143:G144"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="B123:B124"/>
     <mergeCell ref="D123:D124"/>
@@ -4402,11 +4420,8 @@
     <mergeCell ref="C83:C84"/>
     <mergeCell ref="D23:D24"/>
     <mergeCell ref="E83:E84"/>
-    <mergeCell ref="H23:H24"/>
     <mergeCell ref="F63:F64"/>
     <mergeCell ref="F143:F144"/>
-    <mergeCell ref="H103:H104"/>
-    <mergeCell ref="H143:H144"/>
     <mergeCell ref="B2:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4419,11 +4434,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K98"/>
+  <dimension ref="B1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="9" customWidth="1" style="25" min="1" max="1"/>
     <col width="16.6238532110092" customWidth="1" style="3" min="2" max="25"/>
+    <col width="13" customWidth="1" style="25" min="3" max="3"/>
+    <col width="13" customWidth="1" style="25" min="4" max="4"/>
+    <col width="13" customWidth="1" style="25" min="5" max="5"/>
+    <col width="13" customWidth="1" style="25" min="6" max="6"/>
+    <col width="13" customWidth="1" style="25" min="7" max="7"/>
+    <col width="13" customWidth="1" style="25" min="8" max="8"/>
+    <col width="13" customWidth="1" style="25" min="9" max="9"/>
     <col width="9" customWidth="1" style="25" min="26" max="16384"/>
   </cols>
   <sheetData>
@@ -4518,13 +4540,13 @@
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C6" s="40" t="n"/>
-      <c r="D6" s="40" t="n"/>
-      <c r="E6" s="40" t="n"/>
-      <c r="F6" s="40" t="n"/>
-      <c r="G6" s="40" t="n"/>
-      <c r="H6" s="40" t="n"/>
-      <c r="I6" s="40" t="n"/>
+      <c r="C6" s="36" t="n"/>
+      <c r="D6" s="36" t="n"/>
+      <c r="E6" s="36" t="n"/>
+      <c r="F6" s="36" t="n"/>
+      <c r="G6" s="36" t="n"/>
+      <c r="H6" s="36" t="n"/>
+      <c r="I6" s="36" t="n"/>
       <c r="J6" s="51" t="n"/>
       <c r="K6" s="51" t="n"/>
     </row>
@@ -4599,12 +4621,12 @@
         </is>
       </c>
       <c r="C11" s="36" t="n"/>
-      <c r="D11" s="43" t="n"/>
-      <c r="E11" s="43" t="n"/>
-      <c r="F11" s="43" t="n"/>
-      <c r="G11" s="43" t="n"/>
-      <c r="H11" s="43" t="n"/>
-      <c r="I11" s="43" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="36" t="n"/>
+      <c r="F11" s="36" t="n"/>
+      <c r="G11" s="36" t="n"/>
+      <c r="H11" s="36" t="n"/>
+      <c r="I11" s="36" t="n"/>
       <c r="J11" s="51" t="n"/>
       <c r="K11" s="51" t="n"/>
     </row>
@@ -4614,13 +4636,13 @@
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C12" s="46" t="n"/>
-      <c r="D12" s="46" t="n"/>
-      <c r="E12" s="46" t="n"/>
-      <c r="F12" s="46" t="n"/>
-      <c r="G12" s="46" t="n"/>
-      <c r="H12" s="46" t="n"/>
-      <c r="I12" s="46" t="n"/>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="36" t="n"/>
+      <c r="F12" s="36" t="n"/>
+      <c r="G12" s="36" t="n"/>
+      <c r="H12" s="36" t="n"/>
+      <c r="I12" s="36" t="n"/>
       <c r="J12" s="51" t="n"/>
       <c r="K12" s="51" t="n"/>
     </row>
@@ -4655,7 +4677,7 @@
           <t>Heat &amp; Temperature</t>
         </is>
       </c>
-      <c r="E15" s="67" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>Waves, Sound &amp; Light</t>
         </is>
@@ -4670,7 +4692,7 @@
       <c r="B16" s="64" t="n"/>
       <c r="C16" s="66" t="n"/>
       <c r="D16" s="66" t="n"/>
-      <c r="E16" s="65" t="n"/>
+      <c r="E16" s="66" t="n"/>
       <c r="F16" s="51" t="n"/>
       <c r="G16" s="51" t="n"/>
       <c r="H16" s="51" t="n"/>
@@ -4698,9 +4720,9 @@
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C18" s="40" t="n"/>
-      <c r="D18" s="40" t="n"/>
-      <c r="E18" s="40" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
       <c r="F18" s="51" t="n"/>
       <c r="G18" s="51" t="n"/>
       <c r="H18" s="51" t="n"/>
@@ -4773,9 +4795,9 @@
           <t>Nov_2021</t>
         </is>
       </c>
-      <c r="C23" s="43" t="n"/>
-      <c r="D23" s="43" t="n"/>
-      <c r="E23" s="43" t="n"/>
+      <c r="C23" s="36" t="n"/>
+      <c r="D23" s="36" t="n"/>
+      <c r="E23" s="36" t="n"/>
       <c r="F23" s="51" t="n"/>
       <c r="G23" s="51" t="n"/>
       <c r="H23" s="51" t="n"/>
@@ -4788,9 +4810,9 @@
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C24" s="46" t="n"/>
-      <c r="D24" s="46" t="n"/>
-      <c r="E24" s="46" t="n"/>
+      <c r="C24" s="36" t="n"/>
+      <c r="D24" s="36" t="n"/>
+      <c r="E24" s="36" t="n"/>
       <c r="F24" s="51" t="n"/>
       <c r="G24" s="51" t="n"/>
       <c r="H24" s="51" t="n"/>
@@ -4891,13 +4913,13 @@
           <t>Sept_2016</t>
         </is>
       </c>
-      <c r="C30" s="40" t="n"/>
-      <c r="D30" s="40" t="n"/>
-      <c r="E30" s="40" t="n"/>
-      <c r="F30" s="40" t="n"/>
-      <c r="G30" s="40" t="n"/>
-      <c r="H30" s="40" t="n"/>
-      <c r="I30" s="40" t="n"/>
+      <c r="C30" s="36" t="n"/>
+      <c r="D30" s="36" t="n"/>
+      <c r="E30" s="36" t="n"/>
+      <c r="F30" s="36" t="n"/>
+      <c r="G30" s="36" t="n"/>
+      <c r="H30" s="36" t="n"/>
+      <c r="I30" s="36" t="n"/>
       <c r="J30" s="51" t="n"/>
       <c r="K30" s="51" t="n"/>
     </row>
@@ -4972,12 +4994,12 @@
         </is>
       </c>
       <c r="C35" s="36" t="n"/>
-      <c r="D35" s="43" t="n"/>
-      <c r="E35" s="43" t="n"/>
-      <c r="F35" s="43" t="n"/>
-      <c r="G35" s="43" t="n"/>
-      <c r="H35" s="43" t="n"/>
-      <c r="I35" s="43" t="n"/>
+      <c r="D35" s="36" t="n"/>
+      <c r="E35" s="36" t="n"/>
+      <c r="F35" s="36" t="n"/>
+      <c r="G35" s="36" t="n"/>
+      <c r="H35" s="36" t="n"/>
+      <c r="I35" s="36" t="n"/>
       <c r="J35" s="51" t="n"/>
       <c r="K35" s="51" t="n"/>
     </row>
@@ -4987,13 +5009,13 @@
           <t>Sept_2022</t>
         </is>
       </c>
-      <c r="C36" s="46" t="n"/>
-      <c r="D36" s="46" t="n"/>
-      <c r="E36" s="46" t="n"/>
-      <c r="F36" s="46" t="n"/>
-      <c r="G36" s="46" t="n"/>
-      <c r="H36" s="46" t="n"/>
-      <c r="I36" s="46" t="n"/>
+      <c r="C36" s="36" t="n"/>
+      <c r="D36" s="36" t="n"/>
+      <c r="E36" s="36" t="n"/>
+      <c r="F36" s="36" t="n"/>
+      <c r="G36" s="36" t="n"/>
+      <c r="H36" s="36" t="n"/>
+      <c r="I36" s="36" t="n"/>
       <c r="J36" s="51" t="n"/>
       <c r="K36" s="51" t="n"/>
     </row>
@@ -5027,7 +5049,7 @@
           <t>Heat &amp; Temperature</t>
         </is>
       </c>
-      <c r="E39" s="67" t="inlineStr">
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>Waves, Sound &amp; Light</t>
         </is>
@@ -5041,7 +5063,7 @@
       <c r="B40" s="64" t="n"/>
       <c r="C40" s="66" t="n"/>
       <c r="D40" s="66" t="n"/>
-      <c r="E40" s="65" t="n"/>
+      <c r="E40" s="66" t="n"/>
       <c r="F40" s="54" t="n"/>
       <c r="G40" s="54" t="n"/>
       <c r="J40" s="51" t="n"/>
@@ -5067,9 +5089,9 @@
           <t>Sept_2016</t>
         </is>
       </c>
-      <c r="C42" s="40" t="n"/>
-      <c r="D42" s="40" t="n"/>
-      <c r="E42" s="40" t="n"/>
+      <c r="C42" s="36" t="n"/>
+      <c r="D42" s="36" t="n"/>
+      <c r="E42" s="36" t="n"/>
       <c r="F42" s="49" t="n"/>
       <c r="G42" s="49" t="n"/>
       <c r="J42" s="51" t="n"/>
@@ -5137,9 +5159,9 @@
           <t>Sept_2021</t>
         </is>
       </c>
-      <c r="C47" s="43" t="n"/>
-      <c r="D47" s="43" t="n"/>
-      <c r="E47" s="43" t="n"/>
+      <c r="C47" s="36" t="n"/>
+      <c r="D47" s="36" t="n"/>
+      <c r="E47" s="36" t="n"/>
       <c r="F47" s="49" t="n"/>
       <c r="G47" s="49" t="n"/>
       <c r="J47" s="51" t="n"/>
@@ -5151,9 +5173,9 @@
           <t>Sept_2022</t>
         </is>
       </c>
-      <c r="C48" s="46" t="n"/>
-      <c r="D48" s="46" t="n"/>
-      <c r="E48" s="46" t="n"/>
+      <c r="C48" s="36" t="n"/>
+      <c r="D48" s="36" t="n"/>
+      <c r="E48" s="36" t="n"/>
       <c r="F48" s="49" t="n"/>
       <c r="G48" s="49" t="n"/>
       <c r="J48" s="51" t="n"/>
@@ -5253,13 +5275,13 @@
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C54" s="40" t="n"/>
-      <c r="D54" s="40" t="n"/>
-      <c r="E54" s="40" t="n"/>
-      <c r="F54" s="40" t="n"/>
-      <c r="G54" s="40" t="n"/>
-      <c r="H54" s="40" t="n"/>
-      <c r="I54" s="40" t="n"/>
+      <c r="C54" s="36" t="n"/>
+      <c r="D54" s="36" t="n"/>
+      <c r="E54" s="36" t="n"/>
+      <c r="F54" s="36" t="n"/>
+      <c r="G54" s="36" t="n"/>
+      <c r="H54" s="36" t="n"/>
+      <c r="I54" s="36" t="n"/>
       <c r="J54" s="51" t="n"/>
       <c r="K54" s="51" t="n"/>
     </row>
@@ -5312,18 +5334,18 @@
       <c r="K57" s="51" t="n"/>
     </row>
     <row r="58">
-      <c r="B58" s="15" t="inlineStr">
+      <c r="B58" s="68" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C58" s="36" t="n"/>
-      <c r="D58" s="36" t="n"/>
-      <c r="E58" s="36" t="n"/>
-      <c r="F58" s="36" t="n"/>
-      <c r="G58" s="36" t="n"/>
-      <c r="H58" s="36" t="n"/>
-      <c r="I58" s="36" t="n"/>
+      <c r="C58" s="69" t="n"/>
+      <c r="D58" s="69" t="n"/>
+      <c r="E58" s="69" t="n"/>
+      <c r="F58" s="69" t="n"/>
+      <c r="G58" s="69" t="n"/>
+      <c r="H58" s="69" t="n"/>
+      <c r="I58" s="69" t="n"/>
       <c r="J58" s="51" t="n"/>
       <c r="K58" s="51" t="n"/>
     </row>
@@ -5334,12 +5356,12 @@
         </is>
       </c>
       <c r="C59" s="36" t="n"/>
-      <c r="D59" s="43" t="n"/>
-      <c r="E59" s="43" t="n"/>
-      <c r="F59" s="43" t="n"/>
-      <c r="G59" s="43" t="n"/>
-      <c r="H59" s="43" t="n"/>
-      <c r="I59" s="43" t="n"/>
+      <c r="D59" s="36" t="n"/>
+      <c r="E59" s="36" t="n"/>
+      <c r="F59" s="36" t="n"/>
+      <c r="G59" s="36" t="n"/>
+      <c r="H59" s="36" t="n"/>
+      <c r="I59" s="36" t="n"/>
       <c r="J59" s="51" t="n"/>
       <c r="K59" s="51" t="n"/>
     </row>
@@ -5349,13 +5371,13 @@
           <t>May/Jun_2022</t>
         </is>
       </c>
-      <c r="C60" s="46" t="n"/>
-      <c r="D60" s="46" t="n"/>
-      <c r="E60" s="46" t="n"/>
-      <c r="F60" s="46" t="n"/>
-      <c r="G60" s="46" t="n"/>
-      <c r="H60" s="46" t="n"/>
-      <c r="I60" s="46" t="n"/>
+      <c r="C60" s="36" t="n"/>
+      <c r="D60" s="36" t="n"/>
+      <c r="E60" s="36" t="n"/>
+      <c r="F60" s="36" t="n"/>
+      <c r="G60" s="36" t="n"/>
+      <c r="H60" s="36" t="n"/>
+      <c r="I60" s="36" t="n"/>
       <c r="J60" s="51" t="n"/>
       <c r="K60" s="51" t="n"/>
     </row>
@@ -5389,7 +5411,7 @@
           <t>Heat &amp; Temperature</t>
         </is>
       </c>
-      <c r="E63" s="67" t="inlineStr">
+      <c r="E63" s="12" t="inlineStr">
         <is>
           <t>Waves, Sound &amp; Light</t>
         </is>
@@ -5403,7 +5425,7 @@
       <c r="B64" s="64" t="n"/>
       <c r="C64" s="66" t="n"/>
       <c r="D64" s="66" t="n"/>
-      <c r="E64" s="65" t="n"/>
+      <c r="E64" s="66" t="n"/>
       <c r="F64" s="54" t="n"/>
       <c r="G64" s="54" t="n"/>
       <c r="J64" s="51" t="n"/>
@@ -5429,9 +5451,9 @@
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C66" s="40" t="n"/>
-      <c r="D66" s="40" t="n"/>
-      <c r="E66" s="40" t="n"/>
+      <c r="C66" s="36" t="n"/>
+      <c r="D66" s="36" t="n"/>
+      <c r="E66" s="36" t="n"/>
       <c r="F66" s="49" t="n"/>
       <c r="G66" s="49" t="n"/>
       <c r="J66" s="51" t="n"/>
@@ -5480,14 +5502,14 @@
       <c r="K69" s="51" t="n"/>
     </row>
     <row r="70">
-      <c r="B70" s="15" t="inlineStr">
+      <c r="B70" s="68" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C70" s="36" t="n"/>
-      <c r="D70" s="36" t="n"/>
-      <c r="E70" s="36" t="n"/>
+      <c r="C70" s="69" t="n"/>
+      <c r="D70" s="69" t="n"/>
+      <c r="E70" s="69" t="n"/>
       <c r="F70" s="49" t="n"/>
       <c r="G70" s="49" t="n"/>
       <c r="J70" s="51" t="n"/>
@@ -5499,9 +5521,9 @@
           <t>May/Jun_2021</t>
         </is>
       </c>
-      <c r="C71" s="43" t="n"/>
-      <c r="D71" s="43" t="n"/>
-      <c r="E71" s="43" t="n"/>
+      <c r="C71" s="36" t="n"/>
+      <c r="D71" s="36" t="n"/>
+      <c r="E71" s="36" t="n"/>
       <c r="F71" s="49" t="n"/>
       <c r="G71" s="49" t="n"/>
       <c r="J71" s="51" t="n"/>
@@ -5513,9 +5535,9 @@
           <t>May/Jun_2022</t>
         </is>
       </c>
-      <c r="C72" s="46" t="n"/>
-      <c r="D72" s="46" t="n"/>
-      <c r="E72" s="46" t="n"/>
+      <c r="C72" s="36" t="n"/>
+      <c r="D72" s="36" t="n"/>
+      <c r="E72" s="36" t="n"/>
       <c r="F72" s="49" t="n"/>
       <c r="G72" s="49" t="n"/>
       <c r="J72" s="51" t="n"/>
@@ -5615,13 +5637,13 @@
           <t>Feb/Mar_2016</t>
         </is>
       </c>
-      <c r="C78" s="40" t="n"/>
-      <c r="D78" s="40" t="n"/>
-      <c r="E78" s="40" t="n"/>
-      <c r="F78" s="40" t="n"/>
-      <c r="G78" s="40" t="n"/>
-      <c r="H78" s="40" t="n"/>
-      <c r="I78" s="40" t="n"/>
+      <c r="C78" s="36" t="n"/>
+      <c r="D78" s="36" t="n"/>
+      <c r="E78" s="36" t="n"/>
+      <c r="F78" s="36" t="n"/>
+      <c r="G78" s="36" t="n"/>
+      <c r="H78" s="36" t="n"/>
+      <c r="I78" s="36" t="n"/>
       <c r="J78" s="51" t="n"/>
       <c r="K78" s="51" t="n"/>
     </row>
@@ -5696,12 +5718,12 @@
         </is>
       </c>
       <c r="C83" s="36" t="n"/>
-      <c r="D83" s="43" t="n"/>
-      <c r="E83" s="43" t="n"/>
-      <c r="F83" s="43" t="n"/>
-      <c r="G83" s="43" t="n"/>
-      <c r="H83" s="43" t="n"/>
-      <c r="I83" s="43" t="n"/>
+      <c r="D83" s="36" t="n"/>
+      <c r="E83" s="36" t="n"/>
+      <c r="F83" s="36" t="n"/>
+      <c r="G83" s="36" t="n"/>
+      <c r="H83" s="36" t="n"/>
+      <c r="I83" s="36" t="n"/>
       <c r="J83" s="51" t="n"/>
       <c r="K83" s="51" t="n"/>
     </row>
@@ -5711,13 +5733,13 @@
           <t>Feb/Mar_2022</t>
         </is>
       </c>
-      <c r="C84" s="46" t="n"/>
-      <c r="D84" s="46" t="n"/>
-      <c r="E84" s="46" t="n"/>
-      <c r="F84" s="46" t="n"/>
-      <c r="G84" s="46" t="n"/>
-      <c r="H84" s="46" t="n"/>
-      <c r="I84" s="46" t="n"/>
+      <c r="C84" s="36" t="n"/>
+      <c r="D84" s="36" t="n"/>
+      <c r="E84" s="36" t="n"/>
+      <c r="F84" s="36" t="n"/>
+      <c r="G84" s="36" t="n"/>
+      <c r="H84" s="36" t="n"/>
+      <c r="I84" s="36" t="n"/>
       <c r="J84" s="51" t="n"/>
       <c r="K84" s="51" t="n"/>
     </row>
@@ -5751,7 +5773,7 @@
           <t>Heat &amp; Temperature</t>
         </is>
       </c>
-      <c r="E87" s="67" t="inlineStr">
+      <c r="E87" s="12" t="inlineStr">
         <is>
           <t>Waves, Sound &amp; Light</t>
         </is>
@@ -5765,7 +5787,7 @@
       <c r="B88" s="64" t="n"/>
       <c r="C88" s="66" t="n"/>
       <c r="D88" s="66" t="n"/>
-      <c r="E88" s="65" t="n"/>
+      <c r="E88" s="66" t="n"/>
       <c r="F88" s="54" t="n"/>
       <c r="G88" s="54" t="n"/>
       <c r="J88" s="51" t="n"/>
@@ -5791,9 +5813,9 @@
           <t>Feb/Mar_2016</t>
         </is>
       </c>
-      <c r="C90" s="40" t="n"/>
-      <c r="D90" s="40" t="n"/>
-      <c r="E90" s="40" t="n"/>
+      <c r="C90" s="36" t="n"/>
+      <c r="D90" s="36" t="n"/>
+      <c r="E90" s="36" t="n"/>
       <c r="F90" s="49" t="n"/>
       <c r="G90" s="49" t="n"/>
       <c r="J90" s="51" t="n"/>
@@ -5861,9 +5883,9 @@
           <t>Feb/Mar_2021</t>
         </is>
       </c>
-      <c r="C95" s="43" t="n"/>
-      <c r="D95" s="43" t="n"/>
-      <c r="E95" s="43" t="n"/>
+      <c r="C95" s="36" t="n"/>
+      <c r="D95" s="36" t="n"/>
+      <c r="E95" s="36" t="n"/>
       <c r="F95" s="49" t="n"/>
       <c r="G95" s="49" t="n"/>
       <c r="J95" s="51" t="n"/>
@@ -5875,9 +5897,9 @@
           <t>Feb/Mar_2022</t>
         </is>
       </c>
-      <c r="C96" s="46" t="n"/>
-      <c r="D96" s="46" t="n"/>
-      <c r="E96" s="46" t="n"/>
+      <c r="C96" s="36" t="n"/>
+      <c r="D96" s="36" t="n"/>
+      <c r="E96" s="36" t="n"/>
       <c r="F96" s="49" t="n"/>
       <c r="G96" s="49" t="n"/>
       <c r="J96" s="51" t="n"/>
@@ -5962,11 +5984,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K98"/>
+  <dimension ref="B1:K97"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="9" customWidth="1" style="25" min="1" max="1"/>
     <col width="16.6238532110092" customWidth="1" style="3" min="2" max="24"/>
+    <col width="13" customWidth="1" style="25" min="3" max="3"/>
+    <col width="13" customWidth="1" style="25" min="4" max="4"/>
+    <col width="13" customWidth="1" style="25" min="5" max="5"/>
+    <col width="13" customWidth="1" style="25" min="6" max="6"/>
+    <col width="13" customWidth="1" style="25" min="7" max="7"/>
+    <col width="13" customWidth="1" style="25" min="8" max="8"/>
+    <col width="13" customWidth="1" style="25" min="9" max="9"/>
     <col width="9" customWidth="1" style="25" min="25" max="16384"/>
   </cols>
   <sheetData>
@@ -6061,13 +6090,13 @@
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C6" s="40" t="n"/>
-      <c r="D6" s="40" t="n"/>
-      <c r="E6" s="40" t="n"/>
-      <c r="F6" s="40" t="n"/>
-      <c r="G6" s="40" t="n"/>
-      <c r="H6" s="40" t="n"/>
-      <c r="I6" s="40" t="n"/>
+      <c r="C6" s="36" t="n"/>
+      <c r="D6" s="36" t="n"/>
+      <c r="E6" s="36" t="n"/>
+      <c r="F6" s="36" t="n"/>
+      <c r="G6" s="36" t="n"/>
+      <c r="H6" s="36" t="n"/>
+      <c r="I6" s="36" t="n"/>
       <c r="J6" s="51" t="n"/>
       <c r="K6" s="51" t="n"/>
     </row>
@@ -6142,12 +6171,12 @@
         </is>
       </c>
       <c r="C11" s="36" t="n"/>
-      <c r="D11" s="43" t="n"/>
-      <c r="E11" s="43" t="n"/>
-      <c r="F11" s="43" t="n"/>
-      <c r="G11" s="43" t="n"/>
-      <c r="H11" s="43" t="n"/>
-      <c r="I11" s="43" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="36" t="n"/>
+      <c r="F11" s="36" t="n"/>
+      <c r="G11" s="36" t="n"/>
+      <c r="H11" s="36" t="n"/>
+      <c r="I11" s="36" t="n"/>
       <c r="J11" s="51" t="n"/>
       <c r="K11" s="51" t="n"/>
     </row>
@@ -6157,13 +6186,13 @@
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C12" s="46" t="n"/>
-      <c r="D12" s="46" t="n"/>
-      <c r="E12" s="46" t="n"/>
-      <c r="F12" s="46" t="n"/>
-      <c r="G12" s="46" t="n"/>
-      <c r="H12" s="46" t="n"/>
-      <c r="I12" s="46" t="n"/>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="36" t="n"/>
+      <c r="F12" s="36" t="n"/>
+      <c r="G12" s="36" t="n"/>
+      <c r="H12" s="36" t="n"/>
+      <c r="I12" s="36" t="n"/>
       <c r="J12" s="51" t="n"/>
       <c r="K12" s="51" t="n"/>
     </row>
@@ -6198,7 +6227,7 @@
           <t>Heat &amp; Temperature</t>
         </is>
       </c>
-      <c r="E15" s="67" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>Waves, Sound &amp; Light</t>
         </is>
@@ -6213,7 +6242,7 @@
       <c r="B16" s="64" t="n"/>
       <c r="C16" s="66" t="n"/>
       <c r="D16" s="66" t="n"/>
-      <c r="E16" s="65" t="n"/>
+      <c r="E16" s="66" t="n"/>
       <c r="F16" s="51" t="n"/>
       <c r="G16" s="51" t="n"/>
       <c r="H16" s="51" t="n"/>
@@ -6241,9 +6270,9 @@
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C18" s="40" t="n"/>
-      <c r="D18" s="40" t="n"/>
-      <c r="E18" s="40" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
       <c r="F18" s="51" t="n"/>
       <c r="G18" s="51" t="n"/>
       <c r="H18" s="51" t="n"/>
@@ -6316,9 +6345,9 @@
           <t>Nov_2021</t>
         </is>
       </c>
-      <c r="C23" s="43" t="n"/>
-      <c r="D23" s="43" t="n"/>
-      <c r="E23" s="43" t="n"/>
+      <c r="C23" s="36" t="n"/>
+      <c r="D23" s="36" t="n"/>
+      <c r="E23" s="36" t="n"/>
       <c r="F23" s="51" t="n"/>
       <c r="G23" s="51" t="n"/>
       <c r="H23" s="51" t="n"/>
@@ -6331,9 +6360,9 @@
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C24" s="46" t="n"/>
-      <c r="D24" s="46" t="n"/>
-      <c r="E24" s="46" t="n"/>
+      <c r="C24" s="36" t="n"/>
+      <c r="D24" s="36" t="n"/>
+      <c r="E24" s="36" t="n"/>
       <c r="F24" s="51" t="n"/>
       <c r="G24" s="51" t="n"/>
       <c r="H24" s="51" t="n"/>
@@ -6434,13 +6463,13 @@
           <t>Sept_2016</t>
         </is>
       </c>
-      <c r="C30" s="40" t="n"/>
-      <c r="D30" s="40" t="n"/>
-      <c r="E30" s="40" t="n"/>
-      <c r="F30" s="40" t="n"/>
-      <c r="G30" s="40" t="n"/>
-      <c r="H30" s="40" t="n"/>
-      <c r="I30" s="40" t="n"/>
+      <c r="C30" s="36" t="n"/>
+      <c r="D30" s="36" t="n"/>
+      <c r="E30" s="36" t="n"/>
+      <c r="F30" s="36" t="n"/>
+      <c r="G30" s="36" t="n"/>
+      <c r="H30" s="36" t="n"/>
+      <c r="I30" s="36" t="n"/>
       <c r="J30" s="51" t="n"/>
       <c r="K30" s="51" t="n"/>
     </row>
@@ -6515,12 +6544,12 @@
         </is>
       </c>
       <c r="C35" s="36" t="n"/>
-      <c r="D35" s="43" t="n"/>
-      <c r="E35" s="43" t="n"/>
-      <c r="F35" s="43" t="n"/>
-      <c r="G35" s="43" t="n"/>
-      <c r="H35" s="43" t="n"/>
-      <c r="I35" s="43" t="n"/>
+      <c r="D35" s="36" t="n"/>
+      <c r="E35" s="36" t="n"/>
+      <c r="F35" s="36" t="n"/>
+      <c r="G35" s="36" t="n"/>
+      <c r="H35" s="36" t="n"/>
+      <c r="I35" s="36" t="n"/>
       <c r="J35" s="51" t="n"/>
       <c r="K35" s="51" t="n"/>
     </row>
@@ -6530,13 +6559,13 @@
           <t>Sept_2022</t>
         </is>
       </c>
-      <c r="C36" s="46" t="n"/>
-      <c r="D36" s="46" t="n"/>
-      <c r="E36" s="46" t="n"/>
-      <c r="F36" s="46" t="n"/>
-      <c r="G36" s="46" t="n"/>
-      <c r="H36" s="46" t="n"/>
-      <c r="I36" s="46" t="n"/>
+      <c r="C36" s="36" t="n"/>
+      <c r="D36" s="36" t="n"/>
+      <c r="E36" s="36" t="n"/>
+      <c r="F36" s="36" t="n"/>
+      <c r="G36" s="36" t="n"/>
+      <c r="H36" s="36" t="n"/>
+      <c r="I36" s="36" t="n"/>
       <c r="J36" s="51" t="n"/>
       <c r="K36" s="51" t="n"/>
     </row>
@@ -6570,7 +6599,7 @@
           <t>Heat &amp; Temperature</t>
         </is>
       </c>
-      <c r="E39" s="67" t="inlineStr">
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>Waves, Sound &amp; Light</t>
         </is>
@@ -6584,7 +6613,7 @@
       <c r="B40" s="64" t="n"/>
       <c r="C40" s="66" t="n"/>
       <c r="D40" s="66" t="n"/>
-      <c r="E40" s="65" t="n"/>
+      <c r="E40" s="66" t="n"/>
       <c r="F40" s="54" t="n"/>
       <c r="G40" s="54" t="n"/>
       <c r="J40" s="51" t="n"/>
@@ -6610,9 +6639,9 @@
           <t>Sept_2016</t>
         </is>
       </c>
-      <c r="C42" s="40" t="n"/>
-      <c r="D42" s="40" t="n"/>
-      <c r="E42" s="40" t="n"/>
+      <c r="C42" s="36" t="n"/>
+      <c r="D42" s="36" t="n"/>
+      <c r="E42" s="36" t="n"/>
       <c r="F42" s="49" t="n"/>
       <c r="G42" s="49" t="n"/>
       <c r="J42" s="51" t="n"/>
@@ -6680,9 +6709,9 @@
           <t>Sept_2021</t>
         </is>
       </c>
-      <c r="C47" s="43" t="n"/>
-      <c r="D47" s="43" t="n"/>
-      <c r="E47" s="43" t="n"/>
+      <c r="C47" s="36" t="n"/>
+      <c r="D47" s="36" t="n"/>
+      <c r="E47" s="36" t="n"/>
       <c r="F47" s="49" t="n"/>
       <c r="G47" s="49" t="n"/>
       <c r="J47" s="51" t="n"/>
@@ -6694,9 +6723,9 @@
           <t>Sept_2022</t>
         </is>
       </c>
-      <c r="C48" s="46" t="n"/>
-      <c r="D48" s="46" t="n"/>
-      <c r="E48" s="46" t="n"/>
+      <c r="C48" s="36" t="n"/>
+      <c r="D48" s="36" t="n"/>
+      <c r="E48" s="36" t="n"/>
       <c r="F48" s="49" t="n"/>
       <c r="G48" s="49" t="n"/>
       <c r="J48" s="51" t="n"/>
@@ -6796,13 +6825,13 @@
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C54" s="40" t="n"/>
-      <c r="D54" s="40" t="n"/>
-      <c r="E54" s="40" t="n"/>
-      <c r="F54" s="40" t="n"/>
-      <c r="G54" s="40" t="n"/>
-      <c r="H54" s="40" t="n"/>
-      <c r="I54" s="40" t="n"/>
+      <c r="C54" s="36" t="n"/>
+      <c r="D54" s="36" t="n"/>
+      <c r="E54" s="36" t="n"/>
+      <c r="F54" s="36" t="n"/>
+      <c r="G54" s="36" t="n"/>
+      <c r="H54" s="36" t="n"/>
+      <c r="I54" s="36" t="n"/>
       <c r="J54" s="51" t="n"/>
       <c r="K54" s="51" t="n"/>
     </row>
@@ -6855,18 +6884,18 @@
       <c r="K57" s="51" t="n"/>
     </row>
     <row r="58">
-      <c r="B58" s="15" t="inlineStr">
+      <c r="B58" s="68" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C58" s="36" t="n"/>
-      <c r="D58" s="36" t="n"/>
-      <c r="E58" s="36" t="n"/>
-      <c r="F58" s="36" t="n"/>
-      <c r="G58" s="36" t="n"/>
-      <c r="H58" s="36" t="n"/>
-      <c r="I58" s="36" t="n"/>
+      <c r="C58" s="69" t="n"/>
+      <c r="D58" s="69" t="n"/>
+      <c r="E58" s="69" t="n"/>
+      <c r="F58" s="69" t="n"/>
+      <c r="G58" s="69" t="n"/>
+      <c r="H58" s="69" t="n"/>
+      <c r="I58" s="69" t="n"/>
       <c r="J58" s="51" t="n"/>
       <c r="K58" s="51" t="n"/>
     </row>
@@ -6877,12 +6906,12 @@
         </is>
       </c>
       <c r="C59" s="36" t="n"/>
-      <c r="D59" s="43" t="n"/>
-      <c r="E59" s="43" t="n"/>
-      <c r="F59" s="43" t="n"/>
-      <c r="G59" s="43" t="n"/>
-      <c r="H59" s="43" t="n"/>
-      <c r="I59" s="43" t="n"/>
+      <c r="D59" s="36" t="n"/>
+      <c r="E59" s="36" t="n"/>
+      <c r="F59" s="36" t="n"/>
+      <c r="G59" s="36" t="n"/>
+      <c r="H59" s="36" t="n"/>
+      <c r="I59" s="36" t="n"/>
       <c r="J59" s="51" t="n"/>
       <c r="K59" s="51" t="n"/>
     </row>
@@ -6892,13 +6921,13 @@
           <t>May/Jun_2022</t>
         </is>
       </c>
-      <c r="C60" s="46" t="n"/>
-      <c r="D60" s="46" t="n"/>
-      <c r="E60" s="46" t="n"/>
-      <c r="F60" s="46" t="n"/>
-      <c r="G60" s="46" t="n"/>
-      <c r="H60" s="46" t="n"/>
-      <c r="I60" s="46" t="n"/>
+      <c r="C60" s="36" t="n"/>
+      <c r="D60" s="36" t="n"/>
+      <c r="E60" s="36" t="n"/>
+      <c r="F60" s="36" t="n"/>
+      <c r="G60" s="36" t="n"/>
+      <c r="H60" s="36" t="n"/>
+      <c r="I60" s="36" t="n"/>
       <c r="J60" s="51" t="n"/>
       <c r="K60" s="51" t="n"/>
     </row>
@@ -6932,7 +6961,7 @@
           <t>Heat &amp; Temperature</t>
         </is>
       </c>
-      <c r="E63" s="67" t="inlineStr">
+      <c r="E63" s="12" t="inlineStr">
         <is>
           <t>Waves, Sound &amp; Light</t>
         </is>
@@ -6946,7 +6975,7 @@
       <c r="B64" s="64" t="n"/>
       <c r="C64" s="66" t="n"/>
       <c r="D64" s="66" t="n"/>
-      <c r="E64" s="65" t="n"/>
+      <c r="E64" s="66" t="n"/>
       <c r="F64" s="54" t="n"/>
       <c r="G64" s="54" t="n"/>
       <c r="J64" s="51" t="n"/>
@@ -6972,9 +7001,9 @@
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C66" s="40" t="n"/>
-      <c r="D66" s="40" t="n"/>
-      <c r="E66" s="40" t="n"/>
+      <c r="C66" s="36" t="n"/>
+      <c r="D66" s="36" t="n"/>
+      <c r="E66" s="36" t="n"/>
       <c r="F66" s="49" t="n"/>
       <c r="G66" s="49" t="n"/>
       <c r="J66" s="51" t="n"/>
@@ -7023,14 +7052,14 @@
       <c r="K69" s="51" t="n"/>
     </row>
     <row r="70">
-      <c r="B70" s="15" t="inlineStr">
+      <c r="B70" s="68" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C70" s="36" t="n"/>
-      <c r="D70" s="36" t="n"/>
-      <c r="E70" s="36" t="n"/>
+      <c r="C70" s="69" t="n"/>
+      <c r="D70" s="69" t="n"/>
+      <c r="E70" s="69" t="n"/>
       <c r="F70" s="49" t="n"/>
       <c r="G70" s="49" t="n"/>
       <c r="J70" s="51" t="n"/>
@@ -7042,9 +7071,9 @@
           <t>May/Jun_2021</t>
         </is>
       </c>
-      <c r="C71" s="43" t="n"/>
-      <c r="D71" s="43" t="n"/>
-      <c r="E71" s="43" t="n"/>
+      <c r="C71" s="36" t="n"/>
+      <c r="D71" s="36" t="n"/>
+      <c r="E71" s="36" t="n"/>
       <c r="F71" s="49" t="n"/>
       <c r="G71" s="49" t="n"/>
       <c r="J71" s="51" t="n"/>
@@ -7056,9 +7085,9 @@
           <t>May/Jun_2022</t>
         </is>
       </c>
-      <c r="C72" s="46" t="n"/>
-      <c r="D72" s="46" t="n"/>
-      <c r="E72" s="46" t="n"/>
+      <c r="C72" s="36" t="n"/>
+      <c r="D72" s="36" t="n"/>
+      <c r="E72" s="36" t="n"/>
       <c r="F72" s="49" t="n"/>
       <c r="G72" s="49" t="n"/>
       <c r="J72" s="51" t="n"/>
@@ -7158,13 +7187,13 @@
           <t>Feb/Mar_2016</t>
         </is>
       </c>
-      <c r="C78" s="40" t="n"/>
-      <c r="D78" s="40" t="n"/>
-      <c r="E78" s="40" t="n"/>
-      <c r="F78" s="40" t="n"/>
-      <c r="G78" s="40" t="n"/>
-      <c r="H78" s="40" t="n"/>
-      <c r="I78" s="40" t="n"/>
+      <c r="C78" s="36" t="n"/>
+      <c r="D78" s="36" t="n"/>
+      <c r="E78" s="36" t="n"/>
+      <c r="F78" s="36" t="n"/>
+      <c r="G78" s="36" t="n"/>
+      <c r="H78" s="36" t="n"/>
+      <c r="I78" s="36" t="n"/>
       <c r="J78" s="51" t="n"/>
       <c r="K78" s="51" t="n"/>
     </row>
@@ -7239,12 +7268,12 @@
         </is>
       </c>
       <c r="C83" s="36" t="n"/>
-      <c r="D83" s="43" t="n"/>
-      <c r="E83" s="43" t="n"/>
-      <c r="F83" s="43" t="n"/>
-      <c r="G83" s="43" t="n"/>
-      <c r="H83" s="43" t="n"/>
-      <c r="I83" s="43" t="n"/>
+      <c r="D83" s="36" t="n"/>
+      <c r="E83" s="36" t="n"/>
+      <c r="F83" s="36" t="n"/>
+      <c r="G83" s="36" t="n"/>
+      <c r="H83" s="36" t="n"/>
+      <c r="I83" s="36" t="n"/>
       <c r="J83" s="51" t="n"/>
       <c r="K83" s="51" t="n"/>
     </row>
@@ -7254,13 +7283,13 @@
           <t>Feb/Mar_2022</t>
         </is>
       </c>
-      <c r="C84" s="46" t="n"/>
-      <c r="D84" s="46" t="n"/>
-      <c r="E84" s="46" t="n"/>
-      <c r="F84" s="46" t="n"/>
-      <c r="G84" s="46" t="n"/>
-      <c r="H84" s="46" t="n"/>
-      <c r="I84" s="46" t="n"/>
+      <c r="C84" s="36" t="n"/>
+      <c r="D84" s="36" t="n"/>
+      <c r="E84" s="36" t="n"/>
+      <c r="F84" s="36" t="n"/>
+      <c r="G84" s="36" t="n"/>
+      <c r="H84" s="36" t="n"/>
+      <c r="I84" s="36" t="n"/>
       <c r="J84" s="51" t="n"/>
       <c r="K84" s="51" t="n"/>
     </row>
@@ -7294,7 +7323,7 @@
           <t>Heat &amp; Temperature</t>
         </is>
       </c>
-      <c r="E87" s="67" t="inlineStr">
+      <c r="E87" s="12" t="inlineStr">
         <is>
           <t>Waves, Sound &amp; Light</t>
         </is>
@@ -7308,7 +7337,7 @@
       <c r="B88" s="64" t="n"/>
       <c r="C88" s="66" t="n"/>
       <c r="D88" s="66" t="n"/>
-      <c r="E88" s="65" t="n"/>
+      <c r="E88" s="66" t="n"/>
       <c r="F88" s="54" t="n"/>
       <c r="G88" s="54" t="n"/>
       <c r="J88" s="51" t="n"/>
@@ -7334,9 +7363,9 @@
           <t>Feb/Mar_2016</t>
         </is>
       </c>
-      <c r="C90" s="40" t="n"/>
-      <c r="D90" s="40" t="n"/>
-      <c r="E90" s="40" t="n"/>
+      <c r="C90" s="36" t="n"/>
+      <c r="D90" s="36" t="n"/>
+      <c r="E90" s="36" t="n"/>
       <c r="F90" s="49" t="n"/>
       <c r="G90" s="49" t="n"/>
       <c r="J90" s="51" t="n"/>
@@ -7404,9 +7433,9 @@
           <t>Feb/Mar_2021</t>
         </is>
       </c>
-      <c r="C95" s="43" t="n"/>
-      <c r="D95" s="43" t="n"/>
-      <c r="E95" s="43" t="n"/>
+      <c r="C95" s="36" t="n"/>
+      <c r="D95" s="36" t="n"/>
+      <c r="E95" s="36" t="n"/>
       <c r="F95" s="49" t="n"/>
       <c r="G95" s="49" t="n"/>
       <c r="J95" s="51" t="n"/>
@@ -7418,9 +7447,9 @@
           <t>Feb/Mar_2022</t>
         </is>
       </c>
-      <c r="C96" s="46" t="n"/>
-      <c r="D96" s="46" t="n"/>
-      <c r="E96" s="46" t="n"/>
+      <c r="C96" s="36" t="n"/>
+      <c r="D96" s="36" t="n"/>
+      <c r="E96" s="36" t="n"/>
       <c r="F96" s="49" t="n"/>
       <c r="G96" s="49" t="n"/>
       <c r="J96" s="51" t="n"/>
@@ -7430,7 +7459,6 @@
       <c r="J97" s="51" t="n"/>
       <c r="K97" s="51" t="n"/>
     </row>
-    <row r="98"/>
   </sheetData>
   <mergeCells count="56">
     <mergeCell ref="B27:B28"/>
@@ -7500,7 +7528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="B1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.12844036697248" defaultRowHeight="14.25"/>
   <cols>
     <col width="16.6238532110092" customWidth="1" style="3" min="2" max="23"/>
@@ -7906,13 +7934,13 @@
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C6" s="40" t="n"/>
-      <c r="D6" s="40" t="n"/>
-      <c r="E6" s="40" t="n"/>
-      <c r="F6" s="40" t="n"/>
-      <c r="G6" s="40" t="n"/>
-      <c r="H6" s="40" t="n"/>
-      <c r="I6" s="40" t="n"/>
+      <c r="C6" s="36" t="n"/>
+      <c r="D6" s="36" t="n"/>
+      <c r="E6" s="36" t="n"/>
+      <c r="F6" s="36" t="n"/>
+      <c r="G6" s="36" t="n"/>
+      <c r="H6" s="36" t="n"/>
+      <c r="I6" s="36" t="n"/>
     </row>
     <row r="7" ht="14.95" customHeight="1" s="25">
       <c r="B7" s="15" t="inlineStr">
@@ -7977,12 +8005,12 @@
         </is>
       </c>
       <c r="C11" s="36" t="n"/>
-      <c r="D11" s="43" t="n"/>
-      <c r="E11" s="43" t="n"/>
-      <c r="F11" s="43" t="n"/>
-      <c r="G11" s="43" t="n"/>
-      <c r="H11" s="43" t="n"/>
-      <c r="I11" s="43" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="36" t="n"/>
+      <c r="F11" s="36" t="n"/>
+      <c r="G11" s="36" t="n"/>
+      <c r="H11" s="36" t="n"/>
+      <c r="I11" s="36" t="n"/>
     </row>
     <row r="12" ht="14.95" customHeight="1" s="25">
       <c r="B12" s="20" t="inlineStr">
@@ -7990,13 +8018,13 @@
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C12" s="46" t="n"/>
-      <c r="D12" s="46" t="n"/>
-      <c r="E12" s="46" t="n"/>
-      <c r="F12" s="46" t="n"/>
-      <c r="G12" s="46" t="n"/>
-      <c r="H12" s="46" t="n"/>
-      <c r="I12" s="46" t="n"/>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="36" t="n"/>
+      <c r="F12" s="36" t="n"/>
+      <c r="G12" s="36" t="n"/>
+      <c r="H12" s="36" t="n"/>
+      <c r="I12" s="36" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="25"/>
     <row r="14" ht="15" customHeight="1" s="25">
@@ -8024,7 +8052,7 @@
           <t>Heat &amp; Temperature</t>
         </is>
       </c>
-      <c r="E15" s="67" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>Waves, Sound &amp; Light</t>
         </is>
@@ -8037,7 +8065,7 @@
       <c r="B16" s="64" t="n"/>
       <c r="C16" s="66" t="n"/>
       <c r="D16" s="66" t="n"/>
-      <c r="E16" s="65" t="n"/>
+      <c r="E16" s="66" t="n"/>
       <c r="F16" s="51" t="n"/>
       <c r="G16" s="51" t="n"/>
       <c r="H16" s="51" t="n"/>
@@ -8061,9 +8089,9 @@
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C18" s="40" t="n"/>
-      <c r="D18" s="40" t="n"/>
-      <c r="E18" s="40" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
       <c r="F18" s="51" t="n"/>
       <c r="G18" s="51" t="n"/>
       <c r="H18" s="51" t="n"/>
@@ -8126,9 +8154,9 @@
           <t>Nov_2021</t>
         </is>
       </c>
-      <c r="C23" s="43" t="n"/>
-      <c r="D23" s="43" t="n"/>
-      <c r="E23" s="43" t="n"/>
+      <c r="C23" s="36" t="n"/>
+      <c r="D23" s="36" t="n"/>
+      <c r="E23" s="36" t="n"/>
       <c r="F23" s="51" t="n"/>
       <c r="G23" s="51" t="n"/>
       <c r="H23" s="51" t="n"/>
@@ -8139,9 +8167,9 @@
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C24" s="46" t="n"/>
-      <c r="D24" s="46" t="n"/>
-      <c r="E24" s="46" t="n"/>
+      <c r="C24" s="36" t="n"/>
+      <c r="D24" s="36" t="n"/>
+      <c r="E24" s="36" t="n"/>
       <c r="F24" s="51" t="n"/>
       <c r="G24" s="51" t="n"/>
       <c r="H24" s="51" t="n"/>
@@ -8210,116 +8238,116 @@
       <c r="I28" s="66" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B29" s="68" t="inlineStr">
         <is>
           <t>Sept_2015</t>
         </is>
       </c>
-      <c r="C29" s="36" t="n"/>
-      <c r="D29" s="36" t="n"/>
-      <c r="E29" s="36" t="n"/>
-      <c r="F29" s="36" t="n"/>
-      <c r="G29" s="36" t="n"/>
-      <c r="H29" s="36" t="n"/>
-      <c r="I29" s="36" t="n"/>
+      <c r="C29" s="69" t="n"/>
+      <c r="D29" s="69" t="n"/>
+      <c r="E29" s="69" t="n"/>
+      <c r="F29" s="69" t="n"/>
+      <c r="G29" s="69" t="n"/>
+      <c r="H29" s="69" t="n"/>
+      <c r="I29" s="69" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B30" s="68" t="inlineStr">
         <is>
           <t>Sept_2016</t>
         </is>
       </c>
-      <c r="C30" s="40" t="n"/>
-      <c r="D30" s="40" t="n"/>
-      <c r="E30" s="40" t="n"/>
-      <c r="F30" s="40" t="n"/>
-      <c r="G30" s="40" t="n"/>
-      <c r="H30" s="40" t="n"/>
-      <c r="I30" s="40" t="n"/>
+      <c r="C30" s="69" t="n"/>
+      <c r="D30" s="69" t="n"/>
+      <c r="E30" s="69" t="n"/>
+      <c r="F30" s="69" t="n"/>
+      <c r="G30" s="69" t="n"/>
+      <c r="H30" s="69" t="n"/>
+      <c r="I30" s="69" t="n"/>
     </row>
     <row r="31">
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B31" s="68" t="inlineStr">
         <is>
           <t>Sept_2017</t>
         </is>
       </c>
-      <c r="C31" s="36" t="n"/>
-      <c r="D31" s="36" t="n"/>
-      <c r="E31" s="36" t="n"/>
-      <c r="F31" s="36" t="n"/>
-      <c r="G31" s="36" t="n"/>
-      <c r="H31" s="36" t="n"/>
-      <c r="I31" s="36" t="n"/>
+      <c r="C31" s="69" t="n"/>
+      <c r="D31" s="69" t="n"/>
+      <c r="E31" s="69" t="n"/>
+      <c r="F31" s="69" t="n"/>
+      <c r="G31" s="69" t="n"/>
+      <c r="H31" s="69" t="n"/>
+      <c r="I31" s="69" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="15" t="inlineStr">
+      <c r="B32" s="68" t="inlineStr">
         <is>
           <t>Sept_2018</t>
         </is>
       </c>
-      <c r="C32" s="36" t="n"/>
-      <c r="D32" s="36" t="n"/>
-      <c r="E32" s="36" t="n"/>
-      <c r="F32" s="36" t="n"/>
-      <c r="G32" s="36" t="n"/>
-      <c r="H32" s="36" t="n"/>
-      <c r="I32" s="36" t="n"/>
+      <c r="C32" s="69" t="n"/>
+      <c r="D32" s="69" t="n"/>
+      <c r="E32" s="69" t="n"/>
+      <c r="F32" s="69" t="n"/>
+      <c r="G32" s="69" t="n"/>
+      <c r="H32" s="69" t="n"/>
+      <c r="I32" s="69" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B33" s="68" t="inlineStr">
         <is>
           <t>Sept_2019</t>
         </is>
       </c>
-      <c r="C33" s="36" t="n"/>
-      <c r="D33" s="36" t="n"/>
-      <c r="E33" s="36" t="n"/>
-      <c r="F33" s="36" t="n"/>
-      <c r="G33" s="36" t="n"/>
-      <c r="H33" s="36" t="n"/>
-      <c r="I33" s="36" t="n"/>
+      <c r="C33" s="69" t="n"/>
+      <c r="D33" s="69" t="n"/>
+      <c r="E33" s="69" t="n"/>
+      <c r="F33" s="69" t="n"/>
+      <c r="G33" s="69" t="n"/>
+      <c r="H33" s="69" t="n"/>
+      <c r="I33" s="69" t="n"/>
     </row>
     <row r="34">
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B34" s="68" t="inlineStr">
         <is>
           <t>Sept_2020</t>
         </is>
       </c>
-      <c r="C34" s="36" t="n"/>
-      <c r="D34" s="36" t="n"/>
-      <c r="E34" s="36" t="n"/>
-      <c r="F34" s="36" t="n"/>
-      <c r="G34" s="36" t="n"/>
-      <c r="H34" s="36" t="n"/>
-      <c r="I34" s="36" t="n"/>
+      <c r="C34" s="69" t="n"/>
+      <c r="D34" s="69" t="n"/>
+      <c r="E34" s="69" t="n"/>
+      <c r="F34" s="69" t="n"/>
+      <c r="G34" s="69" t="n"/>
+      <c r="H34" s="69" t="n"/>
+      <c r="I34" s="69" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" s="15" t="inlineStr">
+      <c r="B35" s="68" t="inlineStr">
         <is>
           <t>Sept_2021</t>
         </is>
       </c>
-      <c r="C35" s="36" t="n"/>
-      <c r="D35" s="43" t="n"/>
-      <c r="E35" s="43" t="n"/>
-      <c r="F35" s="43" t="n"/>
-      <c r="G35" s="43" t="n"/>
-      <c r="H35" s="43" t="n"/>
-      <c r="I35" s="43" t="n"/>
+      <c r="C35" s="69" t="n"/>
+      <c r="D35" s="69" t="n"/>
+      <c r="E35" s="69" t="n"/>
+      <c r="F35" s="69" t="n"/>
+      <c r="G35" s="69" t="n"/>
+      <c r="H35" s="69" t="n"/>
+      <c r="I35" s="69" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1" s="25">
-      <c r="B36" s="20" t="inlineStr">
+      <c r="B36" s="70" t="inlineStr">
         <is>
           <t>Sept_2022</t>
         </is>
       </c>
-      <c r="C36" s="46" t="n"/>
-      <c r="D36" s="46" t="n"/>
-      <c r="E36" s="46" t="n"/>
-      <c r="F36" s="46" t="n"/>
-      <c r="G36" s="46" t="n"/>
-      <c r="H36" s="46" t="n"/>
-      <c r="I36" s="46" t="n"/>
+      <c r="C36" s="69" t="n"/>
+      <c r="D36" s="69" t="n"/>
+      <c r="E36" s="69" t="n"/>
+      <c r="F36" s="69" t="n"/>
+      <c r="G36" s="69" t="n"/>
+      <c r="H36" s="69" t="n"/>
+      <c r="I36" s="69" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1" s="25"/>
     <row r="38" ht="15" customHeight="1" s="25">
@@ -8346,7 +8374,7 @@
           <t>Heat &amp; Temperature</t>
         </is>
       </c>
-      <c r="E39" s="67" t="inlineStr">
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>Waves, Sound &amp; Light</t>
         </is>
@@ -8358,103 +8386,103 @@
       <c r="B40" s="64" t="n"/>
       <c r="C40" s="66" t="n"/>
       <c r="D40" s="66" t="n"/>
-      <c r="E40" s="65" t="n"/>
+      <c r="E40" s="66" t="n"/>
       <c r="F40" s="54" t="n"/>
       <c r="G40" s="54" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="15" t="inlineStr">
+      <c r="B41" s="68" t="inlineStr">
         <is>
           <t>Sept_2015</t>
         </is>
       </c>
-      <c r="C41" s="36" t="n"/>
-      <c r="D41" s="36" t="n"/>
-      <c r="E41" s="36" t="n"/>
+      <c r="C41" s="69" t="n"/>
+      <c r="D41" s="69" t="n"/>
+      <c r="E41" s="69" t="n"/>
       <c r="F41" s="49" t="n"/>
       <c r="G41" s="49" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" s="15" t="inlineStr">
+      <c r="B42" s="68" t="inlineStr">
         <is>
           <t>Sept_2016</t>
         </is>
       </c>
-      <c r="C42" s="40" t="n"/>
-      <c r="D42" s="40" t="n"/>
-      <c r="E42" s="40" t="n"/>
+      <c r="C42" s="69" t="n"/>
+      <c r="D42" s="69" t="n"/>
+      <c r="E42" s="69" t="n"/>
       <c r="F42" s="49" t="n"/>
       <c r="G42" s="49" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" s="15" t="inlineStr">
+      <c r="B43" s="68" t="inlineStr">
         <is>
           <t>Sept_2017</t>
         </is>
       </c>
-      <c r="C43" s="36" t="n"/>
-      <c r="D43" s="36" t="n"/>
-      <c r="E43" s="36" t="n"/>
+      <c r="C43" s="69" t="n"/>
+      <c r="D43" s="69" t="n"/>
+      <c r="E43" s="69" t="n"/>
       <c r="F43" s="49" t="n"/>
       <c r="G43" s="49" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" s="15" t="inlineStr">
+      <c r="B44" s="68" t="inlineStr">
         <is>
           <t>Sept_2018</t>
         </is>
       </c>
-      <c r="C44" s="36" t="n"/>
-      <c r="D44" s="36" t="n"/>
-      <c r="E44" s="36" t="n"/>
+      <c r="C44" s="69" t="n"/>
+      <c r="D44" s="69" t="n"/>
+      <c r="E44" s="69" t="n"/>
       <c r="F44" s="49" t="n"/>
       <c r="G44" s="49" t="n"/>
     </row>
     <row r="45">
-      <c r="B45" s="15" t="inlineStr">
+      <c r="B45" s="68" t="inlineStr">
         <is>
           <t>Sept_2019</t>
         </is>
       </c>
-      <c r="C45" s="36" t="n"/>
-      <c r="D45" s="36" t="n"/>
-      <c r="E45" s="36" t="n"/>
+      <c r="C45" s="69" t="n"/>
+      <c r="D45" s="69" t="n"/>
+      <c r="E45" s="69" t="n"/>
       <c r="F45" s="49" t="n"/>
       <c r="G45" s="49" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="15" t="inlineStr">
+      <c r="B46" s="68" t="inlineStr">
         <is>
           <t>Sept_2020</t>
         </is>
       </c>
-      <c r="C46" s="36" t="n"/>
-      <c r="D46" s="36" t="n"/>
-      <c r="E46" s="36" t="n"/>
+      <c r="C46" s="69" t="n"/>
+      <c r="D46" s="69" t="n"/>
+      <c r="E46" s="69" t="n"/>
       <c r="F46" s="49" t="n"/>
       <c r="G46" s="49" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="15" t="inlineStr">
+      <c r="B47" s="68" t="inlineStr">
         <is>
           <t>Sept_2021</t>
         </is>
       </c>
-      <c r="C47" s="43" t="n"/>
-      <c r="D47" s="43" t="n"/>
-      <c r="E47" s="43" t="n"/>
+      <c r="C47" s="69" t="n"/>
+      <c r="D47" s="69" t="n"/>
+      <c r="E47" s="69" t="n"/>
       <c r="F47" s="49" t="n"/>
       <c r="G47" s="49" t="n"/>
     </row>
     <row r="48" ht="15" customHeight="1" s="25">
-      <c r="B48" s="20" t="inlineStr">
+      <c r="B48" s="70" t="inlineStr">
         <is>
           <t>Sept_2022</t>
         </is>
       </c>
-      <c r="C48" s="46" t="n"/>
-      <c r="D48" s="46" t="n"/>
-      <c r="E48" s="46" t="n"/>
+      <c r="C48" s="69" t="n"/>
+      <c r="D48" s="69" t="n"/>
+      <c r="E48" s="69" t="n"/>
       <c r="F48" s="49" t="n"/>
       <c r="G48" s="49" t="n"/>
     </row>
@@ -8522,116 +8550,116 @@
       <c r="I52" s="66" t="n"/>
     </row>
     <row r="53">
-      <c r="B53" s="15" t="inlineStr">
+      <c r="B53" s="68" t="inlineStr">
         <is>
           <t>May/Jun_2015</t>
         </is>
       </c>
-      <c r="C53" s="36" t="n"/>
-      <c r="D53" s="36" t="n"/>
-      <c r="E53" s="36" t="n"/>
-      <c r="F53" s="36" t="n"/>
-      <c r="G53" s="36" t="n"/>
-      <c r="H53" s="36" t="n"/>
-      <c r="I53" s="36" t="n"/>
+      <c r="C53" s="69" t="n"/>
+      <c r="D53" s="69" t="n"/>
+      <c r="E53" s="69" t="n"/>
+      <c r="F53" s="69" t="n"/>
+      <c r="G53" s="69" t="n"/>
+      <c r="H53" s="69" t="n"/>
+      <c r="I53" s="69" t="n"/>
     </row>
     <row r="54">
-      <c r="B54" s="15" t="inlineStr">
+      <c r="B54" s="68" t="inlineStr">
         <is>
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C54" s="40" t="n"/>
-      <c r="D54" s="40" t="n"/>
-      <c r="E54" s="40" t="n"/>
-      <c r="F54" s="40" t="n"/>
-      <c r="G54" s="40" t="n"/>
-      <c r="H54" s="40" t="n"/>
-      <c r="I54" s="40" t="n"/>
+      <c r="C54" s="69" t="n"/>
+      <c r="D54" s="69" t="n"/>
+      <c r="E54" s="69" t="n"/>
+      <c r="F54" s="69" t="n"/>
+      <c r="G54" s="69" t="n"/>
+      <c r="H54" s="69" t="n"/>
+      <c r="I54" s="69" t="n"/>
     </row>
     <row r="55">
-      <c r="B55" s="15" t="inlineStr">
+      <c r="B55" s="68" t="inlineStr">
         <is>
           <t>May/Jun_2017</t>
         </is>
       </c>
-      <c r="C55" s="36" t="n"/>
-      <c r="D55" s="36" t="n"/>
-      <c r="E55" s="36" t="n"/>
-      <c r="F55" s="36" t="n"/>
-      <c r="G55" s="36" t="n"/>
-      <c r="H55" s="36" t="n"/>
-      <c r="I55" s="36" t="n"/>
+      <c r="C55" s="69" t="n"/>
+      <c r="D55" s="69" t="n"/>
+      <c r="E55" s="69" t="n"/>
+      <c r="F55" s="69" t="n"/>
+      <c r="G55" s="69" t="n"/>
+      <c r="H55" s="69" t="n"/>
+      <c r="I55" s="69" t="n"/>
     </row>
     <row r="56">
-      <c r="B56" s="15" t="inlineStr">
+      <c r="B56" s="68" t="inlineStr">
         <is>
           <t>May/Jun_2018</t>
         </is>
       </c>
-      <c r="C56" s="36" t="n"/>
-      <c r="D56" s="36" t="n"/>
-      <c r="E56" s="36" t="n"/>
-      <c r="F56" s="36" t="n"/>
-      <c r="G56" s="36" t="n"/>
-      <c r="H56" s="36" t="n"/>
-      <c r="I56" s="36" t="n"/>
+      <c r="C56" s="69" t="n"/>
+      <c r="D56" s="69" t="n"/>
+      <c r="E56" s="69" t="n"/>
+      <c r="F56" s="69" t="n"/>
+      <c r="G56" s="69" t="n"/>
+      <c r="H56" s="69" t="n"/>
+      <c r="I56" s="69" t="n"/>
     </row>
     <row r="57">
-      <c r="B57" s="15" t="inlineStr">
+      <c r="B57" s="68" t="inlineStr">
         <is>
           <t>May/Jun_2019</t>
         </is>
       </c>
-      <c r="C57" s="36" t="n"/>
-      <c r="D57" s="36" t="n"/>
-      <c r="E57" s="36" t="n"/>
-      <c r="F57" s="36" t="n"/>
-      <c r="G57" s="36" t="n"/>
-      <c r="H57" s="36" t="n"/>
-      <c r="I57" s="36" t="n"/>
+      <c r="C57" s="69" t="n"/>
+      <c r="D57" s="69" t="n"/>
+      <c r="E57" s="69" t="n"/>
+      <c r="F57" s="69" t="n"/>
+      <c r="G57" s="69" t="n"/>
+      <c r="H57" s="69" t="n"/>
+      <c r="I57" s="69" t="n"/>
     </row>
     <row r="58">
-      <c r="B58" s="15" t="inlineStr">
+      <c r="B58" s="68" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C58" s="36" t="n"/>
-      <c r="D58" s="36" t="n"/>
-      <c r="E58" s="36" t="n"/>
-      <c r="F58" s="36" t="n"/>
-      <c r="G58" s="36" t="n"/>
-      <c r="H58" s="36" t="n"/>
-      <c r="I58" s="36" t="n"/>
+      <c r="C58" s="69" t="n"/>
+      <c r="D58" s="69" t="n"/>
+      <c r="E58" s="69" t="n"/>
+      <c r="F58" s="69" t="n"/>
+      <c r="G58" s="69" t="n"/>
+      <c r="H58" s="69" t="n"/>
+      <c r="I58" s="69" t="n"/>
     </row>
     <row r="59">
-      <c r="B59" s="15" t="inlineStr">
+      <c r="B59" s="68" t="inlineStr">
         <is>
           <t>May/Jun_2021</t>
         </is>
       </c>
-      <c r="C59" s="36" t="n"/>
-      <c r="D59" s="43" t="n"/>
-      <c r="E59" s="43" t="n"/>
-      <c r="F59" s="43" t="n"/>
-      <c r="G59" s="43" t="n"/>
-      <c r="H59" s="43" t="n"/>
-      <c r="I59" s="43" t="n"/>
+      <c r="C59" s="69" t="n"/>
+      <c r="D59" s="69" t="n"/>
+      <c r="E59" s="69" t="n"/>
+      <c r="F59" s="69" t="n"/>
+      <c r="G59" s="69" t="n"/>
+      <c r="H59" s="69" t="n"/>
+      <c r="I59" s="69" t="n"/>
     </row>
     <row r="60" ht="15" customHeight="1" s="25">
-      <c r="B60" s="20" t="inlineStr">
+      <c r="B60" s="70" t="inlineStr">
         <is>
           <t>May/Jun_2022</t>
         </is>
       </c>
-      <c r="C60" s="46" t="n"/>
-      <c r="D60" s="46" t="n"/>
-      <c r="E60" s="46" t="n"/>
-      <c r="F60" s="46" t="n"/>
-      <c r="G60" s="46" t="n"/>
-      <c r="H60" s="46" t="n"/>
-      <c r="I60" s="46" t="n"/>
+      <c r="C60" s="69" t="n"/>
+      <c r="D60" s="69" t="n"/>
+      <c r="E60" s="69" t="n"/>
+      <c r="F60" s="69" t="n"/>
+      <c r="G60" s="69" t="n"/>
+      <c r="H60" s="69" t="n"/>
+      <c r="I60" s="69" t="n"/>
     </row>
     <row r="61" ht="15" customHeight="1" s="25"/>
     <row r="62" ht="15" customHeight="1" s="25">
@@ -8658,7 +8686,7 @@
           <t>Heat &amp; Temperature</t>
         </is>
       </c>
-      <c r="E63" s="67" t="inlineStr">
+      <c r="E63" s="12" t="inlineStr">
         <is>
           <t>Waves, Sound &amp; Light</t>
         </is>
@@ -8670,103 +8698,103 @@
       <c r="B64" s="64" t="n"/>
       <c r="C64" s="66" t="n"/>
       <c r="D64" s="66" t="n"/>
-      <c r="E64" s="65" t="n"/>
+      <c r="E64" s="66" t="n"/>
       <c r="F64" s="54" t="n"/>
       <c r="G64" s="54" t="n"/>
     </row>
     <row r="65">
-      <c r="B65" s="15" t="inlineStr">
+      <c r="B65" s="68" t="inlineStr">
         <is>
           <t>May/Jun_2015</t>
         </is>
       </c>
-      <c r="C65" s="36" t="n"/>
-      <c r="D65" s="36" t="n"/>
-      <c r="E65" s="36" t="n"/>
+      <c r="C65" s="69" t="n"/>
+      <c r="D65" s="69" t="n"/>
+      <c r="E65" s="69" t="n"/>
       <c r="F65" s="49" t="n"/>
       <c r="G65" s="49" t="n"/>
     </row>
     <row r="66">
-      <c r="B66" s="15" t="inlineStr">
+      <c r="B66" s="68" t="inlineStr">
         <is>
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C66" s="40" t="n"/>
-      <c r="D66" s="40" t="n"/>
-      <c r="E66" s="40" t="n"/>
+      <c r="C66" s="69" t="n"/>
+      <c r="D66" s="69" t="n"/>
+      <c r="E66" s="69" t="n"/>
       <c r="F66" s="49" t="n"/>
       <c r="G66" s="49" t="n"/>
     </row>
     <row r="67">
-      <c r="B67" s="15" t="inlineStr">
+      <c r="B67" s="68" t="inlineStr">
         <is>
           <t>May/Jun_2017</t>
         </is>
       </c>
-      <c r="C67" s="36" t="n"/>
-      <c r="D67" s="36" t="n"/>
-      <c r="E67" s="36" t="n"/>
+      <c r="C67" s="69" t="n"/>
+      <c r="D67" s="69" t="n"/>
+      <c r="E67" s="69" t="n"/>
       <c r="F67" s="49" t="n"/>
       <c r="G67" s="49" t="n"/>
     </row>
     <row r="68">
-      <c r="B68" s="15" t="inlineStr">
+      <c r="B68" s="68" t="inlineStr">
         <is>
           <t>May/Jun_2018</t>
         </is>
       </c>
-      <c r="C68" s="36" t="n"/>
-      <c r="D68" s="36" t="n"/>
-      <c r="E68" s="36" t="n"/>
+      <c r="C68" s="69" t="n"/>
+      <c r="D68" s="69" t="n"/>
+      <c r="E68" s="69" t="n"/>
       <c r="F68" s="49" t="n"/>
       <c r="G68" s="49" t="n"/>
     </row>
     <row r="69">
-      <c r="B69" s="15" t="inlineStr">
+      <c r="B69" s="68" t="inlineStr">
         <is>
           <t>May/Jun_2019</t>
         </is>
       </c>
-      <c r="C69" s="36" t="n"/>
-      <c r="D69" s="36" t="n"/>
-      <c r="E69" s="36" t="n"/>
+      <c r="C69" s="69" t="n"/>
+      <c r="D69" s="69" t="n"/>
+      <c r="E69" s="69" t="n"/>
       <c r="F69" s="49" t="n"/>
       <c r="G69" s="49" t="n"/>
     </row>
     <row r="70">
-      <c r="B70" s="15" t="inlineStr">
+      <c r="B70" s="68" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C70" s="36" t="n"/>
-      <c r="D70" s="36" t="n"/>
-      <c r="E70" s="36" t="n"/>
+      <c r="C70" s="69" t="n"/>
+      <c r="D70" s="69" t="n"/>
+      <c r="E70" s="69" t="n"/>
       <c r="F70" s="49" t="n"/>
       <c r="G70" s="49" t="n"/>
     </row>
     <row r="71">
-      <c r="B71" s="15" t="inlineStr">
+      <c r="B71" s="68" t="inlineStr">
         <is>
           <t>May/Jun_2021</t>
         </is>
       </c>
-      <c r="C71" s="43" t="n"/>
-      <c r="D71" s="43" t="n"/>
-      <c r="E71" s="43" t="n"/>
+      <c r="C71" s="69" t="n"/>
+      <c r="D71" s="69" t="n"/>
+      <c r="E71" s="69" t="n"/>
       <c r="F71" s="49" t="n"/>
       <c r="G71" s="49" t="n"/>
     </row>
     <row r="72" ht="15" customHeight="1" s="25">
-      <c r="B72" s="20" t="inlineStr">
+      <c r="B72" s="70" t="inlineStr">
         <is>
           <t>May/Jun_2022</t>
         </is>
       </c>
-      <c r="C72" s="46" t="n"/>
-      <c r="D72" s="46" t="n"/>
-      <c r="E72" s="46" t="n"/>
+      <c r="C72" s="69" t="n"/>
+      <c r="D72" s="69" t="n"/>
+      <c r="E72" s="69" t="n"/>
       <c r="F72" s="49" t="n"/>
       <c r="G72" s="49" t="n"/>
     </row>
@@ -8834,116 +8862,116 @@
       <c r="I76" s="66" t="n"/>
     </row>
     <row r="77">
-      <c r="B77" s="15" t="inlineStr">
+      <c r="B77" s="68" t="inlineStr">
         <is>
           <t>Feb/Mar_2015</t>
         </is>
       </c>
-      <c r="C77" s="36" t="n"/>
-      <c r="D77" s="36" t="n"/>
-      <c r="E77" s="36" t="n"/>
-      <c r="F77" s="36" t="n"/>
-      <c r="G77" s="36" t="n"/>
-      <c r="H77" s="36" t="n"/>
-      <c r="I77" s="36" t="n"/>
+      <c r="C77" s="69" t="n"/>
+      <c r="D77" s="69" t="n"/>
+      <c r="E77" s="69" t="n"/>
+      <c r="F77" s="69" t="n"/>
+      <c r="G77" s="69" t="n"/>
+      <c r="H77" s="69" t="n"/>
+      <c r="I77" s="69" t="n"/>
     </row>
     <row r="78">
-      <c r="B78" s="15" t="inlineStr">
+      <c r="B78" s="68" t="inlineStr">
         <is>
           <t>Feb/Mar_2016</t>
         </is>
       </c>
-      <c r="C78" s="40" t="n"/>
-      <c r="D78" s="40" t="n"/>
-      <c r="E78" s="40" t="n"/>
-      <c r="F78" s="40" t="n"/>
-      <c r="G78" s="40" t="n"/>
-      <c r="H78" s="40" t="n"/>
-      <c r="I78" s="40" t="n"/>
+      <c r="C78" s="69" t="n"/>
+      <c r="D78" s="69" t="n"/>
+      <c r="E78" s="69" t="n"/>
+      <c r="F78" s="69" t="n"/>
+      <c r="G78" s="69" t="n"/>
+      <c r="H78" s="69" t="n"/>
+      <c r="I78" s="69" t="n"/>
     </row>
     <row r="79">
-      <c r="B79" s="15" t="inlineStr">
+      <c r="B79" s="68" t="inlineStr">
         <is>
           <t>Feb/Mar_2017</t>
         </is>
       </c>
-      <c r="C79" s="36" t="n"/>
-      <c r="D79" s="36" t="n"/>
-      <c r="E79" s="36" t="n"/>
-      <c r="F79" s="36" t="n"/>
-      <c r="G79" s="36" t="n"/>
-      <c r="H79" s="36" t="n"/>
-      <c r="I79" s="36" t="n"/>
+      <c r="C79" s="69" t="n"/>
+      <c r="D79" s="69" t="n"/>
+      <c r="E79" s="69" t="n"/>
+      <c r="F79" s="69" t="n"/>
+      <c r="G79" s="69" t="n"/>
+      <c r="H79" s="69" t="n"/>
+      <c r="I79" s="69" t="n"/>
     </row>
     <row r="80">
-      <c r="B80" s="15" t="inlineStr">
+      <c r="B80" s="68" t="inlineStr">
         <is>
           <t>Feb/Mar_2018</t>
         </is>
       </c>
-      <c r="C80" s="36" t="n"/>
-      <c r="D80" s="36" t="n"/>
-      <c r="E80" s="36" t="n"/>
-      <c r="F80" s="36" t="n"/>
-      <c r="G80" s="36" t="n"/>
-      <c r="H80" s="36" t="n"/>
-      <c r="I80" s="36" t="n"/>
+      <c r="C80" s="69" t="n"/>
+      <c r="D80" s="69" t="n"/>
+      <c r="E80" s="69" t="n"/>
+      <c r="F80" s="69" t="n"/>
+      <c r="G80" s="69" t="n"/>
+      <c r="H80" s="69" t="n"/>
+      <c r="I80" s="69" t="n"/>
     </row>
     <row r="81">
-      <c r="B81" s="15" t="inlineStr">
+      <c r="B81" s="68" t="inlineStr">
         <is>
           <t>Feb/Mar_2019</t>
         </is>
       </c>
-      <c r="C81" s="36" t="n"/>
-      <c r="D81" s="36" t="n"/>
-      <c r="E81" s="36" t="n"/>
-      <c r="F81" s="36" t="n"/>
-      <c r="G81" s="36" t="n"/>
-      <c r="H81" s="36" t="n"/>
-      <c r="I81" s="36" t="n"/>
+      <c r="C81" s="69" t="n"/>
+      <c r="D81" s="69" t="n"/>
+      <c r="E81" s="69" t="n"/>
+      <c r="F81" s="69" t="n"/>
+      <c r="G81" s="69" t="n"/>
+      <c r="H81" s="69" t="n"/>
+      <c r="I81" s="69" t="n"/>
     </row>
     <row r="82">
-      <c r="B82" s="15" t="inlineStr">
+      <c r="B82" s="68" t="inlineStr">
         <is>
           <t>Feb/Mar_2020</t>
         </is>
       </c>
-      <c r="C82" s="36" t="n"/>
-      <c r="D82" s="36" t="n"/>
-      <c r="E82" s="36" t="n"/>
-      <c r="F82" s="36" t="n"/>
-      <c r="G82" s="36" t="n"/>
-      <c r="H82" s="36" t="n"/>
-      <c r="I82" s="36" t="n"/>
+      <c r="C82" s="69" t="n"/>
+      <c r="D82" s="69" t="n"/>
+      <c r="E82" s="69" t="n"/>
+      <c r="F82" s="69" t="n"/>
+      <c r="G82" s="69" t="n"/>
+      <c r="H82" s="69" t="n"/>
+      <c r="I82" s="69" t="n"/>
     </row>
     <row r="83">
-      <c r="B83" s="15" t="inlineStr">
+      <c r="B83" s="68" t="inlineStr">
         <is>
           <t>Feb/Mar_2021</t>
         </is>
       </c>
-      <c r="C83" s="36" t="n"/>
-      <c r="D83" s="43" t="n"/>
-      <c r="E83" s="43" t="n"/>
-      <c r="F83" s="43" t="n"/>
-      <c r="G83" s="43" t="n"/>
-      <c r="H83" s="43" t="n"/>
-      <c r="I83" s="43" t="n"/>
+      <c r="C83" s="69" t="n"/>
+      <c r="D83" s="69" t="n"/>
+      <c r="E83" s="69" t="n"/>
+      <c r="F83" s="69" t="n"/>
+      <c r="G83" s="69" t="n"/>
+      <c r="H83" s="69" t="n"/>
+      <c r="I83" s="69" t="n"/>
     </row>
     <row r="84" ht="15" customHeight="1" s="25">
-      <c r="B84" s="20" t="inlineStr">
+      <c r="B84" s="70" t="inlineStr">
         <is>
           <t>Feb/Mar_2022</t>
         </is>
       </c>
-      <c r="C84" s="46" t="n"/>
-      <c r="D84" s="46" t="n"/>
-      <c r="E84" s="46" t="n"/>
-      <c r="F84" s="46" t="n"/>
-      <c r="G84" s="46" t="n"/>
-      <c r="H84" s="46" t="n"/>
-      <c r="I84" s="46" t="n"/>
+      <c r="C84" s="69" t="n"/>
+      <c r="D84" s="69" t="n"/>
+      <c r="E84" s="69" t="n"/>
+      <c r="F84" s="69" t="n"/>
+      <c r="G84" s="69" t="n"/>
+      <c r="H84" s="69" t="n"/>
+      <c r="I84" s="69" t="n"/>
     </row>
     <row r="85" ht="15" customHeight="1" s="25"/>
     <row r="86" ht="15" customHeight="1" s="25">
@@ -8970,7 +8998,7 @@
           <t>Heat &amp; Temperature</t>
         </is>
       </c>
-      <c r="E87" s="67" t="inlineStr">
+      <c r="E87" s="12" t="inlineStr">
         <is>
           <t>Waves, Sound &amp; Light</t>
         </is>
@@ -8982,103 +9010,103 @@
       <c r="B88" s="64" t="n"/>
       <c r="C88" s="66" t="n"/>
       <c r="D88" s="66" t="n"/>
-      <c r="E88" s="65" t="n"/>
+      <c r="E88" s="66" t="n"/>
       <c r="F88" s="54" t="n"/>
       <c r="G88" s="54" t="n"/>
     </row>
     <row r="89">
-      <c r="B89" s="15" t="inlineStr">
+      <c r="B89" s="68" t="inlineStr">
         <is>
           <t>Feb/Mar_2015</t>
         </is>
       </c>
-      <c r="C89" s="36" t="n"/>
-      <c r="D89" s="36" t="n"/>
-      <c r="E89" s="36" t="n"/>
+      <c r="C89" s="69" t="n"/>
+      <c r="D89" s="69" t="n"/>
+      <c r="E89" s="69" t="n"/>
       <c r="F89" s="49" t="n"/>
       <c r="G89" s="49" t="n"/>
     </row>
     <row r="90">
-      <c r="B90" s="15" t="inlineStr">
+      <c r="B90" s="68" t="inlineStr">
         <is>
           <t>Feb/Mar_2016</t>
         </is>
       </c>
-      <c r="C90" s="40" t="n"/>
-      <c r="D90" s="40" t="n"/>
-      <c r="E90" s="40" t="n"/>
+      <c r="C90" s="69" t="n"/>
+      <c r="D90" s="69" t="n"/>
+      <c r="E90" s="69" t="n"/>
       <c r="F90" s="49" t="n"/>
       <c r="G90" s="49" t="n"/>
     </row>
     <row r="91">
-      <c r="B91" s="15" t="inlineStr">
+      <c r="B91" s="68" t="inlineStr">
         <is>
           <t>Feb/Mar_2017</t>
         </is>
       </c>
-      <c r="C91" s="36" t="n"/>
-      <c r="D91" s="36" t="n"/>
-      <c r="E91" s="36" t="n"/>
+      <c r="C91" s="69" t="n"/>
+      <c r="D91" s="69" t="n"/>
+      <c r="E91" s="69" t="n"/>
       <c r="F91" s="49" t="n"/>
       <c r="G91" s="49" t="n"/>
     </row>
     <row r="92">
-      <c r="B92" s="15" t="inlineStr">
+      <c r="B92" s="68" t="inlineStr">
         <is>
           <t>Feb/Mar_2018</t>
         </is>
       </c>
-      <c r="C92" s="36" t="n"/>
-      <c r="D92" s="36" t="n"/>
-      <c r="E92" s="36" t="n"/>
+      <c r="C92" s="69" t="n"/>
+      <c r="D92" s="69" t="n"/>
+      <c r="E92" s="69" t="n"/>
       <c r="F92" s="49" t="n"/>
       <c r="G92" s="49" t="n"/>
     </row>
     <row r="93">
-      <c r="B93" s="15" t="inlineStr">
+      <c r="B93" s="68" t="inlineStr">
         <is>
           <t>Feb/Mar_2019</t>
         </is>
       </c>
-      <c r="C93" s="36" t="n"/>
-      <c r="D93" s="36" t="n"/>
-      <c r="E93" s="36" t="n"/>
+      <c r="C93" s="69" t="n"/>
+      <c r="D93" s="69" t="n"/>
+      <c r="E93" s="69" t="n"/>
       <c r="F93" s="49" t="n"/>
       <c r="G93" s="49" t="n"/>
     </row>
     <row r="94">
-      <c r="B94" s="15" t="inlineStr">
+      <c r="B94" s="68" t="inlineStr">
         <is>
           <t>Feb/Mar_2020</t>
         </is>
       </c>
-      <c r="C94" s="36" t="n"/>
-      <c r="D94" s="36" t="n"/>
-      <c r="E94" s="36" t="n"/>
+      <c r="C94" s="69" t="n"/>
+      <c r="D94" s="69" t="n"/>
+      <c r="E94" s="69" t="n"/>
       <c r="F94" s="49" t="n"/>
       <c r="G94" s="49" t="n"/>
     </row>
     <row r="95">
-      <c r="B95" s="15" t="inlineStr">
+      <c r="B95" s="68" t="inlineStr">
         <is>
           <t>Feb/Mar_2021</t>
         </is>
       </c>
-      <c r="C95" s="43" t="n"/>
-      <c r="D95" s="43" t="n"/>
-      <c r="E95" s="43" t="n"/>
+      <c r="C95" s="69" t="n"/>
+      <c r="D95" s="69" t="n"/>
+      <c r="E95" s="69" t="n"/>
       <c r="F95" s="49" t="n"/>
       <c r="G95" s="49" t="n"/>
     </row>
     <row r="96" ht="15" customHeight="1" s="25">
-      <c r="B96" s="20" t="inlineStr">
+      <c r="B96" s="70" t="inlineStr">
         <is>
           <t>Feb/Mar_2022</t>
         </is>
       </c>
-      <c r="C96" s="46" t="n"/>
-      <c r="D96" s="46" t="n"/>
-      <c r="E96" s="46" t="n"/>
+      <c r="C96" s="69" t="n"/>
+      <c r="D96" s="69" t="n"/>
+      <c r="E96" s="69" t="n"/>
       <c r="F96" s="49" t="n"/>
       <c r="G96" s="49" t="n"/>
     </row>
@@ -9151,12 +9179,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="B1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.12844036697248" defaultRowHeight="14.25"/>
   <cols>
     <col width="16.7522935779816" customWidth="1" style="25" min="2" max="4"/>
+    <col width="13" customWidth="1" style="25" min="3" max="3"/>
+    <col width="13" customWidth="1" style="25" min="4" max="4"/>
     <col width="17.6238532110092" customWidth="1" style="25" min="5" max="5"/>
     <col width="16.7522935779816" customWidth="1" style="25" min="6" max="14"/>
+    <col width="13" customWidth="1" style="25" min="7" max="7"/>
+    <col width="13" customWidth="1" style="25" min="8" max="8"/>
+    <col width="13" customWidth="1" style="25" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="25"/>
@@ -9223,116 +9256,116 @@
       <c r="I4" s="66" t="n"/>
     </row>
     <row r="5">
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="68" t="inlineStr">
         <is>
           <t>Nov_2015</t>
         </is>
       </c>
-      <c r="C5" s="36" t="n"/>
-      <c r="D5" s="36" t="n"/>
-      <c r="E5" s="36" t="n"/>
-      <c r="F5" s="36" t="n"/>
-      <c r="G5" s="36" t="n"/>
-      <c r="H5" s="36" t="n"/>
-      <c r="I5" s="36" t="n"/>
+      <c r="C5" s="69" t="n"/>
+      <c r="D5" s="69" t="n"/>
+      <c r="E5" s="69" t="n"/>
+      <c r="F5" s="69" t="n"/>
+      <c r="G5" s="69" t="n"/>
+      <c r="H5" s="69" t="n"/>
+      <c r="I5" s="69" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="71" t="inlineStr">
         <is>
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C6" s="40" t="n"/>
-      <c r="D6" s="40" t="n"/>
-      <c r="E6" s="40" t="n"/>
-      <c r="F6" s="40" t="n"/>
-      <c r="G6" s="40" t="n"/>
-      <c r="H6" s="40" t="n"/>
-      <c r="I6" s="40" t="n"/>
+      <c r="C6" s="69" t="n"/>
+      <c r="D6" s="69" t="n"/>
+      <c r="E6" s="69" t="n"/>
+      <c r="F6" s="69" t="n"/>
+      <c r="G6" s="69" t="n"/>
+      <c r="H6" s="69" t="n"/>
+      <c r="I6" s="69" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="68" t="inlineStr">
         <is>
           <t>Nov_2017</t>
         </is>
       </c>
-      <c r="C7" s="36" t="n"/>
-      <c r="D7" s="36" t="n"/>
-      <c r="E7" s="36" t="n"/>
-      <c r="F7" s="36" t="n"/>
-      <c r="G7" s="36" t="n"/>
-      <c r="H7" s="36" t="n"/>
-      <c r="I7" s="36" t="n"/>
+      <c r="C7" s="69" t="n"/>
+      <c r="D7" s="69" t="n"/>
+      <c r="E7" s="69" t="n"/>
+      <c r="F7" s="69" t="n"/>
+      <c r="G7" s="69" t="n"/>
+      <c r="H7" s="69" t="n"/>
+      <c r="I7" s="69" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="68" t="inlineStr">
         <is>
           <t>Nov_2018</t>
         </is>
       </c>
-      <c r="C8" s="36" t="n"/>
-      <c r="D8" s="36" t="n"/>
-      <c r="E8" s="36" t="n"/>
-      <c r="F8" s="36" t="n"/>
-      <c r="G8" s="36" t="n"/>
-      <c r="H8" s="36" t="n"/>
-      <c r="I8" s="36" t="n"/>
+      <c r="C8" s="69" t="n"/>
+      <c r="D8" s="69" t="n"/>
+      <c r="E8" s="69" t="n"/>
+      <c r="F8" s="69" t="n"/>
+      <c r="G8" s="69" t="n"/>
+      <c r="H8" s="69" t="n"/>
+      <c r="I8" s="69" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="68" t="inlineStr">
         <is>
           <t>Nov_2019</t>
         </is>
       </c>
-      <c r="C9" s="36" t="n"/>
-      <c r="D9" s="36" t="n"/>
-      <c r="E9" s="36" t="n"/>
-      <c r="F9" s="36" t="n"/>
-      <c r="G9" s="36" t="n"/>
-      <c r="H9" s="36" t="n"/>
-      <c r="I9" s="36" t="n"/>
+      <c r="C9" s="69" t="n"/>
+      <c r="D9" s="69" t="n"/>
+      <c r="E9" s="69" t="n"/>
+      <c r="F9" s="69" t="n"/>
+      <c r="G9" s="69" t="n"/>
+      <c r="H9" s="69" t="n"/>
+      <c r="I9" s="69" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" s="68" t="inlineStr">
         <is>
           <t>Nov_2020</t>
         </is>
       </c>
-      <c r="C10" s="36" t="n"/>
-      <c r="D10" s="36" t="n"/>
-      <c r="E10" s="36" t="n"/>
-      <c r="F10" s="36" t="n"/>
-      <c r="G10" s="36" t="n"/>
-      <c r="H10" s="36" t="n"/>
-      <c r="I10" s="36" t="n"/>
+      <c r="C10" s="69" t="n"/>
+      <c r="D10" s="69" t="n"/>
+      <c r="E10" s="69" t="n"/>
+      <c r="F10" s="69" t="n"/>
+      <c r="G10" s="69" t="n"/>
+      <c r="H10" s="69" t="n"/>
+      <c r="I10" s="69" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="68" t="inlineStr">
         <is>
           <t>Nov_2021</t>
         </is>
       </c>
-      <c r="C11" s="36" t="n"/>
-      <c r="D11" s="43" t="n"/>
-      <c r="E11" s="43" t="n"/>
-      <c r="F11" s="43" t="n"/>
-      <c r="G11" s="43" t="n"/>
-      <c r="H11" s="43" t="n"/>
-      <c r="I11" s="43" t="n"/>
+      <c r="C11" s="69" t="n"/>
+      <c r="D11" s="69" t="n"/>
+      <c r="E11" s="69" t="n"/>
+      <c r="F11" s="69" t="n"/>
+      <c r="G11" s="69" t="n"/>
+      <c r="H11" s="69" t="n"/>
+      <c r="I11" s="69" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1" s="25">
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="70" t="inlineStr">
         <is>
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C12" s="46" t="n"/>
-      <c r="D12" s="46" t="n"/>
-      <c r="E12" s="46" t="n"/>
-      <c r="F12" s="46" t="n"/>
-      <c r="G12" s="46" t="n"/>
-      <c r="H12" s="46" t="n"/>
-      <c r="I12" s="46" t="n"/>
+      <c r="C12" s="69" t="n"/>
+      <c r="D12" s="69" t="n"/>
+      <c r="E12" s="69" t="n"/>
+      <c r="F12" s="69" t="n"/>
+      <c r="G12" s="69" t="n"/>
+      <c r="H12" s="69" t="n"/>
+      <c r="I12" s="69" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="25"/>
     <row r="14" ht="15" customHeight="1" s="25">
@@ -9360,7 +9393,7 @@
           <t>Heat &amp; Temperature</t>
         </is>
       </c>
-      <c r="E15" s="67" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>Waves, Sound &amp; Light</t>
         </is>
@@ -9373,131 +9406,128 @@
       <c r="B16" s="64" t="n"/>
       <c r="C16" s="66" t="n"/>
       <c r="D16" s="66" t="n"/>
-      <c r="E16" s="65" t="n"/>
+      <c r="E16" s="66" t="n"/>
       <c r="F16" s="51" t="n"/>
       <c r="G16" s="51" t="n"/>
       <c r="H16" s="51" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" s="68" t="inlineStr">
         <is>
           <t>Nov_2015</t>
         </is>
       </c>
-      <c r="C17" s="36" t="n"/>
-      <c r="D17" s="36" t="n"/>
-      <c r="E17" s="36" t="n"/>
+      <c r="C17" s="69" t="n"/>
+      <c r="D17" s="69" t="n"/>
+      <c r="E17" s="69" t="n"/>
       <c r="F17" s="51" t="n"/>
       <c r="G17" s="51" t="n"/>
       <c r="H17" s="51" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="71" t="inlineStr">
         <is>
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C18" s="40" t="n"/>
-      <c r="D18" s="40" t="n"/>
-      <c r="E18" s="40" t="n"/>
+      <c r="C18" s="69" t="n"/>
+      <c r="D18" s="69" t="n"/>
+      <c r="E18" s="69" t="n"/>
       <c r="F18" s="51" t="n"/>
       <c r="G18" s="51" t="n"/>
       <c r="H18" s="51" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="68" t="inlineStr">
         <is>
           <t>Nov_2017</t>
         </is>
       </c>
-      <c r="C19" s="36" t="n"/>
-      <c r="D19" s="36" t="n"/>
-      <c r="E19" s="36" t="n"/>
+      <c r="C19" s="69" t="n"/>
+      <c r="D19" s="69" t="n"/>
+      <c r="E19" s="69" t="n"/>
       <c r="F19" s="51" t="n"/>
       <c r="G19" s="51" t="n"/>
       <c r="H19" s="51" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="68" t="inlineStr">
         <is>
           <t>Nov_2018</t>
         </is>
       </c>
-      <c r="C20" s="36" t="n"/>
-      <c r="D20" s="36" t="n"/>
-      <c r="E20" s="36" t="n"/>
+      <c r="C20" s="69" t="n"/>
+      <c r="D20" s="69" t="n"/>
+      <c r="E20" s="69" t="n"/>
       <c r="F20" s="51" t="n"/>
       <c r="G20" s="51" t="n"/>
       <c r="H20" s="51" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="68" t="inlineStr">
         <is>
           <t>Nov_2019</t>
         </is>
       </c>
-      <c r="C21" s="36" t="n"/>
-      <c r="D21" s="36" t="n"/>
-      <c r="E21" s="36" t="n"/>
+      <c r="C21" s="69" t="n"/>
+      <c r="D21" s="69" t="n"/>
+      <c r="E21" s="69" t="n"/>
       <c r="F21" s="51" t="n"/>
       <c r="G21" s="51" t="n"/>
       <c r="H21" s="51" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B22" s="68" t="inlineStr">
         <is>
           <t>Nov_2020</t>
         </is>
       </c>
-      <c r="C22" s="36" t="n"/>
-      <c r="D22" s="36" t="n"/>
-      <c r="E22" s="36" t="n"/>
+      <c r="C22" s="69" t="n"/>
+      <c r="D22" s="69" t="n"/>
+      <c r="E22" s="69" t="n"/>
       <c r="F22" s="51" t="n"/>
       <c r="G22" s="51" t="n"/>
       <c r="H22" s="51" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B23" s="68" t="inlineStr">
         <is>
           <t>Nov_2021</t>
         </is>
       </c>
-      <c r="C23" s="43" t="n"/>
-      <c r="D23" s="43" t="n"/>
-      <c r="E23" s="43" t="n"/>
+      <c r="C23" s="69" t="n"/>
+      <c r="D23" s="69" t="n"/>
+      <c r="E23" s="69" t="n"/>
       <c r="F23" s="51" t="n"/>
       <c r="G23" s="51" t="n"/>
       <c r="H23" s="51" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1" s="25">
-      <c r="B24" s="20" t="inlineStr">
+      <c r="B24" s="70" t="inlineStr">
         <is>
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C24" s="46" t="n"/>
-      <c r="D24" s="46" t="n"/>
-      <c r="E24" s="46" t="n"/>
+      <c r="C24" s="69" t="n"/>
+      <c r="D24" s="69" t="n"/>
+      <c r="E24" s="69" t="n"/>
       <c r="F24" s="51" t="n"/>
       <c r="G24" s="51" t="n"/>
       <c r="H24" s="51" t="n"/>
     </row>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="D15:D16"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="B2:I2"/>
+    <mergeCell ref="G3:G4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="E3:E4"/>
-    <mergeCell ref="G3:G4"/>
     <mergeCell ref="H3:H4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E15:E16"/>
     <mergeCell ref="C15:C16"/>
-    <mergeCell ref="E15:E16"/>
     <mergeCell ref="I3:I4"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="B14:E14"/>
@@ -9512,7 +9542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K98"/>
+  <dimension ref="B1:K96"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.12844036697248" defaultRowHeight="14.25"/>
   <cols>
     <col width="9.12844036697248" customWidth="1" style="25" min="1" max="1"/>
@@ -9523,6 +9553,7 @@
     <col width="19.7522935779816" customWidth="1" style="3" min="6" max="6"/>
     <col width="23" customWidth="1" style="3" min="7" max="7"/>
     <col width="16.6238532110092" customWidth="1" style="3" min="8" max="25"/>
+    <col width="13" customWidth="1" style="25" min="9" max="9"/>
     <col width="9.12844036697248" customWidth="1" style="25" min="26" max="16384"/>
   </cols>
   <sheetData>
@@ -9617,13 +9648,13 @@
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C6" s="40" t="n"/>
-      <c r="D6" s="40" t="n"/>
-      <c r="E6" s="40" t="n"/>
-      <c r="F6" s="40" t="n"/>
-      <c r="G6" s="40" t="n"/>
-      <c r="H6" s="40" t="n"/>
-      <c r="I6" s="40" t="n"/>
+      <c r="C6" s="36" t="n"/>
+      <c r="D6" s="36" t="n"/>
+      <c r="E6" s="36" t="n"/>
+      <c r="F6" s="36" t="n"/>
+      <c r="G6" s="36" t="n"/>
+      <c r="H6" s="36" t="n"/>
+      <c r="I6" s="36" t="n"/>
       <c r="J6" s="51" t="n"/>
       <c r="K6" s="51" t="n"/>
     </row>
@@ -9698,12 +9729,12 @@
         </is>
       </c>
       <c r="C11" s="36" t="n"/>
-      <c r="D11" s="43" t="n"/>
-      <c r="E11" s="43" t="n"/>
-      <c r="F11" s="43" t="n"/>
-      <c r="G11" s="43" t="n"/>
-      <c r="H11" s="43" t="n"/>
-      <c r="I11" s="43" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="36" t="n"/>
+      <c r="F11" s="36" t="n"/>
+      <c r="G11" s="36" t="n"/>
+      <c r="H11" s="36" t="n"/>
+      <c r="I11" s="36" t="n"/>
       <c r="J11" s="51" t="n"/>
       <c r="K11" s="51" t="n"/>
     </row>
@@ -9713,13 +9744,13 @@
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C12" s="46" t="n"/>
-      <c r="D12" s="46" t="n"/>
-      <c r="E12" s="46" t="n"/>
-      <c r="F12" s="46" t="n"/>
-      <c r="G12" s="46" t="n"/>
-      <c r="H12" s="46" t="n"/>
-      <c r="I12" s="46" t="n"/>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="36" t="n"/>
+      <c r="F12" s="36" t="n"/>
+      <c r="G12" s="36" t="n"/>
+      <c r="H12" s="36" t="n"/>
+      <c r="I12" s="36" t="n"/>
       <c r="J12" s="51" t="n"/>
       <c r="K12" s="51" t="n"/>
     </row>
@@ -9754,7 +9785,7 @@
           <t>Heat &amp; Temperature</t>
         </is>
       </c>
-      <c r="E15" s="67" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>Waves, Sound &amp; Light</t>
         </is>
@@ -9769,7 +9800,7 @@
       <c r="B16" s="64" t="n"/>
       <c r="C16" s="66" t="n"/>
       <c r="D16" s="66" t="n"/>
-      <c r="E16" s="65" t="n"/>
+      <c r="E16" s="66" t="n"/>
       <c r="F16" s="51" t="n"/>
       <c r="G16" s="51" t="n"/>
       <c r="H16" s="51" t="n"/>
@@ -9797,9 +9828,9 @@
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C18" s="40" t="n"/>
-      <c r="D18" s="40" t="n"/>
-      <c r="E18" s="40" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
       <c r="F18" s="51" t="n"/>
       <c r="G18" s="51" t="n"/>
       <c r="H18" s="51" t="n"/>
@@ -9872,9 +9903,9 @@
           <t>Nov_2021</t>
         </is>
       </c>
-      <c r="C23" s="43" t="n"/>
-      <c r="D23" s="43" t="n"/>
-      <c r="E23" s="43" t="n"/>
+      <c r="C23" s="36" t="n"/>
+      <c r="D23" s="36" t="n"/>
+      <c r="E23" s="36" t="n"/>
       <c r="F23" s="51" t="n"/>
       <c r="G23" s="51" t="n"/>
       <c r="H23" s="51" t="n"/>
@@ -9887,9 +9918,9 @@
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C24" s="46" t="n"/>
-      <c r="D24" s="46" t="n"/>
-      <c r="E24" s="46" t="n"/>
+      <c r="C24" s="36" t="n"/>
+      <c r="D24" s="36" t="n"/>
+      <c r="E24" s="36" t="n"/>
       <c r="F24" s="51" t="n"/>
       <c r="G24" s="51" t="n"/>
       <c r="H24" s="51" t="n"/>
@@ -9990,13 +10021,13 @@
           <t>Sept_2016</t>
         </is>
       </c>
-      <c r="C30" s="40" t="n"/>
-      <c r="D30" s="40" t="n"/>
-      <c r="E30" s="40" t="n"/>
-      <c r="F30" s="40" t="n"/>
-      <c r="G30" s="40" t="n"/>
-      <c r="H30" s="40" t="n"/>
-      <c r="I30" s="40" t="n"/>
+      <c r="C30" s="36" t="n"/>
+      <c r="D30" s="36" t="n"/>
+      <c r="E30" s="36" t="n"/>
+      <c r="F30" s="36" t="n"/>
+      <c r="G30" s="36" t="n"/>
+      <c r="H30" s="36" t="n"/>
+      <c r="I30" s="36" t="n"/>
       <c r="J30" s="51" t="n"/>
       <c r="K30" s="51" t="n"/>
     </row>
@@ -10071,12 +10102,12 @@
         </is>
       </c>
       <c r="C35" s="36" t="n"/>
-      <c r="D35" s="43" t="n"/>
-      <c r="E35" s="43" t="n"/>
-      <c r="F35" s="43" t="n"/>
-      <c r="G35" s="43" t="n"/>
-      <c r="H35" s="43" t="n"/>
-      <c r="I35" s="43" t="n"/>
+      <c r="D35" s="36" t="n"/>
+      <c r="E35" s="36" t="n"/>
+      <c r="F35" s="36" t="n"/>
+      <c r="G35" s="36" t="n"/>
+      <c r="H35" s="36" t="n"/>
+      <c r="I35" s="36" t="n"/>
       <c r="J35" s="51" t="n"/>
       <c r="K35" s="51" t="n"/>
     </row>
@@ -10086,13 +10117,13 @@
           <t>Sept_2022</t>
         </is>
       </c>
-      <c r="C36" s="46" t="n"/>
-      <c r="D36" s="46" t="n"/>
-      <c r="E36" s="46" t="n"/>
-      <c r="F36" s="46" t="n"/>
-      <c r="G36" s="46" t="n"/>
-      <c r="H36" s="46" t="n"/>
-      <c r="I36" s="46" t="n"/>
+      <c r="C36" s="36" t="n"/>
+      <c r="D36" s="36" t="n"/>
+      <c r="E36" s="36" t="n"/>
+      <c r="F36" s="36" t="n"/>
+      <c r="G36" s="36" t="n"/>
+      <c r="H36" s="36" t="n"/>
+      <c r="I36" s="36" t="n"/>
       <c r="J36" s="51" t="n"/>
       <c r="K36" s="51" t="n"/>
     </row>
@@ -10126,7 +10157,7 @@
           <t>Heat &amp; Temperature</t>
         </is>
       </c>
-      <c r="E39" s="67" t="inlineStr">
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>Waves, Sound &amp; Light</t>
         </is>
@@ -10140,7 +10171,7 @@
       <c r="B40" s="64" t="n"/>
       <c r="C40" s="66" t="n"/>
       <c r="D40" s="66" t="n"/>
-      <c r="E40" s="65" t="n"/>
+      <c r="E40" s="66" t="n"/>
       <c r="F40" s="54" t="n"/>
       <c r="G40" s="54" t="n"/>
       <c r="J40" s="51" t="n"/>
@@ -10166,9 +10197,9 @@
           <t>Sept_2016</t>
         </is>
       </c>
-      <c r="C42" s="40" t="n"/>
-      <c r="D42" s="40" t="n"/>
-      <c r="E42" s="40" t="n"/>
+      <c r="C42" s="36" t="n"/>
+      <c r="D42" s="36" t="n"/>
+      <c r="E42" s="36" t="n"/>
       <c r="F42" s="49" t="n"/>
       <c r="G42" s="49" t="n"/>
       <c r="J42" s="51" t="n"/>
@@ -10236,9 +10267,9 @@
           <t>Sept_2021</t>
         </is>
       </c>
-      <c r="C47" s="43" t="n"/>
-      <c r="D47" s="43" t="n"/>
-      <c r="E47" s="43" t="n"/>
+      <c r="C47" s="36" t="n"/>
+      <c r="D47" s="36" t="n"/>
+      <c r="E47" s="36" t="n"/>
       <c r="F47" s="49" t="n"/>
       <c r="G47" s="49" t="n"/>
       <c r="J47" s="51" t="n"/>
@@ -10250,9 +10281,9 @@
           <t>Sept_2022</t>
         </is>
       </c>
-      <c r="C48" s="46" t="n"/>
-      <c r="D48" s="46" t="n"/>
-      <c r="E48" s="46" t="n"/>
+      <c r="C48" s="36" t="n"/>
+      <c r="D48" s="36" t="n"/>
+      <c r="E48" s="36" t="n"/>
       <c r="F48" s="49" t="n"/>
       <c r="G48" s="49" t="n"/>
       <c r="J48" s="51" t="n"/>
@@ -10352,13 +10383,13 @@
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C54" s="40" t="n"/>
-      <c r="D54" s="40" t="n"/>
-      <c r="E54" s="40" t="n"/>
-      <c r="F54" s="40" t="n"/>
-      <c r="G54" s="40" t="n"/>
-      <c r="H54" s="40" t="n"/>
-      <c r="I54" s="40" t="n"/>
+      <c r="C54" s="36" t="n"/>
+      <c r="D54" s="36" t="n"/>
+      <c r="E54" s="36" t="n"/>
+      <c r="F54" s="36" t="n"/>
+      <c r="G54" s="36" t="n"/>
+      <c r="H54" s="36" t="n"/>
+      <c r="I54" s="36" t="n"/>
       <c r="J54" s="51" t="n"/>
       <c r="K54" s="51" t="n"/>
     </row>
@@ -10411,18 +10442,18 @@
       <c r="K57" s="51" t="n"/>
     </row>
     <row r="58">
-      <c r="B58" s="15" t="inlineStr">
+      <c r="B58" s="68" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C58" s="36" t="n"/>
-      <c r="D58" s="36" t="n"/>
-      <c r="E58" s="36" t="n"/>
-      <c r="F58" s="36" t="n"/>
-      <c r="G58" s="36" t="n"/>
-      <c r="H58" s="36" t="n"/>
-      <c r="I58" s="36" t="n"/>
+      <c r="C58" s="69" t="n"/>
+      <c r="D58" s="69" t="n"/>
+      <c r="E58" s="69" t="n"/>
+      <c r="F58" s="69" t="n"/>
+      <c r="G58" s="69" t="n"/>
+      <c r="H58" s="69" t="n"/>
+      <c r="I58" s="69" t="n"/>
       <c r="J58" s="51" t="n"/>
       <c r="K58" s="51" t="n"/>
     </row>
@@ -10433,12 +10464,12 @@
         </is>
       </c>
       <c r="C59" s="36" t="n"/>
-      <c r="D59" s="43" t="n"/>
-      <c r="E59" s="43" t="n"/>
-      <c r="F59" s="43" t="n"/>
-      <c r="G59" s="43" t="n"/>
-      <c r="H59" s="43" t="n"/>
-      <c r="I59" s="43" t="n"/>
+      <c r="D59" s="36" t="n"/>
+      <c r="E59" s="36" t="n"/>
+      <c r="F59" s="36" t="n"/>
+      <c r="G59" s="36" t="n"/>
+      <c r="H59" s="36" t="n"/>
+      <c r="I59" s="36" t="n"/>
       <c r="J59" s="51" t="n"/>
       <c r="K59" s="51" t="n"/>
     </row>
@@ -10448,13 +10479,13 @@
           <t>May/Jun_2022</t>
         </is>
       </c>
-      <c r="C60" s="46" t="n"/>
-      <c r="D60" s="46" t="n"/>
-      <c r="E60" s="46" t="n"/>
-      <c r="F60" s="46" t="n"/>
-      <c r="G60" s="46" t="n"/>
-      <c r="H60" s="46" t="n"/>
-      <c r="I60" s="46" t="n"/>
+      <c r="C60" s="36" t="n"/>
+      <c r="D60" s="36" t="n"/>
+      <c r="E60" s="36" t="n"/>
+      <c r="F60" s="36" t="n"/>
+      <c r="G60" s="36" t="n"/>
+      <c r="H60" s="36" t="n"/>
+      <c r="I60" s="36" t="n"/>
       <c r="J60" s="51" t="n"/>
       <c r="K60" s="51" t="n"/>
     </row>
@@ -10488,7 +10519,7 @@
           <t>Heat &amp; Temperature</t>
         </is>
       </c>
-      <c r="E63" s="67" t="inlineStr">
+      <c r="E63" s="12" t="inlineStr">
         <is>
           <t>Waves, Sound &amp; Light</t>
         </is>
@@ -10502,7 +10533,7 @@
       <c r="B64" s="64" t="n"/>
       <c r="C64" s="66" t="n"/>
       <c r="D64" s="66" t="n"/>
-      <c r="E64" s="65" t="n"/>
+      <c r="E64" s="66" t="n"/>
       <c r="F64" s="54" t="n"/>
       <c r="G64" s="54" t="n"/>
       <c r="J64" s="51" t="n"/>
@@ -10528,9 +10559,9 @@
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C66" s="40" t="n"/>
-      <c r="D66" s="40" t="n"/>
-      <c r="E66" s="40" t="n"/>
+      <c r="C66" s="36" t="n"/>
+      <c r="D66" s="36" t="n"/>
+      <c r="E66" s="36" t="n"/>
       <c r="F66" s="49" t="n"/>
       <c r="G66" s="49" t="n"/>
       <c r="J66" s="51" t="n"/>
@@ -10579,14 +10610,14 @@
       <c r="K69" s="51" t="n"/>
     </row>
     <row r="70">
-      <c r="B70" s="15" t="inlineStr">
+      <c r="B70" s="68" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C70" s="36" t="n"/>
-      <c r="D70" s="36" t="n"/>
-      <c r="E70" s="36" t="n"/>
+      <c r="C70" s="69" t="n"/>
+      <c r="D70" s="69" t="n"/>
+      <c r="E70" s="69" t="n"/>
       <c r="F70" s="49" t="n"/>
       <c r="G70" s="49" t="n"/>
       <c r="J70" s="51" t="n"/>
@@ -10598,9 +10629,9 @@
           <t>May/Jun_2021</t>
         </is>
       </c>
-      <c r="C71" s="43" t="n"/>
-      <c r="D71" s="43" t="n"/>
-      <c r="E71" s="43" t="n"/>
+      <c r="C71" s="36" t="n"/>
+      <c r="D71" s="36" t="n"/>
+      <c r="E71" s="36" t="n"/>
       <c r="F71" s="49" t="n"/>
       <c r="G71" s="49" t="n"/>
       <c r="J71" s="51" t="n"/>
@@ -10612,9 +10643,9 @@
           <t>May/Jun_2022</t>
         </is>
       </c>
-      <c r="C72" s="46" t="n"/>
-      <c r="D72" s="46" t="n"/>
-      <c r="E72" s="46" t="n"/>
+      <c r="C72" s="36" t="n"/>
+      <c r="D72" s="36" t="n"/>
+      <c r="E72" s="36" t="n"/>
       <c r="F72" s="49" t="n"/>
       <c r="G72" s="49" t="n"/>
       <c r="J72" s="51" t="n"/>
@@ -10714,13 +10745,13 @@
           <t>Feb/Mar_2016</t>
         </is>
       </c>
-      <c r="C78" s="40" t="n"/>
-      <c r="D78" s="40" t="n"/>
-      <c r="E78" s="40" t="n"/>
-      <c r="F78" s="40" t="n"/>
-      <c r="G78" s="40" t="n"/>
-      <c r="H78" s="40" t="n"/>
-      <c r="I78" s="40" t="n"/>
+      <c r="C78" s="36" t="n"/>
+      <c r="D78" s="36" t="n"/>
+      <c r="E78" s="36" t="n"/>
+      <c r="F78" s="36" t="n"/>
+      <c r="G78" s="36" t="n"/>
+      <c r="H78" s="36" t="n"/>
+      <c r="I78" s="36" t="n"/>
       <c r="J78" s="51" t="n"/>
       <c r="K78" s="51" t="n"/>
     </row>
@@ -10795,12 +10826,12 @@
         </is>
       </c>
       <c r="C83" s="36" t="n"/>
-      <c r="D83" s="43" t="n"/>
-      <c r="E83" s="43" t="n"/>
-      <c r="F83" s="43" t="n"/>
-      <c r="G83" s="43" t="n"/>
-      <c r="H83" s="43" t="n"/>
-      <c r="I83" s="43" t="n"/>
+      <c r="D83" s="36" t="n"/>
+      <c r="E83" s="36" t="n"/>
+      <c r="F83" s="36" t="n"/>
+      <c r="G83" s="36" t="n"/>
+      <c r="H83" s="36" t="n"/>
+      <c r="I83" s="36" t="n"/>
       <c r="J83" s="51" t="n"/>
       <c r="K83" s="51" t="n"/>
     </row>
@@ -10810,13 +10841,13 @@
           <t>Feb/Mar_2022</t>
         </is>
       </c>
-      <c r="C84" s="46" t="n"/>
-      <c r="D84" s="46" t="n"/>
-      <c r="E84" s="46" t="n"/>
-      <c r="F84" s="46" t="n"/>
-      <c r="G84" s="46" t="n"/>
-      <c r="H84" s="46" t="n"/>
-      <c r="I84" s="46" t="n"/>
+      <c r="C84" s="36" t="n"/>
+      <c r="D84" s="36" t="n"/>
+      <c r="E84" s="36" t="n"/>
+      <c r="F84" s="36" t="n"/>
+      <c r="G84" s="36" t="n"/>
+      <c r="H84" s="36" t="n"/>
+      <c r="I84" s="36" t="n"/>
       <c r="J84" s="51" t="n"/>
       <c r="K84" s="51" t="n"/>
     </row>
@@ -10850,7 +10881,7 @@
           <t>Heat &amp; Temperature</t>
         </is>
       </c>
-      <c r="E87" s="67" t="inlineStr">
+      <c r="E87" s="12" t="inlineStr">
         <is>
           <t>Waves, Sound &amp; Light</t>
         </is>
@@ -10864,7 +10895,7 @@
       <c r="B88" s="64" t="n"/>
       <c r="C88" s="66" t="n"/>
       <c r="D88" s="66" t="n"/>
-      <c r="E88" s="65" t="n"/>
+      <c r="E88" s="66" t="n"/>
       <c r="F88" s="54" t="n"/>
       <c r="G88" s="54" t="n"/>
       <c r="J88" s="51" t="n"/>
@@ -10890,9 +10921,9 @@
           <t>Feb/Mar_2016</t>
         </is>
       </c>
-      <c r="C90" s="40" t="n"/>
-      <c r="D90" s="40" t="n"/>
-      <c r="E90" s="40" t="n"/>
+      <c r="C90" s="36" t="n"/>
+      <c r="D90" s="36" t="n"/>
+      <c r="E90" s="36" t="n"/>
       <c r="F90" s="49" t="n"/>
       <c r="G90" s="49" t="n"/>
       <c r="J90" s="51" t="n"/>
@@ -10960,9 +10991,9 @@
           <t>Feb/Mar_2021</t>
         </is>
       </c>
-      <c r="C95" s="43" t="n"/>
-      <c r="D95" s="43" t="n"/>
-      <c r="E95" s="43" t="n"/>
+      <c r="C95" s="36" t="n"/>
+      <c r="D95" s="36" t="n"/>
+      <c r="E95" s="36" t="n"/>
       <c r="F95" s="49" t="n"/>
       <c r="G95" s="49" t="n"/>
       <c r="J95" s="51" t="n"/>
@@ -10974,16 +11005,14 @@
           <t>Feb/Mar_2022</t>
         </is>
       </c>
-      <c r="C96" s="46" t="n"/>
-      <c r="D96" s="46" t="n"/>
-      <c r="E96" s="46" t="n"/>
+      <c r="C96" s="36" t="n"/>
+      <c r="D96" s="36" t="n"/>
+      <c r="E96" s="36" t="n"/>
       <c r="F96" s="49" t="n"/>
       <c r="G96" s="49" t="n"/>
       <c r="J96" s="51" t="n"/>
       <c r="K96" s="51" t="n"/>
     </row>
-    <row r="97"/>
-    <row r="98"/>
   </sheetData>
   <mergeCells count="56">
     <mergeCell ref="B27:B28"/>
@@ -11053,11 +11082,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K99"/>
+  <dimension ref="B1:K99"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.12844036697248" defaultRowHeight="14.25"/>
   <cols>
     <col width="9.12844036697248" customWidth="1" style="25" min="1" max="1"/>
     <col width="16.6238532110092" customWidth="1" style="3" min="2" max="25"/>
+    <col width="13" customWidth="1" style="25" min="3" max="3"/>
+    <col width="13" customWidth="1" style="25" min="4" max="4"/>
+    <col width="13" customWidth="1" style="25" min="5" max="5"/>
+    <col width="13" customWidth="1" style="25" min="6" max="6"/>
+    <col width="13" customWidth="1" style="25" min="7" max="7"/>
+    <col width="13" customWidth="1" style="25" min="8" max="8"/>
+    <col width="13" customWidth="1" style="25" min="9" max="9"/>
     <col width="9.12844036697248" customWidth="1" style="25" min="26" max="16384"/>
   </cols>
   <sheetData>
@@ -11152,13 +11188,13 @@
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C6" s="40" t="n"/>
-      <c r="D6" s="40" t="n"/>
-      <c r="E6" s="40" t="n"/>
-      <c r="F6" s="40" t="n"/>
-      <c r="G6" s="40" t="n"/>
-      <c r="H6" s="40" t="n"/>
-      <c r="I6" s="40" t="n"/>
+      <c r="C6" s="36" t="n"/>
+      <c r="D6" s="36" t="n"/>
+      <c r="E6" s="36" t="n"/>
+      <c r="F6" s="36" t="n"/>
+      <c r="G6" s="36" t="n"/>
+      <c r="H6" s="36" t="n"/>
+      <c r="I6" s="36" t="n"/>
       <c r="J6" s="51" t="n"/>
       <c r="K6" s="51" t="n"/>
     </row>
@@ -11233,12 +11269,12 @@
         </is>
       </c>
       <c r="C11" s="36" t="n"/>
-      <c r="D11" s="43" t="n"/>
-      <c r="E11" s="43" t="n"/>
-      <c r="F11" s="43" t="n"/>
-      <c r="G11" s="43" t="n"/>
-      <c r="H11" s="43" t="n"/>
-      <c r="I11" s="43" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="36" t="n"/>
+      <c r="F11" s="36" t="n"/>
+      <c r="G11" s="36" t="n"/>
+      <c r="H11" s="36" t="n"/>
+      <c r="I11" s="36" t="n"/>
       <c r="J11" s="51" t="n"/>
       <c r="K11" s="51" t="n"/>
     </row>
@@ -11248,13 +11284,13 @@
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C12" s="46" t="n"/>
-      <c r="D12" s="46" t="n"/>
-      <c r="E12" s="46" t="n"/>
-      <c r="F12" s="46" t="n"/>
-      <c r="G12" s="46" t="n"/>
-      <c r="H12" s="46" t="n"/>
-      <c r="I12" s="46" t="n"/>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="36" t="n"/>
+      <c r="F12" s="36" t="n"/>
+      <c r="G12" s="36" t="n"/>
+      <c r="H12" s="36" t="n"/>
+      <c r="I12" s="36" t="n"/>
       <c r="J12" s="51" t="n"/>
       <c r="K12" s="51" t="n"/>
     </row>
@@ -11289,7 +11325,7 @@
           <t>Heat &amp; Temperature</t>
         </is>
       </c>
-      <c r="E15" s="67" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>Waves, Sound &amp; Light</t>
         </is>
@@ -11304,7 +11340,7 @@
       <c r="B16" s="64" t="n"/>
       <c r="C16" s="66" t="n"/>
       <c r="D16" s="66" t="n"/>
-      <c r="E16" s="65" t="n"/>
+      <c r="E16" s="66" t="n"/>
       <c r="F16" s="51" t="n"/>
       <c r="G16" s="51" t="n"/>
       <c r="H16" s="51" t="n"/>
@@ -11332,9 +11368,9 @@
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C18" s="40" t="n"/>
-      <c r="D18" s="40" t="n"/>
-      <c r="E18" s="40" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
       <c r="F18" s="51" t="n"/>
       <c r="G18" s="51" t="n"/>
       <c r="H18" s="51" t="n"/>
@@ -11407,9 +11443,9 @@
           <t>Nov_2021</t>
         </is>
       </c>
-      <c r="C23" s="43" t="n"/>
-      <c r="D23" s="43" t="n"/>
-      <c r="E23" s="43" t="n"/>
+      <c r="C23" s="36" t="n"/>
+      <c r="D23" s="36" t="n"/>
+      <c r="E23" s="36" t="n"/>
       <c r="F23" s="51" t="n"/>
       <c r="G23" s="51" t="n"/>
       <c r="H23" s="51" t="n"/>
@@ -11422,9 +11458,9 @@
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C24" s="46" t="n"/>
-      <c r="D24" s="46" t="n"/>
-      <c r="E24" s="46" t="n"/>
+      <c r="C24" s="36" t="n"/>
+      <c r="D24" s="36" t="n"/>
+      <c r="E24" s="36" t="n"/>
       <c r="F24" s="51" t="n"/>
       <c r="G24" s="51" t="n"/>
       <c r="H24" s="51" t="n"/>
@@ -11525,13 +11561,13 @@
           <t>Sept_2016</t>
         </is>
       </c>
-      <c r="C30" s="40" t="n"/>
-      <c r="D30" s="40" t="n"/>
-      <c r="E30" s="40" t="n"/>
-      <c r="F30" s="40" t="n"/>
-      <c r="G30" s="40" t="n"/>
-      <c r="H30" s="40" t="n"/>
-      <c r="I30" s="40" t="n"/>
+      <c r="C30" s="36" t="n"/>
+      <c r="D30" s="36" t="n"/>
+      <c r="E30" s="36" t="n"/>
+      <c r="F30" s="36" t="n"/>
+      <c r="G30" s="36" t="n"/>
+      <c r="H30" s="36" t="n"/>
+      <c r="I30" s="36" t="n"/>
       <c r="J30" s="51" t="n"/>
       <c r="K30" s="51" t="n"/>
     </row>
@@ -11606,12 +11642,12 @@
         </is>
       </c>
       <c r="C35" s="36" t="n"/>
-      <c r="D35" s="43" t="n"/>
-      <c r="E35" s="43" t="n"/>
-      <c r="F35" s="43" t="n"/>
-      <c r="G35" s="43" t="n"/>
-      <c r="H35" s="43" t="n"/>
-      <c r="I35" s="43" t="n"/>
+      <c r="D35" s="36" t="n"/>
+      <c r="E35" s="36" t="n"/>
+      <c r="F35" s="36" t="n"/>
+      <c r="G35" s="36" t="n"/>
+      <c r="H35" s="36" t="n"/>
+      <c r="I35" s="36" t="n"/>
       <c r="J35" s="51" t="n"/>
       <c r="K35" s="51" t="n"/>
     </row>
@@ -11621,13 +11657,13 @@
           <t>Sept_2022</t>
         </is>
       </c>
-      <c r="C36" s="46" t="n"/>
-      <c r="D36" s="46" t="n"/>
-      <c r="E36" s="46" t="n"/>
-      <c r="F36" s="46" t="n"/>
-      <c r="G36" s="46" t="n"/>
-      <c r="H36" s="46" t="n"/>
-      <c r="I36" s="46" t="n"/>
+      <c r="C36" s="36" t="n"/>
+      <c r="D36" s="36" t="n"/>
+      <c r="E36" s="36" t="n"/>
+      <c r="F36" s="36" t="n"/>
+      <c r="G36" s="36" t="n"/>
+      <c r="H36" s="36" t="n"/>
+      <c r="I36" s="36" t="n"/>
       <c r="J36" s="51" t="n"/>
       <c r="K36" s="51" t="n"/>
     </row>
@@ -11661,7 +11697,7 @@
           <t>Heat &amp; Temperature</t>
         </is>
       </c>
-      <c r="E39" s="67" t="inlineStr">
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>Waves, Sound &amp; Light</t>
         </is>
@@ -11675,7 +11711,7 @@
       <c r="B40" s="64" t="n"/>
       <c r="C40" s="66" t="n"/>
       <c r="D40" s="66" t="n"/>
-      <c r="E40" s="65" t="n"/>
+      <c r="E40" s="66" t="n"/>
       <c r="F40" s="54" t="n"/>
       <c r="G40" s="54" t="n"/>
       <c r="J40" s="51" t="n"/>
@@ -11701,9 +11737,9 @@
           <t>Sept_2016</t>
         </is>
       </c>
-      <c r="C42" s="40" t="n"/>
-      <c r="D42" s="40" t="n"/>
-      <c r="E42" s="40" t="n"/>
+      <c r="C42" s="36" t="n"/>
+      <c r="D42" s="36" t="n"/>
+      <c r="E42" s="36" t="n"/>
       <c r="F42" s="49" t="n"/>
       <c r="G42" s="49" t="n"/>
       <c r="J42" s="51" t="n"/>
@@ -11771,9 +11807,9 @@
           <t>Sept_2021</t>
         </is>
       </c>
-      <c r="C47" s="43" t="n"/>
-      <c r="D47" s="43" t="n"/>
-      <c r="E47" s="43" t="n"/>
+      <c r="C47" s="36" t="n"/>
+      <c r="D47" s="36" t="n"/>
+      <c r="E47" s="36" t="n"/>
       <c r="F47" s="49" t="n"/>
       <c r="G47" s="49" t="n"/>
       <c r="J47" s="51" t="n"/>
@@ -11785,9 +11821,9 @@
           <t>Sept_2022</t>
         </is>
       </c>
-      <c r="C48" s="46" t="n"/>
-      <c r="D48" s="46" t="n"/>
-      <c r="E48" s="46" t="n"/>
+      <c r="C48" s="36" t="n"/>
+      <c r="D48" s="36" t="n"/>
+      <c r="E48" s="36" t="n"/>
       <c r="F48" s="49" t="n"/>
       <c r="G48" s="49" t="n"/>
       <c r="J48" s="51" t="n"/>
@@ -11887,13 +11923,13 @@
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C54" s="40" t="n"/>
-      <c r="D54" s="40" t="n"/>
-      <c r="E54" s="40" t="n"/>
-      <c r="F54" s="40" t="n"/>
-      <c r="G54" s="40" t="n"/>
-      <c r="H54" s="40" t="n"/>
-      <c r="I54" s="40" t="n"/>
+      <c r="C54" s="36" t="n"/>
+      <c r="D54" s="36" t="n"/>
+      <c r="E54" s="36" t="n"/>
+      <c r="F54" s="36" t="n"/>
+      <c r="G54" s="36" t="n"/>
+      <c r="H54" s="36" t="n"/>
+      <c r="I54" s="36" t="n"/>
       <c r="J54" s="51" t="n"/>
       <c r="K54" s="51" t="n"/>
     </row>
@@ -11946,18 +11982,18 @@
       <c r="K57" s="51" t="n"/>
     </row>
     <row r="58">
-      <c r="B58" s="15" t="inlineStr">
+      <c r="B58" s="68" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C58" s="36" t="n"/>
-      <c r="D58" s="36" t="n"/>
-      <c r="E58" s="36" t="n"/>
-      <c r="F58" s="36" t="n"/>
-      <c r="G58" s="36" t="n"/>
-      <c r="H58" s="36" t="n"/>
-      <c r="I58" s="36" t="n"/>
+      <c r="C58" s="69" t="n"/>
+      <c r="D58" s="69" t="n"/>
+      <c r="E58" s="69" t="n"/>
+      <c r="F58" s="69" t="n"/>
+      <c r="G58" s="69" t="n"/>
+      <c r="H58" s="69" t="n"/>
+      <c r="I58" s="69" t="n"/>
       <c r="J58" s="51" t="n"/>
       <c r="K58" s="51" t="n"/>
     </row>
@@ -11968,12 +12004,12 @@
         </is>
       </c>
       <c r="C59" s="36" t="n"/>
-      <c r="D59" s="43" t="n"/>
-      <c r="E59" s="43" t="n"/>
-      <c r="F59" s="43" t="n"/>
-      <c r="G59" s="43" t="n"/>
-      <c r="H59" s="43" t="n"/>
-      <c r="I59" s="43" t="n"/>
+      <c r="D59" s="36" t="n"/>
+      <c r="E59" s="36" t="n"/>
+      <c r="F59" s="36" t="n"/>
+      <c r="G59" s="36" t="n"/>
+      <c r="H59" s="36" t="n"/>
+      <c r="I59" s="36" t="n"/>
       <c r="J59" s="51" t="n"/>
       <c r="K59" s="51" t="n"/>
     </row>
@@ -11983,13 +12019,13 @@
           <t>May/Jun_2022</t>
         </is>
       </c>
-      <c r="C60" s="46" t="n"/>
-      <c r="D60" s="46" t="n"/>
-      <c r="E60" s="46" t="n"/>
-      <c r="F60" s="46" t="n"/>
-      <c r="G60" s="46" t="n"/>
-      <c r="H60" s="46" t="n"/>
-      <c r="I60" s="46" t="n"/>
+      <c r="C60" s="36" t="n"/>
+      <c r="D60" s="36" t="n"/>
+      <c r="E60" s="36" t="n"/>
+      <c r="F60" s="36" t="n"/>
+      <c r="G60" s="36" t="n"/>
+      <c r="H60" s="36" t="n"/>
+      <c r="I60" s="36" t="n"/>
       <c r="J60" s="51" t="n"/>
       <c r="K60" s="51" t="n"/>
     </row>
@@ -12023,7 +12059,7 @@
           <t>Heat &amp; Temperature</t>
         </is>
       </c>
-      <c r="E63" s="67" t="inlineStr">
+      <c r="E63" s="12" t="inlineStr">
         <is>
           <t>Waves, Sound &amp; Light</t>
         </is>
@@ -12037,7 +12073,7 @@
       <c r="B64" s="64" t="n"/>
       <c r="C64" s="66" t="n"/>
       <c r="D64" s="66" t="n"/>
-      <c r="E64" s="65" t="n"/>
+      <c r="E64" s="66" t="n"/>
       <c r="F64" s="54" t="n"/>
       <c r="G64" s="54" t="n"/>
       <c r="J64" s="51" t="n"/>
@@ -12063,9 +12099,9 @@
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C66" s="40" t="n"/>
-      <c r="D66" s="40" t="n"/>
-      <c r="E66" s="40" t="n"/>
+      <c r="C66" s="36" t="n"/>
+      <c r="D66" s="36" t="n"/>
+      <c r="E66" s="36" t="n"/>
       <c r="F66" s="49" t="n"/>
       <c r="G66" s="49" t="n"/>
       <c r="J66" s="51" t="n"/>
@@ -12114,14 +12150,14 @@
       <c r="K69" s="51" t="n"/>
     </row>
     <row r="70">
-      <c r="B70" s="15" t="inlineStr">
+      <c r="B70" s="68" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C70" s="36" t="n"/>
-      <c r="D70" s="36" t="n"/>
-      <c r="E70" s="36" t="n"/>
+      <c r="C70" s="69" t="n"/>
+      <c r="D70" s="69" t="n"/>
+      <c r="E70" s="69" t="n"/>
       <c r="F70" s="49" t="n"/>
       <c r="G70" s="49" t="n"/>
       <c r="J70" s="51" t="n"/>
@@ -12133,9 +12169,9 @@
           <t>May/Jun_2021</t>
         </is>
       </c>
-      <c r="C71" s="43" t="n"/>
-      <c r="D71" s="43" t="n"/>
-      <c r="E71" s="43" t="n"/>
+      <c r="C71" s="36" t="n"/>
+      <c r="D71" s="36" t="n"/>
+      <c r="E71" s="36" t="n"/>
       <c r="F71" s="49" t="n"/>
       <c r="G71" s="49" t="n"/>
       <c r="J71" s="51" t="n"/>
@@ -12147,9 +12183,9 @@
           <t>May/Jun_2022</t>
         </is>
       </c>
-      <c r="C72" s="46" t="n"/>
-      <c r="D72" s="46" t="n"/>
-      <c r="E72" s="46" t="n"/>
+      <c r="C72" s="36" t="n"/>
+      <c r="D72" s="36" t="n"/>
+      <c r="E72" s="36" t="n"/>
       <c r="F72" s="49" t="n"/>
       <c r="G72" s="49" t="n"/>
       <c r="J72" s="51" t="n"/>
@@ -12249,13 +12285,13 @@
           <t>Feb/Mar_2016</t>
         </is>
       </c>
-      <c r="C78" s="40" t="n"/>
-      <c r="D78" s="40" t="n"/>
-      <c r="E78" s="40" t="n"/>
-      <c r="F78" s="40" t="n"/>
-      <c r="G78" s="40" t="n"/>
-      <c r="H78" s="40" t="n"/>
-      <c r="I78" s="40" t="n"/>
+      <c r="C78" s="36" t="n"/>
+      <c r="D78" s="36" t="n"/>
+      <c r="E78" s="36" t="n"/>
+      <c r="F78" s="36" t="n"/>
+      <c r="G78" s="36" t="n"/>
+      <c r="H78" s="36" t="n"/>
+      <c r="I78" s="36" t="n"/>
       <c r="J78" s="51" t="n"/>
       <c r="K78" s="51" t="n"/>
     </row>
@@ -12330,12 +12366,12 @@
         </is>
       </c>
       <c r="C83" s="36" t="n"/>
-      <c r="D83" s="43" t="n"/>
-      <c r="E83" s="43" t="n"/>
-      <c r="F83" s="43" t="n"/>
-      <c r="G83" s="43" t="n"/>
-      <c r="H83" s="43" t="n"/>
-      <c r="I83" s="43" t="n"/>
+      <c r="D83" s="36" t="n"/>
+      <c r="E83" s="36" t="n"/>
+      <c r="F83" s="36" t="n"/>
+      <c r="G83" s="36" t="n"/>
+      <c r="H83" s="36" t="n"/>
+      <c r="I83" s="36" t="n"/>
       <c r="J83" s="51" t="n"/>
       <c r="K83" s="51" t="n"/>
     </row>
@@ -12345,13 +12381,13 @@
           <t>Feb/Mar_2022</t>
         </is>
       </c>
-      <c r="C84" s="46" t="n"/>
-      <c r="D84" s="46" t="n"/>
-      <c r="E84" s="46" t="n"/>
-      <c r="F84" s="46" t="n"/>
-      <c r="G84" s="46" t="n"/>
-      <c r="H84" s="46" t="n"/>
-      <c r="I84" s="46" t="n"/>
+      <c r="C84" s="36" t="n"/>
+      <c r="D84" s="36" t="n"/>
+      <c r="E84" s="36" t="n"/>
+      <c r="F84" s="36" t="n"/>
+      <c r="G84" s="36" t="n"/>
+      <c r="H84" s="36" t="n"/>
+      <c r="I84" s="36" t="n"/>
       <c r="J84" s="51" t="n"/>
       <c r="K84" s="51" t="n"/>
     </row>
@@ -12385,7 +12421,7 @@
           <t>Heat &amp; Temperature</t>
         </is>
       </c>
-      <c r="E87" s="67" t="inlineStr">
+      <c r="E87" s="12" t="inlineStr">
         <is>
           <t>Waves, Sound &amp; Light</t>
         </is>
@@ -12399,7 +12435,7 @@
       <c r="B88" s="64" t="n"/>
       <c r="C88" s="66" t="n"/>
       <c r="D88" s="66" t="n"/>
-      <c r="E88" s="65" t="n"/>
+      <c r="E88" s="66" t="n"/>
       <c r="F88" s="54" t="n"/>
       <c r="G88" s="54" t="n"/>
       <c r="J88" s="51" t="n"/>
@@ -12425,9 +12461,9 @@
           <t>Feb/Mar_2016</t>
         </is>
       </c>
-      <c r="C90" s="40" t="n"/>
-      <c r="D90" s="40" t="n"/>
-      <c r="E90" s="40" t="n"/>
+      <c r="C90" s="36" t="n"/>
+      <c r="D90" s="36" t="n"/>
+      <c r="E90" s="36" t="n"/>
       <c r="F90" s="49" t="n"/>
       <c r="G90" s="49" t="n"/>
       <c r="J90" s="51" t="n"/>
@@ -12495,9 +12531,9 @@
           <t>Feb/Mar_2021</t>
         </is>
       </c>
-      <c r="C95" s="43" t="n"/>
-      <c r="D95" s="43" t="n"/>
-      <c r="E95" s="43" t="n"/>
+      <c r="C95" s="36" t="n"/>
+      <c r="D95" s="36" t="n"/>
+      <c r="E95" s="36" t="n"/>
       <c r="F95" s="49" t="n"/>
       <c r="G95" s="49" t="n"/>
       <c r="J95" s="51" t="n"/>
@@ -12509,9 +12545,9 @@
           <t>Feb/Mar_2022</t>
         </is>
       </c>
-      <c r="C96" s="46" t="n"/>
-      <c r="D96" s="46" t="n"/>
-      <c r="E96" s="46" t="n"/>
+      <c r="C96" s="36" t="n"/>
+      <c r="D96" s="36" t="n"/>
+      <c r="E96" s="36" t="n"/>
       <c r="F96" s="49" t="n"/>
       <c r="G96" s="49" t="n"/>
       <c r="J96" s="51" t="n"/>
@@ -12608,11 +12644,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K98"/>
+  <dimension ref="B1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.12844036697248" defaultRowHeight="14.25"/>
   <cols>
     <col width="9.12844036697248" customWidth="1" style="25" min="1" max="1"/>
     <col width="16.6238532110092" customWidth="1" style="3" min="2" max="25"/>
+    <col width="13" customWidth="1" style="25" min="3" max="3"/>
+    <col width="13" customWidth="1" style="25" min="4" max="4"/>
+    <col width="13" customWidth="1" style="25" min="5" max="5"/>
+    <col width="13" customWidth="1" style="25" min="6" max="6"/>
+    <col width="13" customWidth="1" style="25" min="7" max="7"/>
+    <col width="13" customWidth="1" style="25" min="8" max="8"/>
+    <col width="13" customWidth="1" style="25" min="9" max="9"/>
     <col width="9.12844036697248" customWidth="1" style="25" min="26" max="16384"/>
   </cols>
   <sheetData>
@@ -12707,13 +12750,13 @@
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C6" s="40" t="n"/>
-      <c r="D6" s="40" t="n"/>
-      <c r="E6" s="40" t="n"/>
-      <c r="F6" s="40" t="n"/>
-      <c r="G6" s="40" t="n"/>
-      <c r="H6" s="40" t="n"/>
-      <c r="I6" s="40" t="n"/>
+      <c r="C6" s="36" t="n"/>
+      <c r="D6" s="36" t="n"/>
+      <c r="E6" s="36" t="n"/>
+      <c r="F6" s="36" t="n"/>
+      <c r="G6" s="36" t="n"/>
+      <c r="H6" s="36" t="n"/>
+      <c r="I6" s="36" t="n"/>
       <c r="J6" s="51" t="n"/>
       <c r="K6" s="51" t="n"/>
     </row>
@@ -12788,12 +12831,12 @@
         </is>
       </c>
       <c r="C11" s="36" t="n"/>
-      <c r="D11" s="43" t="n"/>
-      <c r="E11" s="43" t="n"/>
-      <c r="F11" s="43" t="n"/>
-      <c r="G11" s="43" t="n"/>
-      <c r="H11" s="43" t="n"/>
-      <c r="I11" s="43" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="36" t="n"/>
+      <c r="F11" s="36" t="n"/>
+      <c r="G11" s="36" t="n"/>
+      <c r="H11" s="36" t="n"/>
+      <c r="I11" s="36" t="n"/>
       <c r="J11" s="51" t="n"/>
       <c r="K11" s="51" t="n"/>
     </row>
@@ -12803,13 +12846,13 @@
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C12" s="46" t="n"/>
-      <c r="D12" s="46" t="n"/>
-      <c r="E12" s="46" t="n"/>
-      <c r="F12" s="46" t="n"/>
-      <c r="G12" s="46" t="n"/>
-      <c r="H12" s="46" t="n"/>
-      <c r="I12" s="46" t="n"/>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="36" t="n"/>
+      <c r="F12" s="36" t="n"/>
+      <c r="G12" s="36" t="n"/>
+      <c r="H12" s="36" t="n"/>
+      <c r="I12" s="36" t="n"/>
       <c r="J12" s="51" t="n"/>
       <c r="K12" s="51" t="n"/>
     </row>
@@ -12844,7 +12887,7 @@
           <t>Heat &amp; Temperature</t>
         </is>
       </c>
-      <c r="E15" s="67" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>Waves, Sound &amp; Light</t>
         </is>
@@ -12859,7 +12902,7 @@
       <c r="B16" s="64" t="n"/>
       <c r="C16" s="66" t="n"/>
       <c r="D16" s="66" t="n"/>
-      <c r="E16" s="65" t="n"/>
+      <c r="E16" s="66" t="n"/>
       <c r="F16" s="51" t="n"/>
       <c r="G16" s="51" t="n"/>
       <c r="H16" s="51" t="n"/>
@@ -12887,9 +12930,9 @@
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C18" s="40" t="n"/>
-      <c r="D18" s="40" t="n"/>
-      <c r="E18" s="40" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
       <c r="F18" s="51" t="n"/>
       <c r="G18" s="51" t="n"/>
       <c r="H18" s="51" t="n"/>
@@ -12962,9 +13005,9 @@
           <t>Nov_2021</t>
         </is>
       </c>
-      <c r="C23" s="43" t="n"/>
-      <c r="D23" s="43" t="n"/>
-      <c r="E23" s="43" t="n"/>
+      <c r="C23" s="36" t="n"/>
+      <c r="D23" s="36" t="n"/>
+      <c r="E23" s="36" t="n"/>
       <c r="F23" s="51" t="n"/>
       <c r="G23" s="51" t="n"/>
       <c r="H23" s="51" t="n"/>
@@ -12977,9 +13020,9 @@
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C24" s="46" t="n"/>
-      <c r="D24" s="46" t="n"/>
-      <c r="E24" s="46" t="n"/>
+      <c r="C24" s="36" t="n"/>
+      <c r="D24" s="36" t="n"/>
+      <c r="E24" s="36" t="n"/>
       <c r="F24" s="51" t="n"/>
       <c r="G24" s="51" t="n"/>
       <c r="H24" s="51" t="n"/>
@@ -13080,13 +13123,13 @@
           <t>Sept_2016</t>
         </is>
       </c>
-      <c r="C30" s="40" t="n"/>
-      <c r="D30" s="40" t="n"/>
-      <c r="E30" s="40" t="n"/>
-      <c r="F30" s="40" t="n"/>
-      <c r="G30" s="40" t="n"/>
-      <c r="H30" s="40" t="n"/>
-      <c r="I30" s="40" t="n"/>
+      <c r="C30" s="36" t="n"/>
+      <c r="D30" s="36" t="n"/>
+      <c r="E30" s="36" t="n"/>
+      <c r="F30" s="36" t="n"/>
+      <c r="G30" s="36" t="n"/>
+      <c r="H30" s="36" t="n"/>
+      <c r="I30" s="36" t="n"/>
       <c r="J30" s="51" t="n"/>
       <c r="K30" s="51" t="n"/>
     </row>
@@ -13161,12 +13204,12 @@
         </is>
       </c>
       <c r="C35" s="36" t="n"/>
-      <c r="D35" s="43" t="n"/>
-      <c r="E35" s="43" t="n"/>
-      <c r="F35" s="43" t="n"/>
-      <c r="G35" s="43" t="n"/>
-      <c r="H35" s="43" t="n"/>
-      <c r="I35" s="43" t="n"/>
+      <c r="D35" s="36" t="n"/>
+      <c r="E35" s="36" t="n"/>
+      <c r="F35" s="36" t="n"/>
+      <c r="G35" s="36" t="n"/>
+      <c r="H35" s="36" t="n"/>
+      <c r="I35" s="36" t="n"/>
       <c r="J35" s="51" t="n"/>
       <c r="K35" s="51" t="n"/>
     </row>
@@ -13176,13 +13219,13 @@
           <t>Sept_2022</t>
         </is>
       </c>
-      <c r="C36" s="46" t="n"/>
-      <c r="D36" s="46" t="n"/>
-      <c r="E36" s="46" t="n"/>
-      <c r="F36" s="46" t="n"/>
-      <c r="G36" s="46" t="n"/>
-      <c r="H36" s="46" t="n"/>
-      <c r="I36" s="46" t="n"/>
+      <c r="C36" s="36" t="n"/>
+      <c r="D36" s="36" t="n"/>
+      <c r="E36" s="36" t="n"/>
+      <c r="F36" s="36" t="n"/>
+      <c r="G36" s="36" t="n"/>
+      <c r="H36" s="36" t="n"/>
+      <c r="I36" s="36" t="n"/>
       <c r="J36" s="51" t="n"/>
       <c r="K36" s="51" t="n"/>
     </row>
@@ -13216,7 +13259,7 @@
           <t>Heat &amp; Temperature</t>
         </is>
       </c>
-      <c r="E39" s="67" t="inlineStr">
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>Waves, Sound &amp; Light</t>
         </is>
@@ -13230,7 +13273,7 @@
       <c r="B40" s="64" t="n"/>
       <c r="C40" s="66" t="n"/>
       <c r="D40" s="66" t="n"/>
-      <c r="E40" s="65" t="n"/>
+      <c r="E40" s="66" t="n"/>
       <c r="F40" s="54" t="n"/>
       <c r="G40" s="54" t="n"/>
       <c r="J40" s="51" t="n"/>
@@ -13256,9 +13299,9 @@
           <t>Sept_2016</t>
         </is>
       </c>
-      <c r="C42" s="40" t="n"/>
-      <c r="D42" s="40" t="n"/>
-      <c r="E42" s="40" t="n"/>
+      <c r="C42" s="36" t="n"/>
+      <c r="D42" s="36" t="n"/>
+      <c r="E42" s="36" t="n"/>
       <c r="F42" s="49" t="n"/>
       <c r="G42" s="49" t="n"/>
       <c r="J42" s="51" t="n"/>
@@ -13326,9 +13369,9 @@
           <t>Sept_2021</t>
         </is>
       </c>
-      <c r="C47" s="43" t="n"/>
-      <c r="D47" s="43" t="n"/>
-      <c r="E47" s="43" t="n"/>
+      <c r="C47" s="36" t="n"/>
+      <c r="D47" s="36" t="n"/>
+      <c r="E47" s="36" t="n"/>
       <c r="F47" s="49" t="n"/>
       <c r="G47" s="49" t="n"/>
       <c r="J47" s="51" t="n"/>
@@ -13340,9 +13383,9 @@
           <t>Sept_2022</t>
         </is>
       </c>
-      <c r="C48" s="46" t="n"/>
-      <c r="D48" s="46" t="n"/>
-      <c r="E48" s="46" t="n"/>
+      <c r="C48" s="36" t="n"/>
+      <c r="D48" s="36" t="n"/>
+      <c r="E48" s="36" t="n"/>
       <c r="F48" s="49" t="n"/>
       <c r="G48" s="49" t="n"/>
       <c r="J48" s="51" t="n"/>
@@ -13442,13 +13485,13 @@
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C54" s="40" t="n"/>
-      <c r="D54" s="40" t="n"/>
-      <c r="E54" s="40" t="n"/>
-      <c r="F54" s="40" t="n"/>
-      <c r="G54" s="40" t="n"/>
-      <c r="H54" s="40" t="n"/>
-      <c r="I54" s="40" t="n"/>
+      <c r="C54" s="36" t="n"/>
+      <c r="D54" s="36" t="n"/>
+      <c r="E54" s="36" t="n"/>
+      <c r="F54" s="36" t="n"/>
+      <c r="G54" s="36" t="n"/>
+      <c r="H54" s="36" t="n"/>
+      <c r="I54" s="36" t="n"/>
       <c r="J54" s="51" t="n"/>
       <c r="K54" s="51" t="n"/>
     </row>
@@ -13501,18 +13544,18 @@
       <c r="K57" s="51" t="n"/>
     </row>
     <row r="58">
-      <c r="B58" s="15" t="inlineStr">
+      <c r="B58" s="68" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C58" s="36" t="n"/>
-      <c r="D58" s="36" t="n"/>
-      <c r="E58" s="36" t="n"/>
-      <c r="F58" s="36" t="n"/>
-      <c r="G58" s="36" t="n"/>
-      <c r="H58" s="36" t="n"/>
-      <c r="I58" s="36" t="n"/>
+      <c r="C58" s="69" t="n"/>
+      <c r="D58" s="69" t="n"/>
+      <c r="E58" s="69" t="n"/>
+      <c r="F58" s="69" t="n"/>
+      <c r="G58" s="69" t="n"/>
+      <c r="H58" s="69" t="n"/>
+      <c r="I58" s="69" t="n"/>
       <c r="J58" s="51" t="n"/>
       <c r="K58" s="51" t="n"/>
     </row>
@@ -13523,12 +13566,12 @@
         </is>
       </c>
       <c r="C59" s="36" t="n"/>
-      <c r="D59" s="43" t="n"/>
-      <c r="E59" s="43" t="n"/>
-      <c r="F59" s="43" t="n"/>
-      <c r="G59" s="43" t="n"/>
-      <c r="H59" s="43" t="n"/>
-      <c r="I59" s="43" t="n"/>
+      <c r="D59" s="36" t="n"/>
+      <c r="E59" s="36" t="n"/>
+      <c r="F59" s="36" t="n"/>
+      <c r="G59" s="36" t="n"/>
+      <c r="H59" s="36" t="n"/>
+      <c r="I59" s="36" t="n"/>
       <c r="J59" s="51" t="n"/>
       <c r="K59" s="51" t="n"/>
     </row>
@@ -13538,13 +13581,13 @@
           <t>May/Jun_2022</t>
         </is>
       </c>
-      <c r="C60" s="46" t="n"/>
-      <c r="D60" s="46" t="n"/>
-      <c r="E60" s="46" t="n"/>
-      <c r="F60" s="46" t="n"/>
-      <c r="G60" s="46" t="n"/>
-      <c r="H60" s="46" t="n"/>
-      <c r="I60" s="46" t="n"/>
+      <c r="C60" s="36" t="n"/>
+      <c r="D60" s="36" t="n"/>
+      <c r="E60" s="36" t="n"/>
+      <c r="F60" s="36" t="n"/>
+      <c r="G60" s="36" t="n"/>
+      <c r="H60" s="36" t="n"/>
+      <c r="I60" s="36" t="n"/>
       <c r="J60" s="51" t="n"/>
       <c r="K60" s="51" t="n"/>
     </row>
@@ -13578,7 +13621,7 @@
           <t>Heat &amp; Temperature</t>
         </is>
       </c>
-      <c r="E63" s="67" t="inlineStr">
+      <c r="E63" s="12" t="inlineStr">
         <is>
           <t>Waves, Sound &amp; Light</t>
         </is>
@@ -13592,7 +13635,7 @@
       <c r="B64" s="64" t="n"/>
       <c r="C64" s="66" t="n"/>
       <c r="D64" s="66" t="n"/>
-      <c r="E64" s="65" t="n"/>
+      <c r="E64" s="66" t="n"/>
       <c r="F64" s="54" t="n"/>
       <c r="G64" s="54" t="n"/>
       <c r="J64" s="51" t="n"/>
@@ -13618,9 +13661,9 @@
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C66" s="40" t="n"/>
-      <c r="D66" s="40" t="n"/>
-      <c r="E66" s="40" t="n"/>
+      <c r="C66" s="36" t="n"/>
+      <c r="D66" s="36" t="n"/>
+      <c r="E66" s="36" t="n"/>
       <c r="F66" s="49" t="n"/>
       <c r="G66" s="49" t="n"/>
       <c r="J66" s="51" t="n"/>
@@ -13669,14 +13712,14 @@
       <c r="K69" s="51" t="n"/>
     </row>
     <row r="70">
-      <c r="B70" s="15" t="inlineStr">
+      <c r="B70" s="68" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C70" s="36" t="n"/>
-      <c r="D70" s="36" t="n"/>
-      <c r="E70" s="36" t="n"/>
+      <c r="C70" s="69" t="n"/>
+      <c r="D70" s="69" t="n"/>
+      <c r="E70" s="69" t="n"/>
       <c r="F70" s="49" t="n"/>
       <c r="G70" s="49" t="n"/>
       <c r="J70" s="51" t="n"/>
@@ -13688,9 +13731,9 @@
           <t>May/Jun_2021</t>
         </is>
       </c>
-      <c r="C71" s="43" t="n"/>
-      <c r="D71" s="43" t="n"/>
-      <c r="E71" s="43" t="n"/>
+      <c r="C71" s="36" t="n"/>
+      <c r="D71" s="36" t="n"/>
+      <c r="E71" s="36" t="n"/>
       <c r="F71" s="49" t="n"/>
       <c r="G71" s="49" t="n"/>
       <c r="J71" s="51" t="n"/>
@@ -13702,9 +13745,9 @@
           <t>May/Jun_2022</t>
         </is>
       </c>
-      <c r="C72" s="46" t="n"/>
-      <c r="D72" s="46" t="n"/>
-      <c r="E72" s="46" t="n"/>
+      <c r="C72" s="36" t="n"/>
+      <c r="D72" s="36" t="n"/>
+      <c r="E72" s="36" t="n"/>
       <c r="F72" s="49" t="n"/>
       <c r="G72" s="49" t="n"/>
       <c r="J72" s="51" t="n"/>
@@ -13804,13 +13847,13 @@
           <t>Feb/Mar_2016</t>
         </is>
       </c>
-      <c r="C78" s="40" t="n"/>
-      <c r="D78" s="40" t="n"/>
-      <c r="E78" s="40" t="n"/>
-      <c r="F78" s="40" t="n"/>
-      <c r="G78" s="40" t="n"/>
-      <c r="H78" s="40" t="n"/>
-      <c r="I78" s="40" t="n"/>
+      <c r="C78" s="36" t="n"/>
+      <c r="D78" s="36" t="n"/>
+      <c r="E78" s="36" t="n"/>
+      <c r="F78" s="36" t="n"/>
+      <c r="G78" s="36" t="n"/>
+      <c r="H78" s="36" t="n"/>
+      <c r="I78" s="36" t="n"/>
       <c r="J78" s="51" t="n"/>
       <c r="K78" s="51" t="n"/>
     </row>
@@ -13885,12 +13928,12 @@
         </is>
       </c>
       <c r="C83" s="36" t="n"/>
-      <c r="D83" s="43" t="n"/>
-      <c r="E83" s="43" t="n"/>
-      <c r="F83" s="43" t="n"/>
-      <c r="G83" s="43" t="n"/>
-      <c r="H83" s="43" t="n"/>
-      <c r="I83" s="43" t="n"/>
+      <c r="D83" s="36" t="n"/>
+      <c r="E83" s="36" t="n"/>
+      <c r="F83" s="36" t="n"/>
+      <c r="G83" s="36" t="n"/>
+      <c r="H83" s="36" t="n"/>
+      <c r="I83" s="36" t="n"/>
       <c r="J83" s="51" t="n"/>
       <c r="K83" s="51" t="n"/>
     </row>
@@ -13900,13 +13943,13 @@
           <t>Feb/Mar_2022</t>
         </is>
       </c>
-      <c r="C84" s="46" t="n"/>
-      <c r="D84" s="46" t="n"/>
-      <c r="E84" s="46" t="n"/>
-      <c r="F84" s="46" t="n"/>
-      <c r="G84" s="46" t="n"/>
-      <c r="H84" s="46" t="n"/>
-      <c r="I84" s="46" t="n"/>
+      <c r="C84" s="36" t="n"/>
+      <c r="D84" s="36" t="n"/>
+      <c r="E84" s="36" t="n"/>
+      <c r="F84" s="36" t="n"/>
+      <c r="G84" s="36" t="n"/>
+      <c r="H84" s="36" t="n"/>
+      <c r="I84" s="36" t="n"/>
       <c r="J84" s="51" t="n"/>
       <c r="K84" s="51" t="n"/>
     </row>
@@ -13940,7 +13983,7 @@
           <t>Heat &amp; Temperature</t>
         </is>
       </c>
-      <c r="E87" s="67" t="inlineStr">
+      <c r="E87" s="12" t="inlineStr">
         <is>
           <t>Waves, Sound &amp; Light</t>
         </is>
@@ -13954,7 +13997,7 @@
       <c r="B88" s="64" t="n"/>
       <c r="C88" s="66" t="n"/>
       <c r="D88" s="66" t="n"/>
-      <c r="E88" s="65" t="n"/>
+      <c r="E88" s="66" t="n"/>
       <c r="F88" s="54" t="n"/>
       <c r="G88" s="54" t="n"/>
       <c r="J88" s="51" t="n"/>
@@ -13980,9 +14023,9 @@
           <t>Feb/Mar_2016</t>
         </is>
       </c>
-      <c r="C90" s="40" t="n"/>
-      <c r="D90" s="40" t="n"/>
-      <c r="E90" s="40" t="n"/>
+      <c r="C90" s="36" t="n"/>
+      <c r="D90" s="36" t="n"/>
+      <c r="E90" s="36" t="n"/>
       <c r="F90" s="49" t="n"/>
       <c r="G90" s="49" t="n"/>
       <c r="J90" s="51" t="n"/>
@@ -14050,9 +14093,9 @@
           <t>Feb/Mar_2021</t>
         </is>
       </c>
-      <c r="C95" s="43" t="n"/>
-      <c r="D95" s="43" t="n"/>
-      <c r="E95" s="43" t="n"/>
+      <c r="C95" s="36" t="n"/>
+      <c r="D95" s="36" t="n"/>
+      <c r="E95" s="36" t="n"/>
       <c r="F95" s="49" t="n"/>
       <c r="G95" s="49" t="n"/>
       <c r="J95" s="51" t="n"/>
@@ -14064,9 +14107,9 @@
           <t>Feb/Mar_2022</t>
         </is>
       </c>
-      <c r="C96" s="46" t="n"/>
-      <c r="D96" s="46" t="n"/>
-      <c r="E96" s="46" t="n"/>
+      <c r="C96" s="36" t="n"/>
+      <c r="D96" s="36" t="n"/>
+      <c r="E96" s="36" t="n"/>
       <c r="F96" s="49" t="n"/>
       <c r="G96" s="49" t="n"/>
       <c r="J96" s="51" t="n"/>
@@ -14151,11 +14194,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K98"/>
+  <dimension ref="B1:K97"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.12844036697248" defaultRowHeight="14.25"/>
   <cols>
     <col width="9.12844036697248" customWidth="1" style="25" min="1" max="1"/>
     <col width="16.6238532110092" customWidth="1" style="3" min="2" max="25"/>
+    <col width="13" customWidth="1" style="25" min="3" max="3"/>
+    <col width="13" customWidth="1" style="25" min="4" max="4"/>
+    <col width="13" customWidth="1" style="25" min="5" max="5"/>
+    <col width="13" customWidth="1" style="25" min="6" max="6"/>
+    <col width="13" customWidth="1" style="25" min="7" max="7"/>
+    <col width="13" customWidth="1" style="25" min="8" max="8"/>
+    <col width="13" customWidth="1" style="25" min="9" max="9"/>
     <col width="9.12844036697248" customWidth="1" style="25" min="26" max="16384"/>
   </cols>
   <sheetData>
@@ -14250,13 +14300,13 @@
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C6" s="40" t="n"/>
-      <c r="D6" s="40" t="n"/>
-      <c r="E6" s="40" t="n"/>
-      <c r="F6" s="40" t="n"/>
-      <c r="G6" s="40" t="n"/>
-      <c r="H6" s="40" t="n"/>
-      <c r="I6" s="40" t="n"/>
+      <c r="C6" s="36" t="n"/>
+      <c r="D6" s="36" t="n"/>
+      <c r="E6" s="36" t="n"/>
+      <c r="F6" s="36" t="n"/>
+      <c r="G6" s="36" t="n"/>
+      <c r="H6" s="36" t="n"/>
+      <c r="I6" s="36" t="n"/>
       <c r="J6" s="51" t="n"/>
       <c r="K6" s="51" t="n"/>
     </row>
@@ -14331,12 +14381,12 @@
         </is>
       </c>
       <c r="C11" s="36" t="n"/>
-      <c r="D11" s="43" t="n"/>
-      <c r="E11" s="43" t="n"/>
-      <c r="F11" s="43" t="n"/>
-      <c r="G11" s="43" t="n"/>
-      <c r="H11" s="43" t="n"/>
-      <c r="I11" s="43" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="36" t="n"/>
+      <c r="F11" s="36" t="n"/>
+      <c r="G11" s="36" t="n"/>
+      <c r="H11" s="36" t="n"/>
+      <c r="I11" s="36" t="n"/>
       <c r="J11" s="51" t="n"/>
       <c r="K11" s="51" t="n"/>
     </row>
@@ -14346,13 +14396,13 @@
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C12" s="46" t="n"/>
-      <c r="D12" s="46" t="n"/>
-      <c r="E12" s="46" t="n"/>
-      <c r="F12" s="46" t="n"/>
-      <c r="G12" s="46" t="n"/>
-      <c r="H12" s="46" t="n"/>
-      <c r="I12" s="46" t="n"/>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="36" t="n"/>
+      <c r="F12" s="36" t="n"/>
+      <c r="G12" s="36" t="n"/>
+      <c r="H12" s="36" t="n"/>
+      <c r="I12" s="36" t="n"/>
       <c r="J12" s="51" t="n"/>
       <c r="K12" s="51" t="n"/>
     </row>
@@ -14387,7 +14437,7 @@
           <t>Heat &amp; Temperature</t>
         </is>
       </c>
-      <c r="E15" s="67" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>Waves, Sound &amp; Light</t>
         </is>
@@ -14402,7 +14452,7 @@
       <c r="B16" s="64" t="n"/>
       <c r="C16" s="66" t="n"/>
       <c r="D16" s="66" t="n"/>
-      <c r="E16" s="65" t="n"/>
+      <c r="E16" s="66" t="n"/>
       <c r="F16" s="51" t="n"/>
       <c r="G16" s="51" t="n"/>
       <c r="H16" s="51" t="n"/>
@@ -14430,9 +14480,9 @@
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C18" s="40" t="n"/>
-      <c r="D18" s="40" t="n"/>
-      <c r="E18" s="40" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
       <c r="F18" s="51" t="n"/>
       <c r="G18" s="51" t="n"/>
       <c r="H18" s="51" t="n"/>
@@ -14505,9 +14555,9 @@
           <t>Nov_2021</t>
         </is>
       </c>
-      <c r="C23" s="43" t="n"/>
-      <c r="D23" s="43" t="n"/>
-      <c r="E23" s="43" t="n"/>
+      <c r="C23" s="36" t="n"/>
+      <c r="D23" s="36" t="n"/>
+      <c r="E23" s="36" t="n"/>
       <c r="F23" s="51" t="n"/>
       <c r="G23" s="51" t="n"/>
       <c r="H23" s="51" t="n"/>
@@ -14520,9 +14570,9 @@
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C24" s="46" t="n"/>
-      <c r="D24" s="46" t="n"/>
-      <c r="E24" s="46" t="n"/>
+      <c r="C24" s="36" t="n"/>
+      <c r="D24" s="36" t="n"/>
+      <c r="E24" s="36" t="n"/>
       <c r="F24" s="51" t="n"/>
       <c r="G24" s="51" t="n"/>
       <c r="H24" s="51" t="n"/>
@@ -14623,13 +14673,13 @@
           <t>Sept_2016</t>
         </is>
       </c>
-      <c r="C30" s="40" t="n"/>
-      <c r="D30" s="40" t="n"/>
-      <c r="E30" s="40" t="n"/>
-      <c r="F30" s="40" t="n"/>
-      <c r="G30" s="40" t="n"/>
-      <c r="H30" s="40" t="n"/>
-      <c r="I30" s="40" t="n"/>
+      <c r="C30" s="36" t="n"/>
+      <c r="D30" s="36" t="n"/>
+      <c r="E30" s="36" t="n"/>
+      <c r="F30" s="36" t="n"/>
+      <c r="G30" s="36" t="n"/>
+      <c r="H30" s="36" t="n"/>
+      <c r="I30" s="36" t="n"/>
       <c r="J30" s="51" t="n"/>
       <c r="K30" s="51" t="n"/>
     </row>
@@ -14704,12 +14754,12 @@
         </is>
       </c>
       <c r="C35" s="36" t="n"/>
-      <c r="D35" s="43" t="n"/>
-      <c r="E35" s="43" t="n"/>
-      <c r="F35" s="43" t="n"/>
-      <c r="G35" s="43" t="n"/>
-      <c r="H35" s="43" t="n"/>
-      <c r="I35" s="43" t="n"/>
+      <c r="D35" s="36" t="n"/>
+      <c r="E35" s="36" t="n"/>
+      <c r="F35" s="36" t="n"/>
+      <c r="G35" s="36" t="n"/>
+      <c r="H35" s="36" t="n"/>
+      <c r="I35" s="36" t="n"/>
       <c r="J35" s="51" t="n"/>
       <c r="K35" s="51" t="n"/>
     </row>
@@ -14719,13 +14769,13 @@
           <t>Sept_2022</t>
         </is>
       </c>
-      <c r="C36" s="46" t="n"/>
-      <c r="D36" s="46" t="n"/>
-      <c r="E36" s="46" t="n"/>
-      <c r="F36" s="46" t="n"/>
-      <c r="G36" s="46" t="n"/>
-      <c r="H36" s="46" t="n"/>
-      <c r="I36" s="46" t="n"/>
+      <c r="C36" s="36" t="n"/>
+      <c r="D36" s="36" t="n"/>
+      <c r="E36" s="36" t="n"/>
+      <c r="F36" s="36" t="n"/>
+      <c r="G36" s="36" t="n"/>
+      <c r="H36" s="36" t="n"/>
+      <c r="I36" s="36" t="n"/>
       <c r="J36" s="51" t="n"/>
       <c r="K36" s="51" t="n"/>
     </row>
@@ -14759,7 +14809,7 @@
           <t>Heat &amp; Temperature</t>
         </is>
       </c>
-      <c r="E39" s="67" t="inlineStr">
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>Waves, Sound &amp; Light</t>
         </is>
@@ -14773,7 +14823,7 @@
       <c r="B40" s="64" t="n"/>
       <c r="C40" s="66" t="n"/>
       <c r="D40" s="66" t="n"/>
-      <c r="E40" s="65" t="n"/>
+      <c r="E40" s="66" t="n"/>
       <c r="F40" s="54" t="n"/>
       <c r="G40" s="54" t="n"/>
       <c r="J40" s="51" t="n"/>
@@ -14799,9 +14849,9 @@
           <t>Sept_2016</t>
         </is>
       </c>
-      <c r="C42" s="40" t="n"/>
-      <c r="D42" s="40" t="n"/>
-      <c r="E42" s="40" t="n"/>
+      <c r="C42" s="36" t="n"/>
+      <c r="D42" s="36" t="n"/>
+      <c r="E42" s="36" t="n"/>
       <c r="F42" s="49" t="n"/>
       <c r="G42" s="49" t="n"/>
       <c r="J42" s="51" t="n"/>
@@ -14869,9 +14919,9 @@
           <t>Sept_2021</t>
         </is>
       </c>
-      <c r="C47" s="43" t="n"/>
-      <c r="D47" s="43" t="n"/>
-      <c r="E47" s="43" t="n"/>
+      <c r="C47" s="36" t="n"/>
+      <c r="D47" s="36" t="n"/>
+      <c r="E47" s="36" t="n"/>
       <c r="F47" s="49" t="n"/>
       <c r="G47" s="49" t="n"/>
       <c r="J47" s="51" t="n"/>
@@ -14883,9 +14933,9 @@
           <t>Sept_2022</t>
         </is>
       </c>
-      <c r="C48" s="46" t="n"/>
-      <c r="D48" s="46" t="n"/>
-      <c r="E48" s="46" t="n"/>
+      <c r="C48" s="36" t="n"/>
+      <c r="D48" s="36" t="n"/>
+      <c r="E48" s="36" t="n"/>
       <c r="F48" s="49" t="n"/>
       <c r="G48" s="49" t="n"/>
       <c r="J48" s="51" t="n"/>
@@ -14985,13 +15035,13 @@
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C54" s="40" t="n"/>
-      <c r="D54" s="40" t="n"/>
-      <c r="E54" s="40" t="n"/>
-      <c r="F54" s="40" t="n"/>
-      <c r="G54" s="40" t="n"/>
-      <c r="H54" s="40" t="n"/>
-      <c r="I54" s="40" t="n"/>
+      <c r="C54" s="36" t="n"/>
+      <c r="D54" s="36" t="n"/>
+      <c r="E54" s="36" t="n"/>
+      <c r="F54" s="36" t="n"/>
+      <c r="G54" s="36" t="n"/>
+      <c r="H54" s="36" t="n"/>
+      <c r="I54" s="36" t="n"/>
       <c r="J54" s="51" t="n"/>
       <c r="K54" s="51" t="n"/>
     </row>
@@ -15044,18 +15094,18 @@
       <c r="K57" s="51" t="n"/>
     </row>
     <row r="58">
-      <c r="B58" s="15" t="inlineStr">
+      <c r="B58" s="68" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C58" s="36" t="n"/>
-      <c r="D58" s="36" t="n"/>
-      <c r="E58" s="36" t="n"/>
-      <c r="F58" s="36" t="n"/>
-      <c r="G58" s="36" t="n"/>
-      <c r="H58" s="36" t="n"/>
-      <c r="I58" s="36" t="n"/>
+      <c r="C58" s="69" t="n"/>
+      <c r="D58" s="69" t="n"/>
+      <c r="E58" s="69" t="n"/>
+      <c r="F58" s="69" t="n"/>
+      <c r="G58" s="69" t="n"/>
+      <c r="H58" s="69" t="n"/>
+      <c r="I58" s="69" t="n"/>
       <c r="J58" s="51" t="n"/>
       <c r="K58" s="51" t="n"/>
     </row>
@@ -15066,12 +15116,12 @@
         </is>
       </c>
       <c r="C59" s="36" t="n"/>
-      <c r="D59" s="43" t="n"/>
-      <c r="E59" s="43" t="n"/>
-      <c r="F59" s="43" t="n"/>
-      <c r="G59" s="43" t="n"/>
-      <c r="H59" s="43" t="n"/>
-      <c r="I59" s="43" t="n"/>
+      <c r="D59" s="36" t="n"/>
+      <c r="E59" s="36" t="n"/>
+      <c r="F59" s="36" t="n"/>
+      <c r="G59" s="36" t="n"/>
+      <c r="H59" s="36" t="n"/>
+      <c r="I59" s="36" t="n"/>
       <c r="J59" s="51" t="n"/>
       <c r="K59" s="51" t="n"/>
     </row>
@@ -15081,13 +15131,13 @@
           <t>May/Jun_2022</t>
         </is>
       </c>
-      <c r="C60" s="46" t="n"/>
-      <c r="D60" s="46" t="n"/>
-      <c r="E60" s="46" t="n"/>
-      <c r="F60" s="46" t="n"/>
-      <c r="G60" s="46" t="n"/>
-      <c r="H60" s="46" t="n"/>
-      <c r="I60" s="46" t="n"/>
+      <c r="C60" s="36" t="n"/>
+      <c r="D60" s="36" t="n"/>
+      <c r="E60" s="36" t="n"/>
+      <c r="F60" s="36" t="n"/>
+      <c r="G60" s="36" t="n"/>
+      <c r="H60" s="36" t="n"/>
+      <c r="I60" s="36" t="n"/>
       <c r="J60" s="51" t="n"/>
       <c r="K60" s="51" t="n"/>
     </row>
@@ -15121,7 +15171,7 @@
           <t>Heat &amp; Temperature</t>
         </is>
       </c>
-      <c r="E63" s="67" t="inlineStr">
+      <c r="E63" s="12" t="inlineStr">
         <is>
           <t>Waves, Sound &amp; Light</t>
         </is>
@@ -15135,7 +15185,7 @@
       <c r="B64" s="64" t="n"/>
       <c r="C64" s="66" t="n"/>
       <c r="D64" s="66" t="n"/>
-      <c r="E64" s="65" t="n"/>
+      <c r="E64" s="66" t="n"/>
       <c r="F64" s="54" t="n"/>
       <c r="G64" s="54" t="n"/>
       <c r="J64" s="51" t="n"/>
@@ -15161,9 +15211,9 @@
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C66" s="40" t="n"/>
-      <c r="D66" s="40" t="n"/>
-      <c r="E66" s="40" t="n"/>
+      <c r="C66" s="36" t="n"/>
+      <c r="D66" s="36" t="n"/>
+      <c r="E66" s="36" t="n"/>
       <c r="F66" s="49" t="n"/>
       <c r="G66" s="49" t="n"/>
       <c r="J66" s="51" t="n"/>
@@ -15212,14 +15262,14 @@
       <c r="K69" s="51" t="n"/>
     </row>
     <row r="70">
-      <c r="B70" s="15" t="inlineStr">
+      <c r="B70" s="68" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C70" s="36" t="n"/>
-      <c r="D70" s="36" t="n"/>
-      <c r="E70" s="36" t="n"/>
+      <c r="C70" s="69" t="n"/>
+      <c r="D70" s="69" t="n"/>
+      <c r="E70" s="69" t="n"/>
       <c r="F70" s="49" t="n"/>
       <c r="G70" s="49" t="n"/>
       <c r="J70" s="51" t="n"/>
@@ -15231,9 +15281,9 @@
           <t>May/Jun_2021</t>
         </is>
       </c>
-      <c r="C71" s="43" t="n"/>
-      <c r="D71" s="43" t="n"/>
-      <c r="E71" s="43" t="n"/>
+      <c r="C71" s="36" t="n"/>
+      <c r="D71" s="36" t="n"/>
+      <c r="E71" s="36" t="n"/>
       <c r="F71" s="49" t="n"/>
       <c r="G71" s="49" t="n"/>
       <c r="J71" s="51" t="n"/>
@@ -15245,9 +15295,9 @@
           <t>May/Jun_2022</t>
         </is>
       </c>
-      <c r="C72" s="46" t="n"/>
-      <c r="D72" s="46" t="n"/>
-      <c r="E72" s="46" t="n"/>
+      <c r="C72" s="36" t="n"/>
+      <c r="D72" s="36" t="n"/>
+      <c r="E72" s="36" t="n"/>
       <c r="F72" s="49" t="n"/>
       <c r="G72" s="49" t="n"/>
       <c r="J72" s="51" t="n"/>
@@ -15347,13 +15397,13 @@
           <t>Feb/Mar_2016</t>
         </is>
       </c>
-      <c r="C78" s="40" t="n"/>
-      <c r="D78" s="40" t="n"/>
-      <c r="E78" s="40" t="n"/>
-      <c r="F78" s="40" t="n"/>
-      <c r="G78" s="40" t="n"/>
-      <c r="H78" s="40" t="n"/>
-      <c r="I78" s="40" t="n"/>
+      <c r="C78" s="36" t="n"/>
+      <c r="D78" s="36" t="n"/>
+      <c r="E78" s="36" t="n"/>
+      <c r="F78" s="36" t="n"/>
+      <c r="G78" s="36" t="n"/>
+      <c r="H78" s="36" t="n"/>
+      <c r="I78" s="36" t="n"/>
       <c r="J78" s="51" t="n"/>
       <c r="K78" s="51" t="n"/>
     </row>
@@ -15428,12 +15478,12 @@
         </is>
       </c>
       <c r="C83" s="36" t="n"/>
-      <c r="D83" s="43" t="n"/>
-      <c r="E83" s="43" t="n"/>
-      <c r="F83" s="43" t="n"/>
-      <c r="G83" s="43" t="n"/>
-      <c r="H83" s="43" t="n"/>
-      <c r="I83" s="43" t="n"/>
+      <c r="D83" s="36" t="n"/>
+      <c r="E83" s="36" t="n"/>
+      <c r="F83" s="36" t="n"/>
+      <c r="G83" s="36" t="n"/>
+      <c r="H83" s="36" t="n"/>
+      <c r="I83" s="36" t="n"/>
       <c r="J83" s="51" t="n"/>
       <c r="K83" s="51" t="n"/>
     </row>
@@ -15443,13 +15493,13 @@
           <t>Feb/Mar_2022</t>
         </is>
       </c>
-      <c r="C84" s="46" t="n"/>
-      <c r="D84" s="46" t="n"/>
-      <c r="E84" s="46" t="n"/>
-      <c r="F84" s="46" t="n"/>
-      <c r="G84" s="46" t="n"/>
-      <c r="H84" s="46" t="n"/>
-      <c r="I84" s="46" t="n"/>
+      <c r="C84" s="36" t="n"/>
+      <c r="D84" s="36" t="n"/>
+      <c r="E84" s="36" t="n"/>
+      <c r="F84" s="36" t="n"/>
+      <c r="G84" s="36" t="n"/>
+      <c r="H84" s="36" t="n"/>
+      <c r="I84" s="36" t="n"/>
       <c r="J84" s="51" t="n"/>
       <c r="K84" s="51" t="n"/>
     </row>
@@ -15483,7 +15533,7 @@
           <t>Heat &amp; Temperature</t>
         </is>
       </c>
-      <c r="E87" s="67" t="inlineStr">
+      <c r="E87" s="12" t="inlineStr">
         <is>
           <t>Waves, Sound &amp; Light</t>
         </is>
@@ -15497,7 +15547,7 @@
       <c r="B88" s="64" t="n"/>
       <c r="C88" s="66" t="n"/>
       <c r="D88" s="66" t="n"/>
-      <c r="E88" s="65" t="n"/>
+      <c r="E88" s="66" t="n"/>
       <c r="F88" s="54" t="n"/>
       <c r="G88" s="54" t="n"/>
       <c r="J88" s="51" t="n"/>
@@ -15523,9 +15573,9 @@
           <t>Feb/Mar_2016</t>
         </is>
       </c>
-      <c r="C90" s="40" t="n"/>
-      <c r="D90" s="40" t="n"/>
-      <c r="E90" s="40" t="n"/>
+      <c r="C90" s="36" t="n"/>
+      <c r="D90" s="36" t="n"/>
+      <c r="E90" s="36" t="n"/>
       <c r="F90" s="49" t="n"/>
       <c r="G90" s="49" t="n"/>
       <c r="J90" s="51" t="n"/>
@@ -15593,9 +15643,9 @@
           <t>Feb/Mar_2021</t>
         </is>
       </c>
-      <c r="C95" s="43" t="n"/>
-      <c r="D95" s="43" t="n"/>
-      <c r="E95" s="43" t="n"/>
+      <c r="C95" s="36" t="n"/>
+      <c r="D95" s="36" t="n"/>
+      <c r="E95" s="36" t="n"/>
       <c r="F95" s="49" t="n"/>
       <c r="G95" s="49" t="n"/>
       <c r="J95" s="51" t="n"/>
@@ -15607,9 +15657,9 @@
           <t>Feb/Mar_2022</t>
         </is>
       </c>
-      <c r="C96" s="46" t="n"/>
-      <c r="D96" s="46" t="n"/>
-      <c r="E96" s="46" t="n"/>
+      <c r="C96" s="36" t="n"/>
+      <c r="D96" s="36" t="n"/>
+      <c r="E96" s="36" t="n"/>
       <c r="F96" s="49" t="n"/>
       <c r="G96" s="49" t="n"/>
       <c r="J96" s="51" t="n"/>
@@ -15619,7 +15669,6 @@
       <c r="J97" s="51" t="n"/>
       <c r="K97" s="51" t="n"/>
     </row>
-    <row r="98"/>
   </sheetData>
   <mergeCells count="56">
     <mergeCell ref="B27:B28"/>
@@ -15689,11 +15738,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K98"/>
+  <dimension ref="B1:K97"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.12844036697248" defaultRowHeight="14.25"/>
   <cols>
     <col width="9.12844036697248" customWidth="1" style="25" min="1" max="1"/>
     <col width="16.6238532110092" customWidth="1" style="3" min="2" max="25"/>
+    <col width="13" customWidth="1" style="25" min="3" max="3"/>
+    <col width="13" customWidth="1" style="25" min="4" max="4"/>
+    <col width="13" customWidth="1" style="25" min="5" max="5"/>
+    <col width="13" customWidth="1" style="25" min="6" max="6"/>
+    <col width="13" customWidth="1" style="25" min="7" max="7"/>
+    <col width="13" customWidth="1" style="25" min="8" max="8"/>
+    <col width="13" customWidth="1" style="25" min="9" max="9"/>
     <col width="9.12844036697248" customWidth="1" style="25" min="26" max="16384"/>
   </cols>
   <sheetData>
@@ -15788,13 +15844,13 @@
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C6" s="40" t="n"/>
-      <c r="D6" s="40" t="n"/>
-      <c r="E6" s="40" t="n"/>
-      <c r="F6" s="40" t="n"/>
-      <c r="G6" s="40" t="n"/>
-      <c r="H6" s="40" t="n"/>
-      <c r="I6" s="40" t="n"/>
+      <c r="C6" s="36" t="n"/>
+      <c r="D6" s="36" t="n"/>
+      <c r="E6" s="36" t="n"/>
+      <c r="F6" s="36" t="n"/>
+      <c r="G6" s="36" t="n"/>
+      <c r="H6" s="36" t="n"/>
+      <c r="I6" s="36" t="n"/>
       <c r="J6" s="51" t="n"/>
       <c r="K6" s="51" t="n"/>
     </row>
@@ -15869,12 +15925,12 @@
         </is>
       </c>
       <c r="C11" s="36" t="n"/>
-      <c r="D11" s="43" t="n"/>
-      <c r="E11" s="43" t="n"/>
-      <c r="F11" s="43" t="n"/>
-      <c r="G11" s="43" t="n"/>
-      <c r="H11" s="43" t="n"/>
-      <c r="I11" s="43" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="36" t="n"/>
+      <c r="F11" s="36" t="n"/>
+      <c r="G11" s="36" t="n"/>
+      <c r="H11" s="36" t="n"/>
+      <c r="I11" s="36" t="n"/>
       <c r="J11" s="51" t="n"/>
       <c r="K11" s="51" t="n"/>
     </row>
@@ -15884,13 +15940,13 @@
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C12" s="46" t="n"/>
-      <c r="D12" s="46" t="n"/>
-      <c r="E12" s="46" t="n"/>
-      <c r="F12" s="46" t="n"/>
-      <c r="G12" s="46" t="n"/>
-      <c r="H12" s="46" t="n"/>
-      <c r="I12" s="46" t="n"/>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="36" t="n"/>
+      <c r="F12" s="36" t="n"/>
+      <c r="G12" s="36" t="n"/>
+      <c r="H12" s="36" t="n"/>
+      <c r="I12" s="36" t="n"/>
       <c r="J12" s="51" t="n"/>
       <c r="K12" s="51" t="n"/>
     </row>
@@ -15925,7 +15981,7 @@
           <t>Heat &amp; Temperature</t>
         </is>
       </c>
-      <c r="E15" s="67" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>Waves, Sound &amp; Light</t>
         </is>
@@ -15940,7 +15996,7 @@
       <c r="B16" s="64" t="n"/>
       <c r="C16" s="66" t="n"/>
       <c r="D16" s="66" t="n"/>
-      <c r="E16" s="65" t="n"/>
+      <c r="E16" s="66" t="n"/>
       <c r="F16" s="51" t="n"/>
       <c r="G16" s="51" t="n"/>
       <c r="H16" s="51" t="n"/>
@@ -15968,9 +16024,9 @@
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C18" s="40" t="n"/>
-      <c r="D18" s="40" t="n"/>
-      <c r="E18" s="40" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
       <c r="F18" s="51" t="n"/>
       <c r="G18" s="51" t="n"/>
       <c r="H18" s="51" t="n"/>
@@ -16043,9 +16099,9 @@
           <t>Nov_2021</t>
         </is>
       </c>
-      <c r="C23" s="43" t="n"/>
-      <c r="D23" s="43" t="n"/>
-      <c r="E23" s="43" t="n"/>
+      <c r="C23" s="36" t="n"/>
+      <c r="D23" s="36" t="n"/>
+      <c r="E23" s="36" t="n"/>
       <c r="F23" s="51" t="n"/>
       <c r="G23" s="51" t="n"/>
       <c r="H23" s="51" t="n"/>
@@ -16058,9 +16114,9 @@
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C24" s="46" t="n"/>
-      <c r="D24" s="46" t="n"/>
-      <c r="E24" s="46" t="n"/>
+      <c r="C24" s="36" t="n"/>
+      <c r="D24" s="36" t="n"/>
+      <c r="E24" s="36" t="n"/>
       <c r="F24" s="51" t="n"/>
       <c r="G24" s="51" t="n"/>
       <c r="H24" s="51" t="n"/>
@@ -16161,13 +16217,13 @@
           <t>Sept_2016</t>
         </is>
       </c>
-      <c r="C30" s="40" t="n"/>
-      <c r="D30" s="40" t="n"/>
-      <c r="E30" s="40" t="n"/>
-      <c r="F30" s="40" t="n"/>
-      <c r="G30" s="40" t="n"/>
-      <c r="H30" s="40" t="n"/>
-      <c r="I30" s="40" t="n"/>
+      <c r="C30" s="36" t="n"/>
+      <c r="D30" s="36" t="n"/>
+      <c r="E30" s="36" t="n"/>
+      <c r="F30" s="36" t="n"/>
+      <c r="G30" s="36" t="n"/>
+      <c r="H30" s="36" t="n"/>
+      <c r="I30" s="36" t="n"/>
       <c r="J30" s="51" t="n"/>
       <c r="K30" s="51" t="n"/>
     </row>
@@ -16242,12 +16298,12 @@
         </is>
       </c>
       <c r="C35" s="36" t="n"/>
-      <c r="D35" s="43" t="n"/>
-      <c r="E35" s="43" t="n"/>
-      <c r="F35" s="43" t="n"/>
-      <c r="G35" s="43" t="n"/>
-      <c r="H35" s="43" t="n"/>
-      <c r="I35" s="43" t="n"/>
+      <c r="D35" s="36" t="n"/>
+      <c r="E35" s="36" t="n"/>
+      <c r="F35" s="36" t="n"/>
+      <c r="G35" s="36" t="n"/>
+      <c r="H35" s="36" t="n"/>
+      <c r="I35" s="36" t="n"/>
       <c r="J35" s="51" t="n"/>
       <c r="K35" s="51" t="n"/>
     </row>
@@ -16257,13 +16313,13 @@
           <t>Sept_2022</t>
         </is>
       </c>
-      <c r="C36" s="46" t="n"/>
-      <c r="D36" s="46" t="n"/>
-      <c r="E36" s="46" t="n"/>
-      <c r="F36" s="46" t="n"/>
-      <c r="G36" s="46" t="n"/>
-      <c r="H36" s="46" t="n"/>
-      <c r="I36" s="46" t="n"/>
+      <c r="C36" s="36" t="n"/>
+      <c r="D36" s="36" t="n"/>
+      <c r="E36" s="36" t="n"/>
+      <c r="F36" s="36" t="n"/>
+      <c r="G36" s="36" t="n"/>
+      <c r="H36" s="36" t="n"/>
+      <c r="I36" s="36" t="n"/>
       <c r="J36" s="51" t="n"/>
       <c r="K36" s="51" t="n"/>
     </row>
@@ -16297,7 +16353,7 @@
           <t>Heat &amp; Temperature</t>
         </is>
       </c>
-      <c r="E39" s="67" t="inlineStr">
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>Waves, Sound &amp; Light</t>
         </is>
@@ -16311,7 +16367,7 @@
       <c r="B40" s="64" t="n"/>
       <c r="C40" s="66" t="n"/>
       <c r="D40" s="66" t="n"/>
-      <c r="E40" s="65" t="n"/>
+      <c r="E40" s="66" t="n"/>
       <c r="F40" s="54" t="n"/>
       <c r="G40" s="54" t="n"/>
       <c r="J40" s="51" t="n"/>
@@ -16337,9 +16393,9 @@
           <t>Sept_2016</t>
         </is>
       </c>
-      <c r="C42" s="40" t="n"/>
-      <c r="D42" s="40" t="n"/>
-      <c r="E42" s="40" t="n"/>
+      <c r="C42" s="36" t="n"/>
+      <c r="D42" s="36" t="n"/>
+      <c r="E42" s="36" t="n"/>
       <c r="F42" s="49" t="n"/>
       <c r="G42" s="49" t="n"/>
       <c r="J42" s="51" t="n"/>
@@ -16407,9 +16463,9 @@
           <t>Sept_2021</t>
         </is>
       </c>
-      <c r="C47" s="43" t="n"/>
-      <c r="D47" s="43" t="n"/>
-      <c r="E47" s="43" t="n"/>
+      <c r="C47" s="36" t="n"/>
+      <c r="D47" s="36" t="n"/>
+      <c r="E47" s="36" t="n"/>
       <c r="F47" s="49" t="n"/>
       <c r="G47" s="49" t="n"/>
       <c r="J47" s="51" t="n"/>
@@ -16421,9 +16477,9 @@
           <t>Sept_2022</t>
         </is>
       </c>
-      <c r="C48" s="46" t="n"/>
-      <c r="D48" s="46" t="n"/>
-      <c r="E48" s="46" t="n"/>
+      <c r="C48" s="36" t="n"/>
+      <c r="D48" s="36" t="n"/>
+      <c r="E48" s="36" t="n"/>
       <c r="F48" s="49" t="n"/>
       <c r="G48" s="49" t="n"/>
       <c r="J48" s="51" t="n"/>
@@ -16523,13 +16579,13 @@
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C54" s="40" t="n"/>
-      <c r="D54" s="40" t="n"/>
-      <c r="E54" s="40" t="n"/>
-      <c r="F54" s="40" t="n"/>
-      <c r="G54" s="40" t="n"/>
-      <c r="H54" s="40" t="n"/>
-      <c r="I54" s="40" t="n"/>
+      <c r="C54" s="36" t="n"/>
+      <c r="D54" s="36" t="n"/>
+      <c r="E54" s="36" t="n"/>
+      <c r="F54" s="36" t="n"/>
+      <c r="G54" s="36" t="n"/>
+      <c r="H54" s="36" t="n"/>
+      <c r="I54" s="36" t="n"/>
       <c r="J54" s="51" t="n"/>
       <c r="K54" s="51" t="n"/>
     </row>
@@ -16582,18 +16638,18 @@
       <c r="K57" s="51" t="n"/>
     </row>
     <row r="58">
-      <c r="B58" s="15" t="inlineStr">
+      <c r="B58" s="68" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C58" s="36" t="n"/>
-      <c r="D58" s="36" t="n"/>
-      <c r="E58" s="36" t="n"/>
-      <c r="F58" s="36" t="n"/>
-      <c r="G58" s="36" t="n"/>
-      <c r="H58" s="36" t="n"/>
-      <c r="I58" s="36" t="n"/>
+      <c r="C58" s="69" t="n"/>
+      <c r="D58" s="69" t="n"/>
+      <c r="E58" s="69" t="n"/>
+      <c r="F58" s="69" t="n"/>
+      <c r="G58" s="69" t="n"/>
+      <c r="H58" s="69" t="n"/>
+      <c r="I58" s="69" t="n"/>
       <c r="J58" s="51" t="n"/>
       <c r="K58" s="51" t="n"/>
     </row>
@@ -16604,12 +16660,12 @@
         </is>
       </c>
       <c r="C59" s="36" t="n"/>
-      <c r="D59" s="43" t="n"/>
-      <c r="E59" s="43" t="n"/>
-      <c r="F59" s="43" t="n"/>
-      <c r="G59" s="43" t="n"/>
-      <c r="H59" s="43" t="n"/>
-      <c r="I59" s="43" t="n"/>
+      <c r="D59" s="36" t="n"/>
+      <c r="E59" s="36" t="n"/>
+      <c r="F59" s="36" t="n"/>
+      <c r="G59" s="36" t="n"/>
+      <c r="H59" s="36" t="n"/>
+      <c r="I59" s="36" t="n"/>
       <c r="J59" s="51" t="n"/>
       <c r="K59" s="51" t="n"/>
     </row>
@@ -16619,13 +16675,13 @@
           <t>May/Jun_2022</t>
         </is>
       </c>
-      <c r="C60" s="46" t="n"/>
-      <c r="D60" s="46" t="n"/>
-      <c r="E60" s="46" t="n"/>
-      <c r="F60" s="46" t="n"/>
-      <c r="G60" s="46" t="n"/>
-      <c r="H60" s="46" t="n"/>
-      <c r="I60" s="46" t="n"/>
+      <c r="C60" s="36" t="n"/>
+      <c r="D60" s="36" t="n"/>
+      <c r="E60" s="36" t="n"/>
+      <c r="F60" s="36" t="n"/>
+      <c r="G60" s="36" t="n"/>
+      <c r="H60" s="36" t="n"/>
+      <c r="I60" s="36" t="n"/>
       <c r="J60" s="51" t="n"/>
       <c r="K60" s="51" t="n"/>
     </row>
@@ -16659,7 +16715,7 @@
           <t>Heat &amp; Temperature</t>
         </is>
       </c>
-      <c r="E63" s="67" t="inlineStr">
+      <c r="E63" s="12" t="inlineStr">
         <is>
           <t>Waves, Sound &amp; Light</t>
         </is>
@@ -16673,7 +16729,7 @@
       <c r="B64" s="64" t="n"/>
       <c r="C64" s="66" t="n"/>
       <c r="D64" s="66" t="n"/>
-      <c r="E64" s="65" t="n"/>
+      <c r="E64" s="66" t="n"/>
       <c r="F64" s="54" t="n"/>
       <c r="G64" s="54" t="n"/>
       <c r="J64" s="51" t="n"/>
@@ -16699,9 +16755,9 @@
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C66" s="40" t="n"/>
-      <c r="D66" s="40" t="n"/>
-      <c r="E66" s="40" t="n"/>
+      <c r="C66" s="36" t="n"/>
+      <c r="D66" s="36" t="n"/>
+      <c r="E66" s="36" t="n"/>
       <c r="F66" s="49" t="n"/>
       <c r="G66" s="49" t="n"/>
       <c r="J66" s="51" t="n"/>
@@ -16750,14 +16806,14 @@
       <c r="K69" s="51" t="n"/>
     </row>
     <row r="70">
-      <c r="B70" s="15" t="inlineStr">
+      <c r="B70" s="68" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C70" s="36" t="n"/>
-      <c r="D70" s="36" t="n"/>
-      <c r="E70" s="36" t="n"/>
+      <c r="C70" s="69" t="n"/>
+      <c r="D70" s="69" t="n"/>
+      <c r="E70" s="69" t="n"/>
       <c r="F70" s="49" t="n"/>
       <c r="G70" s="49" t="n"/>
       <c r="J70" s="51" t="n"/>
@@ -16769,9 +16825,9 @@
           <t>May/Jun_2021</t>
         </is>
       </c>
-      <c r="C71" s="43" t="n"/>
-      <c r="D71" s="43" t="n"/>
-      <c r="E71" s="43" t="n"/>
+      <c r="C71" s="36" t="n"/>
+      <c r="D71" s="36" t="n"/>
+      <c r="E71" s="36" t="n"/>
       <c r="F71" s="49" t="n"/>
       <c r="G71" s="49" t="n"/>
       <c r="J71" s="51" t="n"/>
@@ -16783,9 +16839,9 @@
           <t>May/Jun_2022</t>
         </is>
       </c>
-      <c r="C72" s="46" t="n"/>
-      <c r="D72" s="46" t="n"/>
-      <c r="E72" s="46" t="n"/>
+      <c r="C72" s="36" t="n"/>
+      <c r="D72" s="36" t="n"/>
+      <c r="E72" s="36" t="n"/>
       <c r="F72" s="49" t="n"/>
       <c r="G72" s="49" t="n"/>
       <c r="J72" s="51" t="n"/>
@@ -16885,13 +16941,13 @@
           <t>Feb/Mar_2016</t>
         </is>
       </c>
-      <c r="C78" s="40" t="n"/>
-      <c r="D78" s="40" t="n"/>
-      <c r="E78" s="40" t="n"/>
-      <c r="F78" s="40" t="n"/>
-      <c r="G78" s="40" t="n"/>
-      <c r="H78" s="40" t="n"/>
-      <c r="I78" s="40" t="n"/>
+      <c r="C78" s="36" t="n"/>
+      <c r="D78" s="36" t="n"/>
+      <c r="E78" s="36" t="n"/>
+      <c r="F78" s="36" t="n"/>
+      <c r="G78" s="36" t="n"/>
+      <c r="H78" s="36" t="n"/>
+      <c r="I78" s="36" t="n"/>
       <c r="J78" s="51" t="n"/>
       <c r="K78" s="51" t="n"/>
     </row>
@@ -16966,12 +17022,12 @@
         </is>
       </c>
       <c r="C83" s="36" t="n"/>
-      <c r="D83" s="43" t="n"/>
-      <c r="E83" s="43" t="n"/>
-      <c r="F83" s="43" t="n"/>
-      <c r="G83" s="43" t="n"/>
-      <c r="H83" s="43" t="n"/>
-      <c r="I83" s="43" t="n"/>
+      <c r="D83" s="36" t="n"/>
+      <c r="E83" s="36" t="n"/>
+      <c r="F83" s="36" t="n"/>
+      <c r="G83" s="36" t="n"/>
+      <c r="H83" s="36" t="n"/>
+      <c r="I83" s="36" t="n"/>
       <c r="J83" s="51" t="n"/>
       <c r="K83" s="51" t="n"/>
     </row>
@@ -16981,13 +17037,13 @@
           <t>Feb/Mar_2022</t>
         </is>
       </c>
-      <c r="C84" s="46" t="n"/>
-      <c r="D84" s="46" t="n"/>
-      <c r="E84" s="46" t="n"/>
-      <c r="F84" s="46" t="n"/>
-      <c r="G84" s="46" t="n"/>
-      <c r="H84" s="46" t="n"/>
-      <c r="I84" s="46" t="n"/>
+      <c r="C84" s="36" t="n"/>
+      <c r="D84" s="36" t="n"/>
+      <c r="E84" s="36" t="n"/>
+      <c r="F84" s="36" t="n"/>
+      <c r="G84" s="36" t="n"/>
+      <c r="H84" s="36" t="n"/>
+      <c r="I84" s="36" t="n"/>
       <c r="J84" s="51" t="n"/>
       <c r="K84" s="51" t="n"/>
     </row>
@@ -17021,7 +17077,7 @@
           <t>Heat &amp; Temperature</t>
         </is>
       </c>
-      <c r="E87" s="67" t="inlineStr">
+      <c r="E87" s="12" t="inlineStr">
         <is>
           <t>Waves, Sound &amp; Light</t>
         </is>
@@ -17035,7 +17091,7 @@
       <c r="B88" s="64" t="n"/>
       <c r="C88" s="66" t="n"/>
       <c r="D88" s="66" t="n"/>
-      <c r="E88" s="65" t="n"/>
+      <c r="E88" s="66" t="n"/>
       <c r="F88" s="54" t="n"/>
       <c r="G88" s="54" t="n"/>
       <c r="J88" s="51" t="n"/>
@@ -17061,9 +17117,9 @@
           <t>Feb/Mar_2016</t>
         </is>
       </c>
-      <c r="C90" s="40" t="n"/>
-      <c r="D90" s="40" t="n"/>
-      <c r="E90" s="40" t="n"/>
+      <c r="C90" s="36" t="n"/>
+      <c r="D90" s="36" t="n"/>
+      <c r="E90" s="36" t="n"/>
       <c r="F90" s="49" t="n"/>
       <c r="G90" s="49" t="n"/>
       <c r="J90" s="51" t="n"/>
@@ -17131,9 +17187,9 @@
           <t>Feb/Mar_2021</t>
         </is>
       </c>
-      <c r="C95" s="43" t="n"/>
-      <c r="D95" s="43" t="n"/>
-      <c r="E95" s="43" t="n"/>
+      <c r="C95" s="36" t="n"/>
+      <c r="D95" s="36" t="n"/>
+      <c r="E95" s="36" t="n"/>
       <c r="F95" s="49" t="n"/>
       <c r="G95" s="49" t="n"/>
       <c r="J95" s="51" t="n"/>
@@ -17145,9 +17201,9 @@
           <t>Feb/Mar_2022</t>
         </is>
       </c>
-      <c r="C96" s="46" t="n"/>
-      <c r="D96" s="46" t="n"/>
-      <c r="E96" s="46" t="n"/>
+      <c r="C96" s="36" t="n"/>
+      <c r="D96" s="36" t="n"/>
+      <c r="E96" s="36" t="n"/>
       <c r="F96" s="49" t="n"/>
       <c r="G96" s="49" t="n"/>
       <c r="J96" s="51" t="n"/>
@@ -17157,7 +17213,6 @@
       <c r="J97" s="51" t="n"/>
       <c r="K97" s="51" t="n"/>
     </row>
-    <row r="98"/>
   </sheetData>
   <mergeCells count="56">
     <mergeCell ref="B27:B28"/>
@@ -17227,11 +17282,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K98"/>
+  <dimension ref="B1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.12844036697248" defaultRowHeight="14.25"/>
   <cols>
     <col width="9.12844036697248" customWidth="1" style="25" min="1" max="1"/>
     <col width="16.6238532110092" customWidth="1" style="3" min="2" max="25"/>
+    <col width="13" customWidth="1" style="25" min="3" max="3"/>
+    <col width="13" customWidth="1" style="25" min="4" max="4"/>
+    <col width="13" customWidth="1" style="25" min="5" max="5"/>
+    <col width="13" customWidth="1" style="25" min="6" max="6"/>
+    <col width="13" customWidth="1" style="25" min="7" max="7"/>
+    <col width="13" customWidth="1" style="25" min="8" max="8"/>
+    <col width="13" customWidth="1" style="25" min="9" max="9"/>
     <col width="9.12844036697248" customWidth="1" style="25" min="26" max="16384"/>
   </cols>
   <sheetData>
@@ -17326,13 +17388,13 @@
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C6" s="40" t="n"/>
-      <c r="D6" s="40" t="n"/>
-      <c r="E6" s="40" t="n"/>
-      <c r="F6" s="40" t="n"/>
-      <c r="G6" s="40" t="n"/>
-      <c r="H6" s="40" t="n"/>
-      <c r="I6" s="40" t="n"/>
+      <c r="C6" s="36" t="n"/>
+      <c r="D6" s="36" t="n"/>
+      <c r="E6" s="36" t="n"/>
+      <c r="F6" s="36" t="n"/>
+      <c r="G6" s="36" t="n"/>
+      <c r="H6" s="36" t="n"/>
+      <c r="I6" s="36" t="n"/>
       <c r="J6" s="51" t="n"/>
       <c r="K6" s="51" t="n"/>
     </row>
@@ -17407,12 +17469,12 @@
         </is>
       </c>
       <c r="C11" s="36" t="n"/>
-      <c r="D11" s="43" t="n"/>
-      <c r="E11" s="43" t="n"/>
-      <c r="F11" s="43" t="n"/>
-      <c r="G11" s="43" t="n"/>
-      <c r="H11" s="43" t="n"/>
-      <c r="I11" s="43" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="36" t="n"/>
+      <c r="F11" s="36" t="n"/>
+      <c r="G11" s="36" t="n"/>
+      <c r="H11" s="36" t="n"/>
+      <c r="I11" s="36" t="n"/>
       <c r="J11" s="51" t="n"/>
       <c r="K11" s="51" t="n"/>
     </row>
@@ -17422,13 +17484,13 @@
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C12" s="46" t="n"/>
-      <c r="D12" s="46" t="n"/>
-      <c r="E12" s="46" t="n"/>
-      <c r="F12" s="46" t="n"/>
-      <c r="G12" s="46" t="n"/>
-      <c r="H12" s="46" t="n"/>
-      <c r="I12" s="46" t="n"/>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="36" t="n"/>
+      <c r="F12" s="36" t="n"/>
+      <c r="G12" s="36" t="n"/>
+      <c r="H12" s="36" t="n"/>
+      <c r="I12" s="36" t="n"/>
       <c r="J12" s="51" t="n"/>
       <c r="K12" s="51" t="n"/>
     </row>
@@ -17463,7 +17525,7 @@
           <t>Heat &amp; Temperature</t>
         </is>
       </c>
-      <c r="E15" s="67" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>Waves, Sound &amp; Light</t>
         </is>
@@ -17478,7 +17540,7 @@
       <c r="B16" s="64" t="n"/>
       <c r="C16" s="66" t="n"/>
       <c r="D16" s="66" t="n"/>
-      <c r="E16" s="65" t="n"/>
+      <c r="E16" s="66" t="n"/>
       <c r="F16" s="51" t="n"/>
       <c r="G16" s="51" t="n"/>
       <c r="H16" s="51" t="n"/>
@@ -17506,9 +17568,9 @@
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C18" s="40" t="n"/>
-      <c r="D18" s="40" t="n"/>
-      <c r="E18" s="40" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
       <c r="F18" s="51" t="n"/>
       <c r="G18" s="51" t="n"/>
       <c r="H18" s="51" t="n"/>
@@ -17581,9 +17643,9 @@
           <t>Nov_2021</t>
         </is>
       </c>
-      <c r="C23" s="43" t="n"/>
-      <c r="D23" s="43" t="n"/>
-      <c r="E23" s="43" t="n"/>
+      <c r="C23" s="36" t="n"/>
+      <c r="D23" s="36" t="n"/>
+      <c r="E23" s="36" t="n"/>
       <c r="F23" s="51" t="n"/>
       <c r="G23" s="51" t="n"/>
       <c r="H23" s="51" t="n"/>
@@ -17596,9 +17658,9 @@
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C24" s="46" t="n"/>
-      <c r="D24" s="46" t="n"/>
-      <c r="E24" s="46" t="n"/>
+      <c r="C24" s="36" t="n"/>
+      <c r="D24" s="36" t="n"/>
+      <c r="E24" s="36" t="n"/>
       <c r="F24" s="51" t="n"/>
       <c r="G24" s="51" t="n"/>
       <c r="H24" s="51" t="n"/>
@@ -17699,13 +17761,13 @@
           <t>Sept_2016</t>
         </is>
       </c>
-      <c r="C30" s="40" t="n"/>
-      <c r="D30" s="40" t="n"/>
-      <c r="E30" s="40" t="n"/>
-      <c r="F30" s="40" t="n"/>
-      <c r="G30" s="40" t="n"/>
-      <c r="H30" s="40" t="n"/>
-      <c r="I30" s="40" t="n"/>
+      <c r="C30" s="36" t="n"/>
+      <c r="D30" s="36" t="n"/>
+      <c r="E30" s="36" t="n"/>
+      <c r="F30" s="36" t="n"/>
+      <c r="G30" s="36" t="n"/>
+      <c r="H30" s="36" t="n"/>
+      <c r="I30" s="36" t="n"/>
       <c r="J30" s="51" t="n"/>
       <c r="K30" s="51" t="n"/>
     </row>
@@ -17780,12 +17842,12 @@
         </is>
       </c>
       <c r="C35" s="36" t="n"/>
-      <c r="D35" s="43" t="n"/>
-      <c r="E35" s="43" t="n"/>
-      <c r="F35" s="43" t="n"/>
-      <c r="G35" s="43" t="n"/>
-      <c r="H35" s="43" t="n"/>
-      <c r="I35" s="43" t="n"/>
+      <c r="D35" s="36" t="n"/>
+      <c r="E35" s="36" t="n"/>
+      <c r="F35" s="36" t="n"/>
+      <c r="G35" s="36" t="n"/>
+      <c r="H35" s="36" t="n"/>
+      <c r="I35" s="36" t="n"/>
       <c r="J35" s="51" t="n"/>
       <c r="K35" s="51" t="n"/>
     </row>
@@ -17795,13 +17857,13 @@
           <t>Sept_2022</t>
         </is>
       </c>
-      <c r="C36" s="46" t="n"/>
-      <c r="D36" s="46" t="n"/>
-      <c r="E36" s="46" t="n"/>
-      <c r="F36" s="46" t="n"/>
-      <c r="G36" s="46" t="n"/>
-      <c r="H36" s="46" t="n"/>
-      <c r="I36" s="46" t="n"/>
+      <c r="C36" s="36" t="n"/>
+      <c r="D36" s="36" t="n"/>
+      <c r="E36" s="36" t="n"/>
+      <c r="F36" s="36" t="n"/>
+      <c r="G36" s="36" t="n"/>
+      <c r="H36" s="36" t="n"/>
+      <c r="I36" s="36" t="n"/>
       <c r="J36" s="51" t="n"/>
       <c r="K36" s="51" t="n"/>
     </row>
@@ -17835,7 +17897,7 @@
           <t>Heat &amp; Temperature</t>
         </is>
       </c>
-      <c r="E39" s="67" t="inlineStr">
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>Waves, Sound &amp; Light</t>
         </is>
@@ -17849,7 +17911,7 @@
       <c r="B40" s="64" t="n"/>
       <c r="C40" s="66" t="n"/>
       <c r="D40" s="66" t="n"/>
-      <c r="E40" s="65" t="n"/>
+      <c r="E40" s="66" t="n"/>
       <c r="F40" s="54" t="n"/>
       <c r="G40" s="54" t="n"/>
       <c r="J40" s="51" t="n"/>
@@ -17875,9 +17937,9 @@
           <t>Sept_2016</t>
         </is>
       </c>
-      <c r="C42" s="40" t="n"/>
-      <c r="D42" s="40" t="n"/>
-      <c r="E42" s="40" t="n"/>
+      <c r="C42" s="36" t="n"/>
+      <c r="D42" s="36" t="n"/>
+      <c r="E42" s="36" t="n"/>
       <c r="F42" s="49" t="n"/>
       <c r="G42" s="49" t="n"/>
       <c r="J42" s="51" t="n"/>
@@ -17945,9 +18007,9 @@
           <t>Sept_2021</t>
         </is>
       </c>
-      <c r="C47" s="43" t="n"/>
-      <c r="D47" s="43" t="n"/>
-      <c r="E47" s="43" t="n"/>
+      <c r="C47" s="36" t="n"/>
+      <c r="D47" s="36" t="n"/>
+      <c r="E47" s="36" t="n"/>
       <c r="F47" s="49" t="n"/>
       <c r="G47" s="49" t="n"/>
       <c r="J47" s="51" t="n"/>
@@ -17959,9 +18021,9 @@
           <t>Sept_2022</t>
         </is>
       </c>
-      <c r="C48" s="46" t="n"/>
-      <c r="D48" s="46" t="n"/>
-      <c r="E48" s="46" t="n"/>
+      <c r="C48" s="36" t="n"/>
+      <c r="D48" s="36" t="n"/>
+      <c r="E48" s="36" t="n"/>
       <c r="F48" s="49" t="n"/>
       <c r="G48" s="49" t="n"/>
       <c r="J48" s="51" t="n"/>
@@ -18061,13 +18123,13 @@
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C54" s="40" t="n"/>
-      <c r="D54" s="40" t="n"/>
-      <c r="E54" s="40" t="n"/>
-      <c r="F54" s="40" t="n"/>
-      <c r="G54" s="40" t="n"/>
-      <c r="H54" s="40" t="n"/>
-      <c r="I54" s="40" t="n"/>
+      <c r="C54" s="36" t="n"/>
+      <c r="D54" s="36" t="n"/>
+      <c r="E54" s="36" t="n"/>
+      <c r="F54" s="36" t="n"/>
+      <c r="G54" s="36" t="n"/>
+      <c r="H54" s="36" t="n"/>
+      <c r="I54" s="36" t="n"/>
       <c r="J54" s="51" t="n"/>
       <c r="K54" s="51" t="n"/>
     </row>
@@ -18120,18 +18182,18 @@
       <c r="K57" s="51" t="n"/>
     </row>
     <row r="58">
-      <c r="B58" s="15" t="inlineStr">
+      <c r="B58" s="68" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C58" s="36" t="n"/>
-      <c r="D58" s="36" t="n"/>
-      <c r="E58" s="36" t="n"/>
-      <c r="F58" s="36" t="n"/>
-      <c r="G58" s="36" t="n"/>
-      <c r="H58" s="36" t="n"/>
-      <c r="I58" s="36" t="n"/>
+      <c r="C58" s="69" t="n"/>
+      <c r="D58" s="69" t="n"/>
+      <c r="E58" s="69" t="n"/>
+      <c r="F58" s="69" t="n"/>
+      <c r="G58" s="69" t="n"/>
+      <c r="H58" s="69" t="n"/>
+      <c r="I58" s="69" t="n"/>
       <c r="J58" s="51" t="n"/>
       <c r="K58" s="51" t="n"/>
     </row>
@@ -18142,12 +18204,12 @@
         </is>
       </c>
       <c r="C59" s="36" t="n"/>
-      <c r="D59" s="43" t="n"/>
-      <c r="E59" s="43" t="n"/>
-      <c r="F59" s="43" t="n"/>
-      <c r="G59" s="43" t="n"/>
-      <c r="H59" s="43" t="n"/>
-      <c r="I59" s="43" t="n"/>
+      <c r="D59" s="36" t="n"/>
+      <c r="E59" s="36" t="n"/>
+      <c r="F59" s="36" t="n"/>
+      <c r="G59" s="36" t="n"/>
+      <c r="H59" s="36" t="n"/>
+      <c r="I59" s="36" t="n"/>
       <c r="J59" s="51" t="n"/>
       <c r="K59" s="51" t="n"/>
     </row>
@@ -18157,13 +18219,13 @@
           <t>May/Jun_2022</t>
         </is>
       </c>
-      <c r="C60" s="46" t="n"/>
-      <c r="D60" s="46" t="n"/>
-      <c r="E60" s="46" t="n"/>
-      <c r="F60" s="46" t="n"/>
-      <c r="G60" s="46" t="n"/>
-      <c r="H60" s="46" t="n"/>
-      <c r="I60" s="46" t="n"/>
+      <c r="C60" s="36" t="n"/>
+      <c r="D60" s="36" t="n"/>
+      <c r="E60" s="36" t="n"/>
+      <c r="F60" s="36" t="n"/>
+      <c r="G60" s="36" t="n"/>
+      <c r="H60" s="36" t="n"/>
+      <c r="I60" s="36" t="n"/>
       <c r="J60" s="51" t="n"/>
       <c r="K60" s="51" t="n"/>
     </row>
@@ -18197,7 +18259,7 @@
           <t>Heat &amp; Temperature</t>
         </is>
       </c>
-      <c r="E63" s="67" t="inlineStr">
+      <c r="E63" s="12" t="inlineStr">
         <is>
           <t>Waves, Sound &amp; Light</t>
         </is>
@@ -18211,7 +18273,7 @@
       <c r="B64" s="64" t="n"/>
       <c r="C64" s="66" t="n"/>
       <c r="D64" s="66" t="n"/>
-      <c r="E64" s="65" t="n"/>
+      <c r="E64" s="66" t="n"/>
       <c r="F64" s="54" t="n"/>
       <c r="G64" s="54" t="n"/>
       <c r="J64" s="51" t="n"/>
@@ -18237,9 +18299,9 @@
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C66" s="40" t="n"/>
-      <c r="D66" s="40" t="n"/>
-      <c r="E66" s="40" t="n"/>
+      <c r="C66" s="36" t="n"/>
+      <c r="D66" s="36" t="n"/>
+      <c r="E66" s="36" t="n"/>
       <c r="F66" s="49" t="n"/>
       <c r="G66" s="49" t="n"/>
       <c r="J66" s="51" t="n"/>
@@ -18288,14 +18350,14 @@
       <c r="K69" s="51" t="n"/>
     </row>
     <row r="70">
-      <c r="B70" s="15" t="inlineStr">
+      <c r="B70" s="68" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C70" s="36" t="n"/>
-      <c r="D70" s="36" t="n"/>
-      <c r="E70" s="36" t="n"/>
+      <c r="C70" s="69" t="n"/>
+      <c r="D70" s="69" t="n"/>
+      <c r="E70" s="69" t="n"/>
       <c r="F70" s="49" t="n"/>
       <c r="G70" s="49" t="n"/>
       <c r="J70" s="51" t="n"/>
@@ -18307,9 +18369,9 @@
           <t>May/Jun_2021</t>
         </is>
       </c>
-      <c r="C71" s="43" t="n"/>
-      <c r="D71" s="43" t="n"/>
-      <c r="E71" s="43" t="n"/>
+      <c r="C71" s="36" t="n"/>
+      <c r="D71" s="36" t="n"/>
+      <c r="E71" s="36" t="n"/>
       <c r="F71" s="49" t="n"/>
       <c r="G71" s="49" t="n"/>
       <c r="J71" s="51" t="n"/>
@@ -18321,9 +18383,9 @@
           <t>May/Jun_2022</t>
         </is>
       </c>
-      <c r="C72" s="46" t="n"/>
-      <c r="D72" s="46" t="n"/>
-      <c r="E72" s="46" t="n"/>
+      <c r="C72" s="36" t="n"/>
+      <c r="D72" s="36" t="n"/>
+      <c r="E72" s="36" t="n"/>
       <c r="F72" s="49" t="n"/>
       <c r="G72" s="49" t="n"/>
       <c r="J72" s="51" t="n"/>
@@ -18423,13 +18485,13 @@
           <t>Feb/Mar_2016</t>
         </is>
       </c>
-      <c r="C78" s="40" t="n"/>
-      <c r="D78" s="40" t="n"/>
-      <c r="E78" s="40" t="n"/>
-      <c r="F78" s="40" t="n"/>
-      <c r="G78" s="40" t="n"/>
-      <c r="H78" s="40" t="n"/>
-      <c r="I78" s="40" t="n"/>
+      <c r="C78" s="36" t="n"/>
+      <c r="D78" s="36" t="n"/>
+      <c r="E78" s="36" t="n"/>
+      <c r="F78" s="36" t="n"/>
+      <c r="G78" s="36" t="n"/>
+      <c r="H78" s="36" t="n"/>
+      <c r="I78" s="36" t="n"/>
       <c r="J78" s="51" t="n"/>
       <c r="K78" s="51" t="n"/>
     </row>
@@ -18504,12 +18566,12 @@
         </is>
       </c>
       <c r="C83" s="36" t="n"/>
-      <c r="D83" s="43" t="n"/>
-      <c r="E83" s="43" t="n"/>
-      <c r="F83" s="43" t="n"/>
-      <c r="G83" s="43" t="n"/>
-      <c r="H83" s="43" t="n"/>
-      <c r="I83" s="43" t="n"/>
+      <c r="D83" s="36" t="n"/>
+      <c r="E83" s="36" t="n"/>
+      <c r="F83" s="36" t="n"/>
+      <c r="G83" s="36" t="n"/>
+      <c r="H83" s="36" t="n"/>
+      <c r="I83" s="36" t="n"/>
       <c r="J83" s="51" t="n"/>
       <c r="K83" s="51" t="n"/>
     </row>
@@ -18519,13 +18581,13 @@
           <t>Feb/Mar_2022</t>
         </is>
       </c>
-      <c r="C84" s="46" t="n"/>
-      <c r="D84" s="46" t="n"/>
-      <c r="E84" s="46" t="n"/>
-      <c r="F84" s="46" t="n"/>
-      <c r="G84" s="46" t="n"/>
-      <c r="H84" s="46" t="n"/>
-      <c r="I84" s="46" t="n"/>
+      <c r="C84" s="36" t="n"/>
+      <c r="D84" s="36" t="n"/>
+      <c r="E84" s="36" t="n"/>
+      <c r="F84" s="36" t="n"/>
+      <c r="G84" s="36" t="n"/>
+      <c r="H84" s="36" t="n"/>
+      <c r="I84" s="36" t="n"/>
       <c r="J84" s="51" t="n"/>
       <c r="K84" s="51" t="n"/>
     </row>
@@ -18559,7 +18621,7 @@
           <t>Heat &amp; Temperature</t>
         </is>
       </c>
-      <c r="E87" s="67" t="inlineStr">
+      <c r="E87" s="12" t="inlineStr">
         <is>
           <t>Waves, Sound &amp; Light</t>
         </is>
@@ -18573,7 +18635,7 @@
       <c r="B88" s="64" t="n"/>
       <c r="C88" s="66" t="n"/>
       <c r="D88" s="66" t="n"/>
-      <c r="E88" s="65" t="n"/>
+      <c r="E88" s="66" t="n"/>
       <c r="F88" s="54" t="n"/>
       <c r="G88" s="54" t="n"/>
       <c r="J88" s="51" t="n"/>
@@ -18599,9 +18661,9 @@
           <t>Feb/Mar_2016</t>
         </is>
       </c>
-      <c r="C90" s="40" t="n"/>
-      <c r="D90" s="40" t="n"/>
-      <c r="E90" s="40" t="n"/>
+      <c r="C90" s="36" t="n"/>
+      <c r="D90" s="36" t="n"/>
+      <c r="E90" s="36" t="n"/>
       <c r="F90" s="49" t="n"/>
       <c r="G90" s="49" t="n"/>
       <c r="J90" s="51" t="n"/>
@@ -18669,9 +18731,9 @@
           <t>Feb/Mar_2021</t>
         </is>
       </c>
-      <c r="C95" s="43" t="n"/>
-      <c r="D95" s="43" t="n"/>
-      <c r="E95" s="43" t="n"/>
+      <c r="C95" s="36" t="n"/>
+      <c r="D95" s="36" t="n"/>
+      <c r="E95" s="36" t="n"/>
       <c r="F95" s="49" t="n"/>
       <c r="G95" s="49" t="n"/>
       <c r="J95" s="51" t="n"/>
@@ -18683,9 +18745,9 @@
           <t>Feb/Mar_2022</t>
         </is>
       </c>
-      <c r="C96" s="46" t="n"/>
-      <c r="D96" s="46" t="n"/>
-      <c r="E96" s="46" t="n"/>
+      <c r="C96" s="36" t="n"/>
+      <c r="D96" s="36" t="n"/>
+      <c r="E96" s="36" t="n"/>
       <c r="F96" s="49" t="n"/>
       <c r="G96" s="49" t="n"/>
       <c r="J96" s="51" t="n"/>
